--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80102496</v>
+        <v>133828801</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518419.8025041927</v>
+        <v>518177</v>
       </c>
       <c r="R2" t="n">
-        <v>6897075.934320698</v>
+        <v>6896922</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +748,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-09-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +783,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80102573</v>
+        <v>133828817</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518569.9138730163</v>
+        <v>518197</v>
       </c>
       <c r="R3" t="n">
-        <v>6897144.42513525</v>
+        <v>6896885</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +868,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-09-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-09-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +903,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80102577</v>
+        <v>133828802</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,37 +926,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518584.9961028327</v>
+        <v>518181</v>
       </c>
       <c r="R4" t="n">
-        <v>6897206.107304208</v>
+        <v>6896920</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +988,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-09-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-09-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,19 +1023,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80102585</v>
+        <v>80102496</v>
       </c>
       <c r="B5" t="n">
         <v>78569</v>
@@ -1051,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518605.8736727864</v>
+        <v>518419.8025041927</v>
       </c>
       <c r="R5" t="n">
-        <v>6897233.755057353</v>
+        <v>6897075.934320698</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1123,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80102495</v>
+        <v>80102573</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
+        <v>95519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1159,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518386.4989540733</v>
+        <v>518569.9138730163</v>
       </c>
       <c r="R6" t="n">
-        <v>6897098.152638793</v>
+        <v>6897144.42513525</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1235,7 +1259,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80102575</v>
+        <v>80102577</v>
       </c>
       <c r="B7" t="n">
         <v>78569</v>
@@ -1275,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518582.8190446115</v>
+        <v>518584.9961028327</v>
       </c>
       <c r="R7" t="n">
-        <v>6897177.162566802</v>
+        <v>6897206.107304208</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1347,7 +1371,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80102493</v>
+        <v>80102585</v>
       </c>
       <c r="B8" t="n">
         <v>78569</v>
@@ -1387,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518410.7273821924</v>
+        <v>518605.8736727864</v>
       </c>
       <c r="R8" t="n">
-        <v>6897197.217424974</v>
+        <v>6897233.755057353</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1459,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80102586</v>
+        <v>80102495</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
+        <v>77258</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1499,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518597.828767497</v>
+        <v>518386.4989540733</v>
       </c>
       <c r="R9" t="n">
-        <v>6897251.909987585</v>
+        <v>6897098.152638793</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1571,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80102492</v>
+        <v>80102575</v>
       </c>
       <c r="B10" t="n">
-        <v>78596</v>
+        <v>78569</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1607,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518420.0483857279</v>
+        <v>518582.8190446115</v>
       </c>
       <c r="R10" t="n">
-        <v>6897201.934924643</v>
+        <v>6897177.162566802</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1683,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80102491</v>
+        <v>80102493</v>
       </c>
       <c r="B11" t="n">
-        <v>77258</v>
+        <v>78569</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1723,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518582.2487737532</v>
+        <v>518410.7273821924</v>
       </c>
       <c r="R11" t="n">
-        <v>6897195.825727271</v>
+        <v>6897197.217424974</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1795,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>80102582</v>
+        <v>80102586</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
+        <v>77506</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1835,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1859,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518619.1494726859</v>
+        <v>518597.828767497</v>
       </c>
       <c r="R12" t="n">
-        <v>6897199.296031502</v>
+        <v>6897251.909987585</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1907,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80102507</v>
+        <v>80102492</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
+        <v>78596</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1943,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1971,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518235.0579339796</v>
+        <v>518420.0483857279</v>
       </c>
       <c r="R13" t="n">
-        <v>6896928.857831408</v>
+        <v>6897201.934924643</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2019,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>80102576</v>
+        <v>80102491</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
+        <v>77258</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2059,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2083,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518585.5818316408</v>
+        <v>518582.2487737532</v>
       </c>
       <c r="R14" t="n">
-        <v>6897184.644339841</v>
+        <v>6897195.825727271</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2131,7 +2155,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>80102578</v>
+        <v>80102582</v>
       </c>
       <c r="B15" t="n">
         <v>78569</v>
@@ -2171,10 +2195,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518601.370494597</v>
+        <v>518619.1494726859</v>
       </c>
       <c r="R15" t="n">
-        <v>6897202.931076979</v>
+        <v>6897199.296031502</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2243,7 +2267,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>80102584</v>
+        <v>80102507</v>
       </c>
       <c r="B16" t="n">
         <v>78569</v>
@@ -2283,10 +2307,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518611.5975138397</v>
+        <v>518235.0579339796</v>
       </c>
       <c r="R16" t="n">
-        <v>6897212.787302623</v>
+        <v>6896928.857831408</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2355,7 +2379,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>80102583</v>
+        <v>80102576</v>
       </c>
       <c r="B17" t="n">
         <v>78569</v>
@@ -2395,10 +2419,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518610.2264721559</v>
+        <v>518585.5818316408</v>
       </c>
       <c r="R17" t="n">
-        <v>6897207.179876219</v>
+        <v>6897184.644339841</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2467,7 +2491,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>80102579</v>
+        <v>80102578</v>
       </c>
       <c r="B18" t="n">
         <v>78569</v>
@@ -2507,10 +2531,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518627.9899583974</v>
+        <v>518601.370494597</v>
       </c>
       <c r="R18" t="n">
-        <v>6897206.344727577</v>
+        <v>6897202.931076979</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2579,7 +2603,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>80102484</v>
+        <v>80102584</v>
       </c>
       <c r="B19" t="n">
         <v>78569</v>
@@ -2619,10 +2643,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518324.1013247595</v>
+        <v>518611.5975138397</v>
       </c>
       <c r="R19" t="n">
-        <v>6897056.278893237</v>
+        <v>6897212.787302623</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2649,7 +2673,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2019-09-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2659,7 +2683,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2019-09-19</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2688,6 +2712,8564 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>80102583</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78569</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>518610.2264721559</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6897207.179876219</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2019-09-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2019-09-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>80102579</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78569</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>518627.9899583974</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6897206.344727577</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2019-09-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2019-09-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>80102484</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78569</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>518324.1013247595</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6897056.278893237</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133828824</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>518273</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6896829</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133828823</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>518272</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6896819</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>20 ex</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133828845</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>518477</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6897110</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>50 ex</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133828841</v>
+      </c>
+      <c r="B26" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>308</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>518489</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6897064</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133828848</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>518510</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6897194</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133828837</v>
+      </c>
+      <c r="B28" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>308</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>518437</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6897050</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133828789</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>518446</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6897134</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>10 ex</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133828807</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>518247</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6896909</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133828775</v>
+      </c>
+      <c r="B31" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>308</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>518420</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6897194</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133828821</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>518263</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6896809</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133828813</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>518235</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6896853</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133828831</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>518389</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6897022</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133828825</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>518279</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6896843</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1 ex</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133828820</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>518236</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6896830</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133828790</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>518391</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6897080</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>16 ex</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>133828829</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>518329</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6896969</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>20 ex</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133828840</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>518482</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6897062</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>133828788</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79090</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>518403</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6897135</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>133828792</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>518356</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6897080</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>133828796</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79090</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>518327</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6897018</v>
+      </c>
+      <c r="S42" t="n">
+        <v>6</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>133828818</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>518222</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6896820</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>133828805</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>518243</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6896917</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>3 ex</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>133828811</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>518240</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6896871</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>133828793</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79365</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>185</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>518352</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6897090</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>133828816</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>518222</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6896862</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>133828800</v>
+      </c>
+      <c r="B48" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>308</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>518301</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6896988</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>133828778</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>518437</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6897164</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>133828783</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>518406</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6897153</v>
+      </c>
+      <c r="S50" t="n">
+        <v>7</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>11 ex</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>133828819</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>518221</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6896825</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>133828833</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>518405</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6897021</v>
+      </c>
+      <c r="S52" t="n">
+        <v>7</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>133828773</v>
+      </c>
+      <c r="B53" t="n">
+        <v>83315</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>518414</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6897216</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>133828806</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>518246</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6896911</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>133828784</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>518400</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6897160</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>5 ex</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>133828850</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>518594</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6897257</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>133828809</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>518251</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6896886</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>133828812</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80439</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>518235</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6896851</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>133828776</v>
+      </c>
+      <c r="B59" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>308</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>518435</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6897176</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>133828795</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79090</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>518327</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6897030</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>133828847</v>
+      </c>
+      <c r="B61" t="n">
+        <v>83315</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>518474</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6897109</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>133828822</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>518264</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6896807</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>1 ex</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>133828797</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>518329</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6897013</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>133828779</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>518437</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6897164</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>133828839</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>518455</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6897046</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>133828851</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>518585</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6897256</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>15 ex</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>133828777</v>
+      </c>
+      <c r="B67" t="n">
+        <v>83298</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>518435</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6897176</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>133828798</v>
+      </c>
+      <c r="B68" t="n">
+        <v>83298</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>518339</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6897004</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>133828827</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>518303</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6896962</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>133828808</v>
+      </c>
+      <c r="B70" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>518250</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6896903</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>133828843</v>
+      </c>
+      <c r="B71" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>518502</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6897111</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>133828849</v>
+      </c>
+      <c r="B72" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>518564</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6897207</v>
+      </c>
+      <c r="S72" t="n">
+        <v>6</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>133828803</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>518221</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6896911</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>3 ex</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>133828771</v>
+      </c>
+      <c r="B74" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>518411</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6897234</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>133828787</v>
+      </c>
+      <c r="B75" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>308</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>518402</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6897136</v>
+      </c>
+      <c r="S75" t="n">
+        <v>6</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>133828826</v>
+      </c>
+      <c r="B76" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>308</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>518269</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6896902</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>133828815</v>
+      </c>
+      <c r="B77" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>518230</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6896858</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>133828772</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>518419</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6897228</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>7 ex</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>133828780</v>
+      </c>
+      <c r="B79" t="n">
+        <v>97243</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>518441</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6897163</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>133828836</v>
+      </c>
+      <c r="B80" t="n">
+        <v>83315</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>518403</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6897037</v>
+      </c>
+      <c r="S80" t="n">
+        <v>6</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>133828786</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>518399</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6897137</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>85 ex</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>133828799</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>518312</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6896987</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>133828782</v>
+      </c>
+      <c r="B83" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>518424</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6897159</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>133828814</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>518236</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6896855</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>45 ex</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>133828791</v>
+      </c>
+      <c r="B85" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>308</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>518371</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6897086</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>133828830</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>518373</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6897009</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>9 ex</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>133828835</v>
+      </c>
+      <c r="B87" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>518407</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6897030</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>133828781</v>
+      </c>
+      <c r="B88" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>308</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>518427</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6897159</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>133828838</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79090</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>518440</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6897045</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>133828834</v>
+      </c>
+      <c r="B90" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>518405</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6897020</v>
+      </c>
+      <c r="S90" t="n">
+        <v>7</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>133828844</v>
+      </c>
+      <c r="B91" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>518502</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6897113</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>133828804</v>
+      </c>
+      <c r="B92" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>518231</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6896913</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>133828810</v>
+      </c>
+      <c r="B93" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>518240</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6896871</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>133828785</v>
+      </c>
+      <c r="B94" t="n">
+        <v>80342</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>518394</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6897139</v>
+      </c>
+      <c r="S94" t="n">
+        <v>6</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>133828842</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79090</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>518539</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6897099</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>133828852</v>
+      </c>
+      <c r="B96" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>518557</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6897217</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>133828794</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>518380</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6897032</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -3054,7 +3054,7 @@
         <v>133828824</v>
       </c>
       <c r="B23" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,10 +3158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133828823</v>
+        <v>133828845</v>
       </c>
       <c r="B24" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518272</v>
+        <v>518477</v>
       </c>
       <c r="R24" t="n">
-        <v>6896819</v>
+        <v>6897110</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,10 +3270,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133828845</v>
+        <v>133828823</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3305,10 +3305,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518477</v>
+        <v>518272</v>
       </c>
       <c r="R25" t="n">
-        <v>6897110</v>
+        <v>6896819</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3385,7 +3385,7 @@
         <v>133828841</v>
       </c>
       <c r="B26" t="n">
-        <v>83307</v>
+        <v>83308</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>133828837</v>
       </c>
       <c r="B28" t="n">
-        <v>83307</v>
+        <v>83308</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>133828789</v>
       </c>
       <c r="B29" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3828,10 +3828,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828807</v>
+        <v>133828775</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>83308</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3839,21 +3839,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518247</v>
+        <v>518420</v>
       </c>
       <c r="R30" t="n">
-        <v>6896909</v>
+        <v>6897194</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3935,10 +3935,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133828775</v>
+        <v>133828807</v>
       </c>
       <c r="B31" t="n">
-        <v>83307</v>
+        <v>79334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3946,21 +3946,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518420</v>
+        <v>518247</v>
       </c>
       <c r="R31" t="n">
-        <v>6897194</v>
+        <v>6896909</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4042,10 +4042,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828821</v>
+        <v>133828831</v>
       </c>
       <c r="B32" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518263</v>
+        <v>518389</v>
       </c>
       <c r="R32" t="n">
-        <v>6896809</v>
+        <v>6897022</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4152,7 +4152,7 @@
         <v>133828813</v>
       </c>
       <c r="B33" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133828831</v>
+        <v>133828820</v>
       </c>
       <c r="B34" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518389</v>
+        <v>518236</v>
       </c>
       <c r="R34" t="n">
-        <v>6897022</v>
+        <v>6896830</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4363,32 +4363,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133828825</v>
+        <v>133828821</v>
       </c>
       <c r="B35" t="n">
-        <v>99130</v>
+        <v>80439</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518279</v>
+        <v>518263</v>
       </c>
       <c r="R35" t="n">
-        <v>6896843</v>
+        <v>6896809</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4443,12 +4443,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1 ex</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4475,32 +4470,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133828820</v>
+        <v>133828825</v>
       </c>
       <c r="B36" t="n">
-        <v>80438</v>
+        <v>99132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4510,10 +4505,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518236</v>
+        <v>518279</v>
       </c>
       <c r="R36" t="n">
-        <v>6896830</v>
+        <v>6896843</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4545,7 +4540,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4555,7 +4550,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4582,10 +4582,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133828790</v>
+        <v>133828829</v>
       </c>
       <c r="B37" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518391</v>
+        <v>518329</v>
       </c>
       <c r="R37" t="n">
-        <v>6897080</v>
+        <v>6896969</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>16 ex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4694,10 +4694,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133828829</v>
+        <v>133828790</v>
       </c>
       <c r="B38" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518329</v>
+        <v>518391</v>
       </c>
       <c r="R38" t="n">
-        <v>6896969</v>
+        <v>6897080</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>16 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4806,10 +4806,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133828840</v>
+        <v>133828788</v>
       </c>
       <c r="B39" t="n">
-        <v>57958</v>
+        <v>79091</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4817,42 +4817,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518482</v>
+        <v>518403</v>
       </c>
       <c r="R39" t="n">
-        <v>6897062</v>
+        <v>6897135</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4884,7 +4876,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4894,12 +4886,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4926,10 +4913,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133828788</v>
+        <v>133828840</v>
       </c>
       <c r="B40" t="n">
-        <v>79090</v>
+        <v>57958</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4937,34 +4924,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518403</v>
+        <v>518482</v>
       </c>
       <c r="R40" t="n">
-        <v>6897135</v>
+        <v>6897062</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4996,7 +4991,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5006,7 +5001,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5033,10 +5033,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133828792</v>
+        <v>133828796</v>
       </c>
       <c r="B41" t="n">
-        <v>57958</v>
+        <v>79091</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5044,45 +5044,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518356</v>
+        <v>518327</v>
       </c>
       <c r="R41" t="n">
-        <v>6897080</v>
+        <v>6897018</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5111,7 +5103,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5121,12 +5113,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5153,10 +5140,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133828796</v>
+        <v>133828818</v>
       </c>
       <c r="B42" t="n">
-        <v>79090</v>
+        <v>57958</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5164,37 +5151,45 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518327</v>
+        <v>518222</v>
       </c>
       <c r="R42" t="n">
-        <v>6897018</v>
+        <v>6896820</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5223,7 +5218,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5233,7 +5228,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5260,7 +5260,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133828818</v>
+        <v>133828792</v>
       </c>
       <c r="B43" t="n">
         <v>57958</v>
@@ -5303,10 +5303,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518222</v>
+        <v>518356</v>
       </c>
       <c r="R43" t="n">
-        <v>6896820</v>
+        <v>6897080</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5380,32 +5380,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133828805</v>
+        <v>133828811</v>
       </c>
       <c r="B44" t="n">
-        <v>99130</v>
+        <v>80439</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518243</v>
+        <v>518240</v>
       </c>
       <c r="R44" t="n">
-        <v>6896917</v>
+        <v>6896871</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5460,12 +5460,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5492,32 +5487,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133828811</v>
+        <v>133828805</v>
       </c>
       <c r="B45" t="n">
-        <v>80438</v>
+        <v>99132</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5527,10 +5522,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518240</v>
+        <v>518243</v>
       </c>
       <c r="R45" t="n">
-        <v>6896871</v>
+        <v>6896917</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5562,7 +5557,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5572,7 +5567,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5602,7 +5602,7 @@
         <v>133828793</v>
       </c>
       <c r="B46" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5706,10 +5706,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133828816</v>
+        <v>133828800</v>
       </c>
       <c r="B47" t="n">
-        <v>79333</v>
+        <v>83308</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5717,21 +5717,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518222</v>
+        <v>518301</v>
       </c>
       <c r="R47" t="n">
-        <v>6896862</v>
+        <v>6896988</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5813,10 +5813,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133828800</v>
+        <v>133828816</v>
       </c>
       <c r="B48" t="n">
-        <v>83307</v>
+        <v>79334</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5824,21 +5824,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518301</v>
+        <v>518222</v>
       </c>
       <c r="R48" t="n">
-        <v>6896988</v>
+        <v>6896862</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5923,7 +5923,7 @@
         <v>133828778</v>
       </c>
       <c r="B49" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>133828783</v>
       </c>
       <c r="B50" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6139,10 +6139,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133828819</v>
+        <v>133828773</v>
       </c>
       <c r="B51" t="n">
-        <v>57958</v>
+        <v>83316</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6150,42 +6150,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518221</v>
+        <v>518414</v>
       </c>
       <c r="R51" t="n">
-        <v>6896825</v>
+        <v>6897216</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6217,7 +6209,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6227,12 +6219,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6262,7 +6249,7 @@
         <v>133828833</v>
       </c>
       <c r="B52" t="n">
-        <v>80467</v>
+        <v>80468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6366,10 +6353,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133828773</v>
+        <v>133828819</v>
       </c>
       <c r="B53" t="n">
-        <v>83315</v>
+        <v>57958</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6377,34 +6364,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518414</v>
+        <v>518221</v>
       </c>
       <c r="R53" t="n">
-        <v>6897216</v>
+        <v>6896825</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6436,7 +6431,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6446,7 +6441,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6476,7 +6476,7 @@
         <v>133828806</v>
       </c>
       <c r="B54" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6580,32 +6580,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133828784</v>
+        <v>133828809</v>
       </c>
       <c r="B55" t="n">
-        <v>99130</v>
+        <v>80439</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518400</v>
+        <v>518251</v>
       </c>
       <c r="R55" t="n">
-        <v>6897160</v>
+        <v>6896886</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6660,12 +6660,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>5 ex</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6695,7 +6690,7 @@
         <v>133828850</v>
       </c>
       <c r="B56" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6799,32 +6794,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133828809</v>
+        <v>133828784</v>
       </c>
       <c r="B57" t="n">
-        <v>80438</v>
+        <v>99132</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6834,10 +6829,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518251</v>
+        <v>518400</v>
       </c>
       <c r="R57" t="n">
-        <v>6896886</v>
+        <v>6897160</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6869,7 +6864,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6879,7 +6874,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6909,7 +6909,7 @@
         <v>133828812</v>
       </c>
       <c r="B58" t="n">
-        <v>80439</v>
+        <v>80440</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7013,10 +7013,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133828776</v>
+        <v>133828795</v>
       </c>
       <c r="B59" t="n">
-        <v>83307</v>
+        <v>79091</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7024,21 +7024,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>308</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518435</v>
+        <v>518327</v>
       </c>
       <c r="R59" t="n">
-        <v>6897176</v>
+        <v>6897030</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7120,10 +7120,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133828795</v>
+        <v>133828776</v>
       </c>
       <c r="B60" t="n">
-        <v>79090</v>
+        <v>83308</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7131,21 +7131,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518327</v>
+        <v>518435</v>
       </c>
       <c r="R60" t="n">
-        <v>6897030</v>
+        <v>6897176</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7227,10 +7227,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133828847</v>
+        <v>133828797</v>
       </c>
       <c r="B61" t="n">
-        <v>83315</v>
+        <v>57958</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7238,34 +7238,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518474</v>
+        <v>518329</v>
       </c>
       <c r="R61" t="n">
-        <v>6897109</v>
+        <v>6897013</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7297,7 +7305,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7307,7 +7315,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7337,7 +7350,7 @@
         <v>133828822</v>
       </c>
       <c r="B62" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7446,10 +7459,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133828797</v>
+        <v>133828847</v>
       </c>
       <c r="B63" t="n">
-        <v>57958</v>
+        <v>83316</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7457,42 +7470,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518329</v>
+        <v>518474</v>
       </c>
       <c r="R63" t="n">
-        <v>6897013</v>
+        <v>6897109</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7524,7 +7529,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7534,12 +7539,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7569,7 +7569,7 @@
         <v>133828779</v>
       </c>
       <c r="B64" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>133828851</v>
       </c>
       <c r="B66" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7905,32 +7905,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133828777</v>
+        <v>133828808</v>
       </c>
       <c r="B67" t="n">
-        <v>83298</v>
+        <v>80439</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7940,10 +7940,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518435</v>
+        <v>518250</v>
       </c>
       <c r="R67" t="n">
-        <v>6897176</v>
+        <v>6896903</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8015,7 +8015,7 @@
         <v>133828798</v>
       </c>
       <c r="B68" t="n">
-        <v>83298</v>
+        <v>83299</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8119,53 +8119,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133828827</v>
+        <v>133828777</v>
       </c>
       <c r="B69" t="n">
-        <v>57958</v>
+        <v>83299</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>518303</v>
+        <v>518435</v>
       </c>
       <c r="R69" t="n">
-        <v>6896962</v>
+        <v>6897176</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8197,7 +8189,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8207,12 +8199,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8239,10 +8226,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133828808</v>
+        <v>133828827</v>
       </c>
       <c r="B70" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8250,34 +8237,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>518250</v>
+        <v>518303</v>
       </c>
       <c r="R70" t="n">
-        <v>6896903</v>
+        <v>6896962</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8309,7 +8304,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8319,7 +8314,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8346,32 +8346,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133828843</v>
+        <v>133828849</v>
       </c>
       <c r="B71" t="n">
-        <v>80467</v>
+        <v>80439</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518502</v>
+        <v>518564</v>
       </c>
       <c r="R71" t="n">
-        <v>6897111</v>
+        <v>6897207</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8453,32 +8453,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133828849</v>
+        <v>133828843</v>
       </c>
       <c r="B72" t="n">
-        <v>80438</v>
+        <v>80468</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8488,13 +8488,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>518564</v>
+        <v>518502</v>
       </c>
       <c r="R72" t="n">
-        <v>6897207</v>
+        <v>6897111</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8560,32 +8560,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133828803</v>
+        <v>133828771</v>
       </c>
       <c r="B73" t="n">
-        <v>99130</v>
+        <v>80468</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8595,10 +8595,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>518221</v>
+        <v>518411</v>
       </c>
       <c r="R73" t="n">
-        <v>6896911</v>
+        <v>6897234</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8640,12 +8640,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8672,32 +8667,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133828771</v>
+        <v>133828787</v>
       </c>
       <c r="B74" t="n">
-        <v>80467</v>
+        <v>83308</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8707,13 +8702,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518411</v>
+        <v>518402</v>
       </c>
       <c r="R74" t="n">
-        <v>6897234</v>
+        <v>6897136</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8742,7 +8737,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8752,7 +8747,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8779,32 +8774,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133828787</v>
+        <v>133828803</v>
       </c>
       <c r="B75" t="n">
-        <v>83307</v>
+        <v>99132</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8814,13 +8809,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>518402</v>
+        <v>518221</v>
       </c>
       <c r="R75" t="n">
-        <v>6897136</v>
+        <v>6896911</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8849,7 +8844,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8859,7 +8854,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8889,7 +8889,7 @@
         <v>133828826</v>
       </c>
       <c r="B76" t="n">
-        <v>83307</v>
+        <v>83308</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>133828815</v>
       </c>
       <c r="B77" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>133828772</v>
       </c>
       <c r="B78" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>133828780</v>
       </c>
       <c r="B79" t="n">
-        <v>97243</v>
+        <v>97245</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>133828836</v>
       </c>
       <c r="B80" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>133828786</v>
       </c>
       <c r="B81" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9538,10 +9538,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133828799</v>
+        <v>133828782</v>
       </c>
       <c r="B82" t="n">
-        <v>57958</v>
+        <v>80439</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9549,42 +9549,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>518312</v>
+        <v>518424</v>
       </c>
       <c r="R82" t="n">
-        <v>6896987</v>
+        <v>6897159</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9616,7 +9608,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9626,12 +9618,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9658,10 +9645,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133828782</v>
+        <v>133828799</v>
       </c>
       <c r="B83" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9669,34 +9656,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>518424</v>
+        <v>518312</v>
       </c>
       <c r="R83" t="n">
-        <v>6897159</v>
+        <v>6896987</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9728,7 +9723,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9738,7 +9733,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9765,32 +9765,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133828814</v>
+        <v>133828791</v>
       </c>
       <c r="B84" t="n">
-        <v>99130</v>
+        <v>83308</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518236</v>
+        <v>518371</v>
       </c>
       <c r="R84" t="n">
-        <v>6896855</v>
+        <v>6897086</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9845,12 +9845,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>45 ex</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9877,10 +9872,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133828791</v>
+        <v>133828781</v>
       </c>
       <c r="B85" t="n">
-        <v>83307</v>
+        <v>83308</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9912,10 +9907,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518371</v>
+        <v>518427</v>
       </c>
       <c r="R85" t="n">
-        <v>6897086</v>
+        <v>6897159</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9947,7 +9942,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9957,7 +9952,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9984,32 +9979,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133828830</v>
+        <v>133828835</v>
       </c>
       <c r="B86" t="n">
-        <v>99130</v>
+        <v>80439</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10019,10 +10014,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518373</v>
+        <v>518407</v>
       </c>
       <c r="R86" t="n">
-        <v>6897009</v>
+        <v>6897030</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10054,7 +10049,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10064,12 +10059,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>9 ex</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10096,32 +10086,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133828835</v>
+        <v>133828830</v>
       </c>
       <c r="B87" t="n">
-        <v>80438</v>
+        <v>99132</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10131,10 +10121,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518407</v>
+        <v>518373</v>
       </c>
       <c r="R87" t="n">
-        <v>6897030</v>
+        <v>6897009</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10166,7 +10156,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10176,7 +10166,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10203,32 +10198,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133828781</v>
+        <v>133828814</v>
       </c>
       <c r="B88" t="n">
-        <v>83307</v>
+        <v>99132</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10238,10 +10233,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>518427</v>
+        <v>518236</v>
       </c>
       <c r="R88" t="n">
-        <v>6897159</v>
+        <v>6896855</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10273,7 +10268,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10283,7 +10278,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10313,7 +10313,7 @@
         <v>133828838</v>
       </c>
       <c r="B89" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10417,10 +10417,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133828834</v>
+        <v>133828844</v>
       </c>
       <c r="B90" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10452,13 +10452,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>518405</v>
+        <v>518502</v>
       </c>
       <c r="R90" t="n">
-        <v>6897020</v>
+        <v>6897113</v>
       </c>
       <c r="S90" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10524,10 +10524,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133828844</v>
+        <v>133828834</v>
       </c>
       <c r="B91" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>518502</v>
+        <v>518405</v>
       </c>
       <c r="R91" t="n">
-        <v>6897113</v>
+        <v>6897020</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10631,32 +10631,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133828804</v>
+        <v>133828810</v>
       </c>
       <c r="B92" t="n">
-        <v>80438</v>
+        <v>80468</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10666,10 +10666,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>518231</v>
+        <v>518240</v>
       </c>
       <c r="R92" t="n">
-        <v>6896913</v>
+        <v>6896871</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10738,32 +10738,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133828810</v>
+        <v>133828804</v>
       </c>
       <c r="B93" t="n">
-        <v>80467</v>
+        <v>80439</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10773,10 +10773,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>518240</v>
+        <v>518231</v>
       </c>
       <c r="R93" t="n">
-        <v>6896871</v>
+        <v>6896913</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10845,32 +10845,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133828785</v>
+        <v>133828794</v>
       </c>
       <c r="B94" t="n">
-        <v>80342</v>
+        <v>79334</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10880,13 +10880,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>518394</v>
+        <v>518380</v>
       </c>
       <c r="R94" t="n">
-        <v>6897139</v>
+        <v>6897032</v>
       </c>
       <c r="S94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10952,32 +10952,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133828842</v>
+        <v>133828785</v>
       </c>
       <c r="B95" t="n">
-        <v>79090</v>
+        <v>80343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>518539</v>
+        <v>518394</v>
       </c>
       <c r="R95" t="n">
-        <v>6897099</v>
+        <v>6897139</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11059,10 +11059,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133828852</v>
+        <v>133828842</v>
       </c>
       <c r="B96" t="n">
-        <v>80438</v>
+        <v>79091</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11070,21 +11070,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>518557</v>
+        <v>518539</v>
       </c>
       <c r="R96" t="n">
-        <v>6897217</v>
+        <v>6897099</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11166,10 +11166,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133828794</v>
+        <v>133828852</v>
       </c>
       <c r="B97" t="n">
-        <v>79333</v>
+        <v>80439</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11177,21 +11177,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11201,10 +11201,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>518380</v>
+        <v>518557</v>
       </c>
       <c r="R97" t="n">
-        <v>6897032</v>
+        <v>6897217</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -3382,32 +3382,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133828841</v>
+        <v>133828789</v>
       </c>
       <c r="B26" t="n">
-        <v>83308</v>
+        <v>99132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3417,13 +3417,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518489</v>
+        <v>518446</v>
       </c>
       <c r="R26" t="n">
-        <v>6897064</v>
+        <v>6897134</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,7 +3462,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3489,10 +3494,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133828848</v>
+        <v>133828841</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>83308</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3500,42 +3505,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518510</v>
+        <v>518489</v>
       </c>
       <c r="R27" t="n">
-        <v>6897194</v>
+        <v>6897064</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3567,7 +3564,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3577,12 +3574,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3609,10 +3601,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133828837</v>
+        <v>133828848</v>
       </c>
       <c r="B28" t="n">
-        <v>83308</v>
+        <v>57958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3620,34 +3612,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518437</v>
+        <v>518510</v>
       </c>
       <c r="R28" t="n">
-        <v>6897050</v>
+        <v>6897194</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3689,7 +3689,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3716,32 +3721,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133828789</v>
+        <v>133828837</v>
       </c>
       <c r="B29" t="n">
-        <v>99132</v>
+        <v>83308</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3751,13 +3756,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518446</v>
+        <v>518437</v>
       </c>
       <c r="R29" t="n">
-        <v>6897134</v>
+        <v>6897050</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3786,7 +3791,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3796,12 +3801,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -6473,10 +6473,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133828806</v>
+        <v>133828850</v>
       </c>
       <c r="B54" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6484,21 +6484,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518246</v>
+        <v>518594</v>
       </c>
       <c r="R54" t="n">
-        <v>6896911</v>
+        <v>6897257</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6580,7 +6580,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133828809</v>
+        <v>133828806</v>
       </c>
       <c r="B55" t="n">
         <v>80439</v>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518251</v>
+        <v>518246</v>
       </c>
       <c r="R55" t="n">
-        <v>6896886</v>
+        <v>6896911</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6687,10 +6687,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133828850</v>
+        <v>133828809</v>
       </c>
       <c r="B56" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6698,21 +6698,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6722,10 +6722,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518594</v>
+        <v>518251</v>
       </c>
       <c r="R56" t="n">
-        <v>6897257</v>
+        <v>6896886</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6906,10 +6906,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133828812</v>
+        <v>133828776</v>
       </c>
       <c r="B58" t="n">
-        <v>80440</v>
+        <v>83308</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6917,21 +6917,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6941,10 +6941,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518235</v>
+        <v>518435</v>
       </c>
       <c r="R58" t="n">
-        <v>6896851</v>
+        <v>6897176</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7013,10 +7013,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133828795</v>
+        <v>133828812</v>
       </c>
       <c r="B59" t="n">
-        <v>79091</v>
+        <v>80440</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7024,21 +7024,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518327</v>
+        <v>518235</v>
       </c>
       <c r="R59" t="n">
-        <v>6897030</v>
+        <v>6896851</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7120,10 +7120,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133828776</v>
+        <v>133828795</v>
       </c>
       <c r="B60" t="n">
-        <v>83308</v>
+        <v>79091</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7131,21 +7131,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>308</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518435</v>
+        <v>518327</v>
       </c>
       <c r="R60" t="n">
-        <v>6897176</v>
+        <v>6897030</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8886,10 +8886,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133828826</v>
+        <v>133828815</v>
       </c>
       <c r="B76" t="n">
-        <v>83308</v>
+        <v>80439</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8897,21 +8897,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>518269</v>
+        <v>518230</v>
       </c>
       <c r="R76" t="n">
-        <v>6896902</v>
+        <v>6896858</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8993,32 +8993,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133828815</v>
+        <v>133828772</v>
       </c>
       <c r="B77" t="n">
-        <v>80439</v>
+        <v>99132</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>518230</v>
+        <v>518419</v>
       </c>
       <c r="R77" t="n">
-        <v>6896858</v>
+        <v>6897228</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9073,7 +9073,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9100,32 +9105,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133828772</v>
+        <v>133828826</v>
       </c>
       <c r="B78" t="n">
-        <v>99132</v>
+        <v>83308</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9135,10 +9140,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>518419</v>
+        <v>518269</v>
       </c>
       <c r="R78" t="n">
-        <v>6897228</v>
+        <v>6896902</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9170,7 +9175,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9180,12 +9185,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>7 ex</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9426,32 +9426,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133828786</v>
+        <v>133828782</v>
       </c>
       <c r="B81" t="n">
-        <v>99132</v>
+        <v>80439</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>518399</v>
+        <v>518424</v>
       </c>
       <c r="R81" t="n">
-        <v>6897137</v>
+        <v>6897159</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9506,12 +9506,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:33</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>85 ex</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9538,10 +9533,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133828782</v>
+        <v>133828799</v>
       </c>
       <c r="B82" t="n">
-        <v>80439</v>
+        <v>57958</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9549,34 +9544,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>518424</v>
+        <v>518312</v>
       </c>
       <c r="R82" t="n">
-        <v>6897159</v>
+        <v>6896987</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9608,7 +9611,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9618,7 +9621,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9645,53 +9653,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133828799</v>
+        <v>133828786</v>
       </c>
       <c r="B83" t="n">
-        <v>57958</v>
+        <v>99132</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>518312</v>
+        <v>518399</v>
       </c>
       <c r="R83" t="n">
-        <v>6896987</v>
+        <v>6897137</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9733,12 +9733,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9765,32 +9765,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133828791</v>
+        <v>133828814</v>
       </c>
       <c r="B84" t="n">
-        <v>83308</v>
+        <v>99132</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518371</v>
+        <v>518236</v>
       </c>
       <c r="R84" t="n">
-        <v>6897086</v>
+        <v>6896855</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9845,7 +9845,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9872,7 +9877,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133828781</v>
+        <v>133828791</v>
       </c>
       <c r="B85" t="n">
         <v>83308</v>
@@ -9907,10 +9912,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518427</v>
+        <v>518371</v>
       </c>
       <c r="R85" t="n">
-        <v>6897159</v>
+        <v>6897086</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9942,7 +9947,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9952,7 +9957,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9979,10 +9984,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133828835</v>
+        <v>133828781</v>
       </c>
       <c r="B86" t="n">
-        <v>80439</v>
+        <v>83308</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9990,21 +9995,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10014,10 +10019,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518407</v>
+        <v>518427</v>
       </c>
       <c r="R86" t="n">
-        <v>6897030</v>
+        <v>6897159</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10049,7 +10054,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10059,7 +10064,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10086,32 +10091,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133828830</v>
+        <v>133828835</v>
       </c>
       <c r="B87" t="n">
-        <v>99132</v>
+        <v>80439</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10121,10 +10126,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518373</v>
+        <v>518407</v>
       </c>
       <c r="R87" t="n">
-        <v>6897009</v>
+        <v>6897030</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10156,7 +10161,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10166,12 +10171,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>9 ex</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10198,7 +10198,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133828814</v>
+        <v>133828830</v>
       </c>
       <c r="B88" t="n">
         <v>99132</v>
@@ -10233,10 +10233,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>518236</v>
+        <v>518373</v>
       </c>
       <c r="R88" t="n">
-        <v>6896855</v>
+        <v>6897009</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10278,12 +10278,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -3054,7 +3054,7 @@
         <v>133828824</v>
       </c>
       <c r="B23" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>133828845</v>
       </c>
       <c r="B24" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>133828823</v>
       </c>
       <c r="B25" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,32 +3382,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133828789</v>
+        <v>133828841</v>
       </c>
       <c r="B26" t="n">
-        <v>99132</v>
+        <v>83310</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3417,13 +3417,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518446</v>
+        <v>518489</v>
       </c>
       <c r="R26" t="n">
-        <v>6897134</v>
+        <v>6897064</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,12 +3462,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3494,10 +3489,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133828841</v>
+        <v>133828837</v>
       </c>
       <c r="B27" t="n">
-        <v>83308</v>
+        <v>83310</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,10 +3524,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518489</v>
+        <v>518437</v>
       </c>
       <c r="R27" t="n">
-        <v>6897064</v>
+        <v>6897050</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3564,7 +3559,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3574,7 +3569,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3721,32 +3716,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133828837</v>
+        <v>133828789</v>
       </c>
       <c r="B29" t="n">
-        <v>83308</v>
+        <v>99138</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3756,13 +3751,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518437</v>
+        <v>518446</v>
       </c>
       <c r="R29" t="n">
-        <v>6897050</v>
+        <v>6897134</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3791,7 +3786,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3801,7 +3796,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,7 +3831,7 @@
         <v>133828775</v>
       </c>
       <c r="B30" t="n">
-        <v>83308</v>
+        <v>83310</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133828807</v>
+        <v>133828831</v>
       </c>
       <c r="B31" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3946,21 +3946,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518247</v>
+        <v>518389</v>
       </c>
       <c r="R31" t="n">
-        <v>6896909</v>
+        <v>6897022</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4042,7 +4042,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828831</v>
+        <v>133828813</v>
       </c>
       <c r="B32" t="n">
         <v>80439</v>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518389</v>
+        <v>518235</v>
       </c>
       <c r="R32" t="n">
-        <v>6897022</v>
+        <v>6896853</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4149,7 +4149,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133828813</v>
+        <v>133828820</v>
       </c>
       <c r="B33" t="n">
         <v>80439</v>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518235</v>
+        <v>518236</v>
       </c>
       <c r="R33" t="n">
-        <v>6896853</v>
+        <v>6896830</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,7 +4256,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133828820</v>
+        <v>133828821</v>
       </c>
       <c r="B34" t="n">
         <v>80439</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518236</v>
+        <v>518263</v>
       </c>
       <c r="R34" t="n">
-        <v>6896830</v>
+        <v>6896809</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4363,10 +4363,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133828821</v>
+        <v>133828807</v>
       </c>
       <c r="B35" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518263</v>
+        <v>518247</v>
       </c>
       <c r="R35" t="n">
-        <v>6896809</v>
+        <v>6896909</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4473,7 +4473,7 @@
         <v>133828825</v>
       </c>
       <c r="B36" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4582,32 +4582,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133828829</v>
+        <v>133828788</v>
       </c>
       <c r="B37" t="n">
-        <v>99132</v>
+        <v>79091</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518329</v>
+        <v>518403</v>
       </c>
       <c r="R37" t="n">
-        <v>6896969</v>
+        <v>6897135</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4662,12 +4662,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4694,45 +4689,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133828790</v>
+        <v>133828840</v>
       </c>
       <c r="B38" t="n">
-        <v>99132</v>
+        <v>57958</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518391</v>
+        <v>518482</v>
       </c>
       <c r="R38" t="n">
-        <v>6897080</v>
+        <v>6897062</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4764,7 +4767,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4774,12 +4777,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>16 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4806,32 +4809,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133828788</v>
+        <v>133828829</v>
       </c>
       <c r="B39" t="n">
-        <v>79091</v>
+        <v>99138</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4841,10 +4844,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518403</v>
+        <v>518329</v>
       </c>
       <c r="R39" t="n">
-        <v>6897135</v>
+        <v>6896969</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4876,7 +4879,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4886,7 +4889,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4913,53 +4921,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133828840</v>
+        <v>133828790</v>
       </c>
       <c r="B40" t="n">
-        <v>57958</v>
+        <v>99138</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518482</v>
+        <v>518391</v>
       </c>
       <c r="R40" t="n">
-        <v>6897062</v>
+        <v>6897080</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>16 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5490,7 +5490,7 @@
         <v>133828805</v>
       </c>
       <c r="B45" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133828793</v>
+        <v>133828816</v>
       </c>
       <c r="B46" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5610,21 +5610,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5634,10 +5634,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518352</v>
+        <v>518222</v>
       </c>
       <c r="R46" t="n">
-        <v>6897090</v>
+        <v>6896862</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5706,10 +5706,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133828800</v>
+        <v>133828778</v>
       </c>
       <c r="B47" t="n">
-        <v>83308</v>
+        <v>79334</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5717,21 +5717,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518301</v>
+        <v>518437</v>
       </c>
       <c r="R47" t="n">
-        <v>6896988</v>
+        <v>6897164</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5813,10 +5813,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133828816</v>
+        <v>133828793</v>
       </c>
       <c r="B48" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5824,21 +5824,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518222</v>
+        <v>518352</v>
       </c>
       <c r="R48" t="n">
-        <v>6896862</v>
+        <v>6897090</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5920,10 +5920,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133828778</v>
+        <v>133828800</v>
       </c>
       <c r="B49" t="n">
-        <v>79334</v>
+        <v>83310</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5931,21 +5931,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518437</v>
+        <v>518301</v>
       </c>
       <c r="R49" t="n">
-        <v>6897164</v>
+        <v>6896988</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6030,7 +6030,7 @@
         <v>133828783</v>
       </c>
       <c r="B50" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6139,32 +6139,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133828773</v>
+        <v>133828833</v>
       </c>
       <c r="B51" t="n">
-        <v>83316</v>
+        <v>80468</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6174,13 +6174,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518414</v>
+        <v>518405</v>
       </c>
       <c r="R51" t="n">
-        <v>6897216</v>
+        <v>6897021</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6246,48 +6246,56 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133828833</v>
+        <v>133828819</v>
       </c>
       <c r="B52" t="n">
-        <v>80468</v>
+        <v>57958</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518405</v>
+        <v>518221</v>
       </c>
       <c r="R52" t="n">
-        <v>6897021</v>
+        <v>6896825</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6316,7 +6324,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6326,7 +6334,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6353,10 +6366,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133828819</v>
+        <v>133828773</v>
       </c>
       <c r="B53" t="n">
-        <v>57958</v>
+        <v>83318</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6364,42 +6377,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518221</v>
+        <v>518414</v>
       </c>
       <c r="R53" t="n">
-        <v>6896825</v>
+        <v>6897216</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6431,7 +6436,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6441,12 +6446,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6473,32 +6473,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133828850</v>
+        <v>133828784</v>
       </c>
       <c r="B54" t="n">
-        <v>79334</v>
+        <v>99138</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518594</v>
+        <v>518400</v>
       </c>
       <c r="R54" t="n">
-        <v>6897257</v>
+        <v>6897160</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6553,7 +6553,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6580,10 +6585,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133828806</v>
+        <v>133828850</v>
       </c>
       <c r="B55" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6591,21 +6596,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6615,10 +6620,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518246</v>
+        <v>518594</v>
       </c>
       <c r="R55" t="n">
-        <v>6896911</v>
+        <v>6897257</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6650,7 +6655,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6660,7 +6665,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6794,32 +6799,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133828784</v>
+        <v>133828806</v>
       </c>
       <c r="B57" t="n">
-        <v>99132</v>
+        <v>80439</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6829,10 +6834,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518400</v>
+        <v>518246</v>
       </c>
       <c r="R57" t="n">
-        <v>6897160</v>
+        <v>6896911</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6864,7 +6869,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6874,12 +6879,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>5 ex</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6906,10 +6906,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133828776</v>
+        <v>133828812</v>
       </c>
       <c r="B58" t="n">
-        <v>83308</v>
+        <v>80440</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6917,21 +6917,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6941,10 +6941,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518435</v>
+        <v>518235</v>
       </c>
       <c r="R58" t="n">
-        <v>6897176</v>
+        <v>6896851</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7013,10 +7013,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133828812</v>
+        <v>133828776</v>
       </c>
       <c r="B59" t="n">
-        <v>80440</v>
+        <v>83310</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7024,21 +7024,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518235</v>
+        <v>518435</v>
       </c>
       <c r="R59" t="n">
-        <v>6896851</v>
+        <v>6897176</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7227,53 +7227,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133828797</v>
+        <v>133828822</v>
       </c>
       <c r="B61" t="n">
-        <v>57958</v>
+        <v>99138</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518329</v>
+        <v>518264</v>
       </c>
       <c r="R61" t="n">
-        <v>6897013</v>
+        <v>6896807</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7305,7 +7297,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7315,12 +7307,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7347,32 +7339,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133828822</v>
+        <v>133828847</v>
       </c>
       <c r="B62" t="n">
-        <v>99132</v>
+        <v>83318</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7382,10 +7374,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518264</v>
+        <v>518474</v>
       </c>
       <c r="R62" t="n">
-        <v>6896807</v>
+        <v>6897109</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7417,7 +7409,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7427,12 +7419,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>1 ex</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7459,10 +7446,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133828847</v>
+        <v>133828797</v>
       </c>
       <c r="B63" t="n">
-        <v>83316</v>
+        <v>57958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7470,34 +7457,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518474</v>
+        <v>518329</v>
       </c>
       <c r="R63" t="n">
-        <v>6897109</v>
+        <v>6897013</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7529,7 +7524,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7539,7 +7534,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7566,32 +7566,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133828779</v>
+        <v>133828851</v>
       </c>
       <c r="B64" t="n">
-        <v>91883</v>
+        <v>99138</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518437</v>
+        <v>518585</v>
       </c>
       <c r="R64" t="n">
-        <v>6897164</v>
+        <v>6897256</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7646,7 +7646,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7673,53 +7678,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133828839</v>
+        <v>133828779</v>
       </c>
       <c r="B65" t="n">
-        <v>57958</v>
+        <v>91889</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518455</v>
+        <v>518437</v>
       </c>
       <c r="R65" t="n">
-        <v>6897046</v>
+        <v>6897164</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7751,7 +7748,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7761,12 +7758,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7793,45 +7785,53 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133828851</v>
+        <v>133828839</v>
       </c>
       <c r="B66" t="n">
-        <v>99132</v>
+        <v>57958</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518585</v>
+        <v>518455</v>
       </c>
       <c r="R66" t="n">
-        <v>6897256</v>
+        <v>6897046</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7905,10 +7905,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133828808</v>
+        <v>133828827</v>
       </c>
       <c r="B67" t="n">
-        <v>80439</v>
+        <v>57958</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7916,34 +7916,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518250</v>
+        <v>518303</v>
       </c>
       <c r="R67" t="n">
-        <v>6896903</v>
+        <v>6896962</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7975,7 +7983,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7985,7 +7993,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8012,32 +8025,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133828798</v>
+        <v>133828808</v>
       </c>
       <c r="B68" t="n">
-        <v>83299</v>
+        <v>80439</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8047,10 +8060,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518339</v>
+        <v>518250</v>
       </c>
       <c r="R68" t="n">
-        <v>6897004</v>
+        <v>6896903</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8082,7 +8095,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8092,7 +8105,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8119,10 +8132,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133828777</v>
+        <v>133828798</v>
       </c>
       <c r="B69" t="n">
-        <v>83299</v>
+        <v>83301</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8154,10 +8167,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>518435</v>
+        <v>518339</v>
       </c>
       <c r="R69" t="n">
-        <v>6897176</v>
+        <v>6897004</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8189,7 +8202,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8199,7 +8212,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8226,53 +8239,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133828827</v>
+        <v>133828777</v>
       </c>
       <c r="B70" t="n">
-        <v>57958</v>
+        <v>83301</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>518303</v>
+        <v>518435</v>
       </c>
       <c r="R70" t="n">
-        <v>6896962</v>
+        <v>6897176</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8304,7 +8309,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8314,12 +8319,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8667,32 +8667,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133828787</v>
+        <v>133828803</v>
       </c>
       <c r="B74" t="n">
-        <v>83308</v>
+        <v>99138</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8702,13 +8702,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518402</v>
+        <v>518221</v>
       </c>
       <c r="R74" t="n">
-        <v>6897136</v>
+        <v>6896911</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8747,7 +8747,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8774,32 +8779,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133828803</v>
+        <v>133828787</v>
       </c>
       <c r="B75" t="n">
-        <v>99132</v>
+        <v>83310</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8809,13 +8814,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>518221</v>
+        <v>518402</v>
       </c>
       <c r="R75" t="n">
-        <v>6896911</v>
+        <v>6897136</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8844,7 +8849,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8854,12 +8859,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8886,32 +8886,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133828815</v>
+        <v>133828772</v>
       </c>
       <c r="B76" t="n">
-        <v>80439</v>
+        <v>99138</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>518230</v>
+        <v>518419</v>
       </c>
       <c r="R76" t="n">
-        <v>6896858</v>
+        <v>6897228</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8966,7 +8966,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8993,32 +8998,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133828772</v>
+        <v>133828826</v>
       </c>
       <c r="B77" t="n">
-        <v>99132</v>
+        <v>83310</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9028,10 +9033,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>518419</v>
+        <v>518269</v>
       </c>
       <c r="R77" t="n">
-        <v>6897228</v>
+        <v>6896902</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9063,7 +9068,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9073,12 +9078,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>7 ex</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9105,10 +9105,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133828826</v>
+        <v>133828815</v>
       </c>
       <c r="B78" t="n">
-        <v>83308</v>
+        <v>80439</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9116,21 +9116,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9140,10 +9140,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>518269</v>
+        <v>518230</v>
       </c>
       <c r="R78" t="n">
-        <v>6896902</v>
+        <v>6896858</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9215,7 +9215,7 @@
         <v>133828780</v>
       </c>
       <c r="B79" t="n">
-        <v>97245</v>
+        <v>97251</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>133828836</v>
       </c>
       <c r="B80" t="n">
-        <v>83316</v>
+        <v>83318</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>133828786</v>
       </c>
       <c r="B83" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9765,32 +9765,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133828814</v>
+        <v>133828791</v>
       </c>
       <c r="B84" t="n">
-        <v>99132</v>
+        <v>83310</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518236</v>
+        <v>518371</v>
       </c>
       <c r="R84" t="n">
-        <v>6896855</v>
+        <v>6897086</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9845,12 +9845,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>45 ex</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9877,10 +9872,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133828791</v>
+        <v>133828781</v>
       </c>
       <c r="B85" t="n">
-        <v>83308</v>
+        <v>83310</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9912,10 +9907,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518371</v>
+        <v>518427</v>
       </c>
       <c r="R85" t="n">
-        <v>6897086</v>
+        <v>6897159</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9947,7 +9942,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9957,7 +9952,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9984,32 +9979,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133828781</v>
+        <v>133828830</v>
       </c>
       <c r="B86" t="n">
-        <v>83308</v>
+        <v>99138</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10019,10 +10014,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518427</v>
+        <v>518373</v>
       </c>
       <c r="R86" t="n">
-        <v>6897159</v>
+        <v>6897009</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10054,7 +10049,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10064,7 +10059,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10091,32 +10091,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133828835</v>
+        <v>133828814</v>
       </c>
       <c r="B87" t="n">
-        <v>80439</v>
+        <v>99138</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518407</v>
+        <v>518236</v>
       </c>
       <c r="R87" t="n">
-        <v>6897030</v>
+        <v>6896855</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10171,7 +10171,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10198,32 +10203,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133828830</v>
+        <v>133828835</v>
       </c>
       <c r="B88" t="n">
-        <v>99132</v>
+        <v>80439</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10233,10 +10238,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>518373</v>
+        <v>518407</v>
       </c>
       <c r="R88" t="n">
-        <v>6897009</v>
+        <v>6897030</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10268,7 +10273,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10278,12 +10283,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>9 ex</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10310,10 +10310,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133828838</v>
+        <v>133828834</v>
       </c>
       <c r="B89" t="n">
-        <v>79091</v>
+        <v>80439</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10321,21 +10321,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10345,13 +10345,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>518440</v>
+        <v>518405</v>
       </c>
       <c r="R89" t="n">
-        <v>6897045</v>
+        <v>6897020</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10417,32 +10417,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133828844</v>
+        <v>133828810</v>
       </c>
       <c r="B90" t="n">
-        <v>80439</v>
+        <v>80468</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10452,10 +10452,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>518502</v>
+        <v>518240</v>
       </c>
       <c r="R90" t="n">
-        <v>6897113</v>
+        <v>6896871</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10524,7 +10524,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133828834</v>
+        <v>133828844</v>
       </c>
       <c r="B91" t="n">
         <v>80439</v>
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>518405</v>
+        <v>518502</v>
       </c>
       <c r="R91" t="n">
-        <v>6897020</v>
+        <v>6897113</v>
       </c>
       <c r="S91" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10631,32 +10631,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133828810</v>
+        <v>133828804</v>
       </c>
       <c r="B92" t="n">
-        <v>80468</v>
+        <v>80439</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10666,10 +10666,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>518240</v>
+        <v>518231</v>
       </c>
       <c r="R92" t="n">
-        <v>6896871</v>
+        <v>6896913</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10738,10 +10738,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133828804</v>
+        <v>133828838</v>
       </c>
       <c r="B93" t="n">
-        <v>80439</v>
+        <v>79091</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10749,21 +10749,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10773,10 +10773,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>518231</v>
+        <v>518440</v>
       </c>
       <c r="R93" t="n">
-        <v>6896913</v>
+        <v>6897045</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10845,32 +10845,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133828794</v>
+        <v>133828785</v>
       </c>
       <c r="B94" t="n">
-        <v>79334</v>
+        <v>80343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10880,13 +10880,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>518380</v>
+        <v>518394</v>
       </c>
       <c r="R94" t="n">
-        <v>6897032</v>
+        <v>6897139</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10952,32 +10952,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133828785</v>
+        <v>133828852</v>
       </c>
       <c r="B95" t="n">
-        <v>80343</v>
+        <v>80439</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>518394</v>
+        <v>518557</v>
       </c>
       <c r="R95" t="n">
-        <v>6897139</v>
+        <v>6897217</v>
       </c>
       <c r="S95" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11059,10 +11059,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133828842</v>
+        <v>133828794</v>
       </c>
       <c r="B96" t="n">
-        <v>79091</v>
+        <v>79334</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11070,21 +11070,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>518539</v>
+        <v>518380</v>
       </c>
       <c r="R96" t="n">
-        <v>6897099</v>
+        <v>6897032</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11166,10 +11166,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133828852</v>
+        <v>133828842</v>
       </c>
       <c r="B97" t="n">
-        <v>80439</v>
+        <v>79091</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11177,21 +11177,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11201,10 +11201,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>518557</v>
+        <v>518539</v>
       </c>
       <c r="R97" t="n">
-        <v>6897217</v>
+        <v>6897099</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -3054,7 +3054,7 @@
         <v>133828824</v>
       </c>
       <c r="B23" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>133828845</v>
       </c>
       <c r="B24" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>133828823</v>
       </c>
       <c r="B25" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,32 +3382,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133828841</v>
+        <v>133828789</v>
       </c>
       <c r="B26" t="n">
-        <v>83310</v>
+        <v>99140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3417,13 +3417,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518489</v>
+        <v>518446</v>
       </c>
       <c r="R26" t="n">
-        <v>6897064</v>
+        <v>6897134</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,7 +3462,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3489,10 +3494,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133828837</v>
+        <v>133828841</v>
       </c>
       <c r="B27" t="n">
-        <v>83310</v>
+        <v>83311</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3524,10 +3529,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518437</v>
+        <v>518489</v>
       </c>
       <c r="R27" t="n">
-        <v>6897050</v>
+        <v>6897064</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3559,7 +3564,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3569,7 +3574,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3596,10 +3601,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133828848</v>
+        <v>133828837</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>83311</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,42 +3612,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518510</v>
+        <v>518437</v>
       </c>
       <c r="R28" t="n">
-        <v>6897194</v>
+        <v>6897050</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3674,7 +3671,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3684,12 +3681,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3716,48 +3708,56 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133828789</v>
+        <v>133828848</v>
       </c>
       <c r="B29" t="n">
-        <v>99138</v>
+        <v>57958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518446</v>
+        <v>518510</v>
       </c>
       <c r="R29" t="n">
-        <v>6897134</v>
+        <v>6897194</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,7 +3831,7 @@
         <v>133828775</v>
       </c>
       <c r="B30" t="n">
-        <v>83310</v>
+        <v>83311</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133828820</v>
+        <v>133828807</v>
       </c>
       <c r="B33" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518236</v>
+        <v>518247</v>
       </c>
       <c r="R33" t="n">
-        <v>6896830</v>
+        <v>6896909</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,7 +4256,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133828821</v>
+        <v>133828820</v>
       </c>
       <c r="B34" t="n">
         <v>80439</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518263</v>
+        <v>518236</v>
       </c>
       <c r="R34" t="n">
-        <v>6896809</v>
+        <v>6896830</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4363,10 +4363,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133828807</v>
+        <v>133828821</v>
       </c>
       <c r="B35" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518247</v>
+        <v>518263</v>
       </c>
       <c r="R35" t="n">
-        <v>6896909</v>
+        <v>6896809</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4473,7 +4473,7 @@
         <v>133828825</v>
       </c>
       <c r="B36" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>133828829</v>
       </c>
       <c r="B39" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>133828790</v>
       </c>
       <c r="B40" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5033,10 +5033,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133828796</v>
+        <v>133828818</v>
       </c>
       <c r="B41" t="n">
-        <v>79091</v>
+        <v>57958</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5044,37 +5044,45 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518327</v>
+        <v>518222</v>
       </c>
       <c r="R41" t="n">
-        <v>6897018</v>
+        <v>6896820</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5103,7 +5111,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5113,7 +5121,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5140,7 +5153,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133828818</v>
+        <v>133828792</v>
       </c>
       <c r="B42" t="n">
         <v>57958</v>
@@ -5183,10 +5196,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518222</v>
+        <v>518356</v>
       </c>
       <c r="R42" t="n">
-        <v>6896820</v>
+        <v>6897080</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5218,7 +5231,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5228,7 +5241,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5260,10 +5273,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133828792</v>
+        <v>133828796</v>
       </c>
       <c r="B43" t="n">
-        <v>57958</v>
+        <v>79091</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5271,45 +5284,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518356</v>
+        <v>518327</v>
       </c>
       <c r="R43" t="n">
-        <v>6897080</v>
+        <v>6897018</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5338,7 +5343,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5348,12 +5353,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5490,7 +5490,7 @@
         <v>133828805</v>
       </c>
       <c r="B45" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133828816</v>
+        <v>133828793</v>
       </c>
       <c r="B46" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5610,21 +5610,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5634,10 +5634,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518222</v>
+        <v>518352</v>
       </c>
       <c r="R46" t="n">
-        <v>6896862</v>
+        <v>6897090</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5706,10 +5706,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133828778</v>
+        <v>133828800</v>
       </c>
       <c r="B47" t="n">
-        <v>79334</v>
+        <v>83311</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5717,21 +5717,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518437</v>
+        <v>518301</v>
       </c>
       <c r="R47" t="n">
-        <v>6897164</v>
+        <v>6896988</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5813,10 +5813,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133828793</v>
+        <v>133828816</v>
       </c>
       <c r="B48" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5824,21 +5824,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518352</v>
+        <v>518222</v>
       </c>
       <c r="R48" t="n">
-        <v>6897090</v>
+        <v>6896862</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5920,10 +5920,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133828800</v>
+        <v>133828778</v>
       </c>
       <c r="B49" t="n">
-        <v>83310</v>
+        <v>79334</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5931,21 +5931,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518301</v>
+        <v>518437</v>
       </c>
       <c r="R49" t="n">
-        <v>6896988</v>
+        <v>6897164</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6030,7 +6030,7 @@
         <v>133828783</v>
       </c>
       <c r="B50" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6139,32 +6139,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133828833</v>
+        <v>133828773</v>
       </c>
       <c r="B51" t="n">
-        <v>80468</v>
+        <v>83319</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6174,13 +6174,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518405</v>
+        <v>518414</v>
       </c>
       <c r="R51" t="n">
-        <v>6897021</v>
+        <v>6897216</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6246,56 +6246,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133828819</v>
+        <v>133828833</v>
       </c>
       <c r="B52" t="n">
-        <v>57958</v>
+        <v>80468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518221</v>
+        <v>518405</v>
       </c>
       <c r="R52" t="n">
-        <v>6896825</v>
+        <v>6897021</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6324,7 +6316,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6334,12 +6326,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6366,10 +6353,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133828773</v>
+        <v>133828819</v>
       </c>
       <c r="B53" t="n">
-        <v>83318</v>
+        <v>57958</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6377,34 +6364,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518414</v>
+        <v>518221</v>
       </c>
       <c r="R53" t="n">
-        <v>6897216</v>
+        <v>6896825</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6436,7 +6431,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6446,7 +6441,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6473,32 +6473,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133828784</v>
+        <v>133828806</v>
       </c>
       <c r="B54" t="n">
-        <v>99138</v>
+        <v>80439</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518400</v>
+        <v>518246</v>
       </c>
       <c r="R54" t="n">
-        <v>6897160</v>
+        <v>6896911</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6553,12 +6553,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>5 ex</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6585,10 +6580,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133828850</v>
+        <v>133828809</v>
       </c>
       <c r="B55" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6596,21 +6591,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6620,10 +6615,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518594</v>
+        <v>518251</v>
       </c>
       <c r="R55" t="n">
-        <v>6897257</v>
+        <v>6896886</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6655,7 +6650,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6665,7 +6660,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6692,10 +6687,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133828809</v>
+        <v>133828850</v>
       </c>
       <c r="B56" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6703,21 +6698,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6727,10 +6722,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518251</v>
+        <v>518594</v>
       </c>
       <c r="R56" t="n">
-        <v>6896886</v>
+        <v>6897257</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6762,7 +6757,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6772,7 +6767,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6799,32 +6794,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133828806</v>
+        <v>133828784</v>
       </c>
       <c r="B57" t="n">
-        <v>80439</v>
+        <v>99140</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6834,10 +6829,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518246</v>
+        <v>518400</v>
       </c>
       <c r="R57" t="n">
-        <v>6896911</v>
+        <v>6897160</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6869,7 +6864,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6879,7 +6874,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7016,7 +7016,7 @@
         <v>133828776</v>
       </c>
       <c r="B59" t="n">
-        <v>83310</v>
+        <v>83311</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>133828822</v>
       </c>
       <c r="B61" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>133828847</v>
       </c>
       <c r="B62" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7566,32 +7566,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133828851</v>
+        <v>133828779</v>
       </c>
       <c r="B64" t="n">
-        <v>99138</v>
+        <v>91891</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518585</v>
+        <v>518437</v>
       </c>
       <c r="R64" t="n">
-        <v>6897256</v>
+        <v>6897164</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7646,12 +7646,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7678,45 +7673,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133828779</v>
+        <v>133828839</v>
       </c>
       <c r="B65" t="n">
-        <v>91889</v>
+        <v>57958</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518437</v>
+        <v>518455</v>
       </c>
       <c r="R65" t="n">
-        <v>6897164</v>
+        <v>6897046</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7748,7 +7751,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7758,7 +7761,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7785,53 +7793,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133828839</v>
+        <v>133828851</v>
       </c>
       <c r="B66" t="n">
-        <v>57958</v>
+        <v>99140</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518455</v>
+        <v>518585</v>
       </c>
       <c r="R66" t="n">
-        <v>6897046</v>
+        <v>6897256</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8135,7 +8135,7 @@
         <v>133828798</v>
       </c>
       <c r="B69" t="n">
-        <v>83301</v>
+        <v>83302</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>133828777</v>
       </c>
       <c r="B70" t="n">
-        <v>83301</v>
+        <v>83302</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8346,10 +8346,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133828849</v>
+        <v>133828787</v>
       </c>
       <c r="B71" t="n">
-        <v>80439</v>
+        <v>83311</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8357,21 +8357,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518564</v>
+        <v>518402</v>
       </c>
       <c r="R71" t="n">
-        <v>6897207</v>
+        <v>6897136</v>
       </c>
       <c r="S71" t="n">
         <v>6</v>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8453,32 +8453,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133828843</v>
+        <v>133828849</v>
       </c>
       <c r="B72" t="n">
-        <v>80468</v>
+        <v>80439</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8488,13 +8488,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>518502</v>
+        <v>518564</v>
       </c>
       <c r="R72" t="n">
-        <v>6897111</v>
+        <v>6897207</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8560,7 +8560,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133828771</v>
+        <v>133828843</v>
       </c>
       <c r="B73" t="n">
         <v>80468</v>
@@ -8595,10 +8595,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>518411</v>
+        <v>518502</v>
       </c>
       <c r="R73" t="n">
-        <v>6897234</v>
+        <v>6897111</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8667,32 +8667,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133828803</v>
+        <v>133828771</v>
       </c>
       <c r="B74" t="n">
-        <v>99138</v>
+        <v>80468</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8702,10 +8702,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518221</v>
+        <v>518411</v>
       </c>
       <c r="R74" t="n">
-        <v>6896911</v>
+        <v>6897234</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8747,12 +8747,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8779,32 +8774,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133828787</v>
+        <v>133828803</v>
       </c>
       <c r="B75" t="n">
-        <v>83310</v>
+        <v>99140</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8814,13 +8809,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>518402</v>
+        <v>518221</v>
       </c>
       <c r="R75" t="n">
-        <v>6897136</v>
+        <v>6896911</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8849,7 +8844,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8859,7 +8854,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8886,32 +8886,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133828772</v>
+        <v>133828826</v>
       </c>
       <c r="B76" t="n">
-        <v>99138</v>
+        <v>83311</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>518419</v>
+        <v>518269</v>
       </c>
       <c r="R76" t="n">
-        <v>6897228</v>
+        <v>6896902</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8966,12 +8966,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>7 ex</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8998,10 +8993,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133828826</v>
+        <v>133828815</v>
       </c>
       <c r="B77" t="n">
-        <v>83310</v>
+        <v>80439</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9009,21 +9004,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9033,10 +9028,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>518269</v>
+        <v>518230</v>
       </c>
       <c r="R77" t="n">
-        <v>6896902</v>
+        <v>6896858</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9068,7 +9063,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9078,7 +9073,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9105,32 +9100,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133828815</v>
+        <v>133828772</v>
       </c>
       <c r="B78" t="n">
-        <v>80439</v>
+        <v>99140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9140,10 +9135,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>518230</v>
+        <v>518419</v>
       </c>
       <c r="R78" t="n">
-        <v>6896858</v>
+        <v>6897228</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9175,7 +9170,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9185,7 +9180,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9212,32 +9212,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133828780</v>
+        <v>133828836</v>
       </c>
       <c r="B79" t="n">
-        <v>97251</v>
+        <v>83319</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2869</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9247,13 +9247,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>518441</v>
+        <v>518403</v>
       </c>
       <c r="R79" t="n">
-        <v>6897163</v>
+        <v>6897037</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9319,32 +9319,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133828836</v>
+        <v>133828780</v>
       </c>
       <c r="B80" t="n">
-        <v>83318</v>
+        <v>97253</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>2869</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9354,13 +9354,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>518403</v>
+        <v>518441</v>
       </c>
       <c r="R80" t="n">
-        <v>6897037</v>
+        <v>6897163</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9533,53 +9533,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133828799</v>
+        <v>133828786</v>
       </c>
       <c r="B82" t="n">
-        <v>57958</v>
+        <v>99140</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>518312</v>
+        <v>518399</v>
       </c>
       <c r="R82" t="n">
-        <v>6896987</v>
+        <v>6897137</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9611,7 +9603,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9621,12 +9613,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9653,45 +9645,53 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133828786</v>
+        <v>133828799</v>
       </c>
       <c r="B83" t="n">
-        <v>99138</v>
+        <v>57958</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>518399</v>
+        <v>518312</v>
       </c>
       <c r="R83" t="n">
-        <v>6897137</v>
+        <v>6896987</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9733,12 +9733,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>85 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9765,32 +9765,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133828791</v>
+        <v>133828814</v>
       </c>
       <c r="B84" t="n">
-        <v>83310</v>
+        <v>99140</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518371</v>
+        <v>518236</v>
       </c>
       <c r="R84" t="n">
-        <v>6897086</v>
+        <v>6896855</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9845,7 +9845,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9872,32 +9877,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133828781</v>
+        <v>133828830</v>
       </c>
       <c r="B85" t="n">
-        <v>83310</v>
+        <v>99140</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9907,10 +9912,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518427</v>
+        <v>518373</v>
       </c>
       <c r="R85" t="n">
-        <v>6897159</v>
+        <v>6897009</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9942,7 +9947,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9952,7 +9957,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9979,32 +9989,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133828830</v>
+        <v>133828791</v>
       </c>
       <c r="B86" t="n">
-        <v>99138</v>
+        <v>83311</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10014,10 +10024,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518373</v>
+        <v>518371</v>
       </c>
       <c r="R86" t="n">
-        <v>6897009</v>
+        <v>6897086</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10049,7 +10059,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10059,12 +10069,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>9 ex</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10091,32 +10096,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133828814</v>
+        <v>133828781</v>
       </c>
       <c r="B87" t="n">
-        <v>99138</v>
+        <v>83311</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10126,10 +10131,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518236</v>
+        <v>518427</v>
       </c>
       <c r="R87" t="n">
-        <v>6896855</v>
+        <v>6897159</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10161,7 +10166,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10171,12 +10176,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>45 ex</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10310,10 +10310,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133828834</v>
+        <v>133828838</v>
       </c>
       <c r="B89" t="n">
-        <v>80439</v>
+        <v>79091</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10321,21 +10321,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10345,13 +10345,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>518405</v>
+        <v>518440</v>
       </c>
       <c r="R89" t="n">
-        <v>6897020</v>
+        <v>6897045</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10417,32 +10417,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133828810</v>
+        <v>133828844</v>
       </c>
       <c r="B90" t="n">
-        <v>80468</v>
+        <v>80439</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10452,10 +10452,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>518240</v>
+        <v>518502</v>
       </c>
       <c r="R90" t="n">
-        <v>6896871</v>
+        <v>6897113</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10524,7 +10524,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133828844</v>
+        <v>133828834</v>
       </c>
       <c r="B91" t="n">
         <v>80439</v>
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>518502</v>
+        <v>518405</v>
       </c>
       <c r="R91" t="n">
-        <v>6897113</v>
+        <v>6897020</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10631,32 +10631,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133828804</v>
+        <v>133828810</v>
       </c>
       <c r="B92" t="n">
-        <v>80439</v>
+        <v>80468</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10666,10 +10666,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>518231</v>
+        <v>518240</v>
       </c>
       <c r="R92" t="n">
-        <v>6896913</v>
+        <v>6896871</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10738,10 +10738,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133828838</v>
+        <v>133828804</v>
       </c>
       <c r="B93" t="n">
-        <v>79091</v>
+        <v>80439</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10749,21 +10749,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10773,10 +10773,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>518440</v>
+        <v>518231</v>
       </c>
       <c r="R93" t="n">
-        <v>6897045</v>
+        <v>6896913</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10845,32 +10845,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133828785</v>
+        <v>133828794</v>
       </c>
       <c r="B94" t="n">
-        <v>80343</v>
+        <v>79334</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10880,13 +10880,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>518394</v>
+        <v>518380</v>
       </c>
       <c r="R94" t="n">
-        <v>6897139</v>
+        <v>6897032</v>
       </c>
       <c r="S94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10952,32 +10952,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133828852</v>
+        <v>133828785</v>
       </c>
       <c r="B95" t="n">
-        <v>80439</v>
+        <v>80343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>518557</v>
+        <v>518394</v>
       </c>
       <c r="R95" t="n">
-        <v>6897217</v>
+        <v>6897139</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11059,10 +11059,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133828794</v>
+        <v>133828842</v>
       </c>
       <c r="B96" t="n">
-        <v>79334</v>
+        <v>79091</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11070,21 +11070,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>518380</v>
+        <v>518539</v>
       </c>
       <c r="R96" t="n">
-        <v>6897032</v>
+        <v>6897099</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11166,10 +11166,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133828842</v>
+        <v>133828852</v>
       </c>
       <c r="B97" t="n">
-        <v>79091</v>
+        <v>80439</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11177,21 +11177,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11201,10 +11201,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>518539</v>
+        <v>518557</v>
       </c>
       <c r="R97" t="n">
-        <v>6897099</v>
+        <v>6897217</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -7227,32 +7227,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133828822</v>
+        <v>133828847</v>
       </c>
       <c r="B61" t="n">
-        <v>99140</v>
+        <v>83319</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518264</v>
+        <v>518474</v>
       </c>
       <c r="R61" t="n">
-        <v>6896807</v>
+        <v>6897109</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7307,12 +7307,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>1 ex</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7339,10 +7334,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133828847</v>
+        <v>133828797</v>
       </c>
       <c r="B62" t="n">
-        <v>83319</v>
+        <v>57958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7350,34 +7345,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518474</v>
+        <v>518329</v>
       </c>
       <c r="R62" t="n">
-        <v>6897109</v>
+        <v>6897013</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7409,7 +7412,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7419,7 +7422,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7446,53 +7454,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133828797</v>
+        <v>133828822</v>
       </c>
       <c r="B63" t="n">
-        <v>57958</v>
+        <v>99140</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518329</v>
+        <v>518264</v>
       </c>
       <c r="R63" t="n">
-        <v>6897013</v>
+        <v>6896807</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7905,10 +7905,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133828827</v>
+        <v>133828808</v>
       </c>
       <c r="B67" t="n">
-        <v>57958</v>
+        <v>80439</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7916,42 +7916,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518303</v>
+        <v>518250</v>
       </c>
       <c r="R67" t="n">
-        <v>6896962</v>
+        <v>6896903</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7983,7 +7975,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7993,12 +7985,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8025,32 +8012,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133828808</v>
+        <v>133828798</v>
       </c>
       <c r="B68" t="n">
-        <v>80439</v>
+        <v>83302</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8060,10 +8047,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518250</v>
+        <v>518339</v>
       </c>
       <c r="R68" t="n">
-        <v>6896903</v>
+        <v>6897004</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8095,7 +8082,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8105,7 +8092,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8132,7 +8119,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133828798</v>
+        <v>133828777</v>
       </c>
       <c r="B69" t="n">
         <v>83302</v>
@@ -8167,10 +8154,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>518339</v>
+        <v>518435</v>
       </c>
       <c r="R69" t="n">
-        <v>6897004</v>
+        <v>6897176</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8202,7 +8189,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8212,7 +8199,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8239,45 +8226,53 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133828777</v>
+        <v>133828827</v>
       </c>
       <c r="B70" t="n">
-        <v>83302</v>
+        <v>57958</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>518435</v>
+        <v>518303</v>
       </c>
       <c r="R70" t="n">
-        <v>6897176</v>
+        <v>6896962</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8309,7 +8304,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8319,7 +8314,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8886,32 +8886,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133828826</v>
+        <v>133828772</v>
       </c>
       <c r="B76" t="n">
-        <v>83311</v>
+        <v>99140</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>518269</v>
+        <v>518419</v>
       </c>
       <c r="R76" t="n">
-        <v>6896902</v>
+        <v>6897228</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8966,7 +8966,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8993,10 +8998,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133828815</v>
+        <v>133828826</v>
       </c>
       <c r="B77" t="n">
-        <v>80439</v>
+        <v>83311</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9004,21 +9009,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9028,10 +9033,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>518230</v>
+        <v>518269</v>
       </c>
       <c r="R77" t="n">
-        <v>6896858</v>
+        <v>6896902</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9063,7 +9068,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9073,7 +9078,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9100,32 +9105,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133828772</v>
+        <v>133828815</v>
       </c>
       <c r="B78" t="n">
-        <v>99140</v>
+        <v>80439</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9135,10 +9140,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>518419</v>
+        <v>518230</v>
       </c>
       <c r="R78" t="n">
-        <v>6897228</v>
+        <v>6896858</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9170,7 +9175,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9180,12 +9185,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>7 ex</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9212,32 +9212,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133828836</v>
+        <v>133828780</v>
       </c>
       <c r="B79" t="n">
-        <v>83319</v>
+        <v>97253</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>2869</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9247,13 +9247,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>518403</v>
+        <v>518441</v>
       </c>
       <c r="R79" t="n">
-        <v>6897037</v>
+        <v>6897163</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9319,32 +9319,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133828780</v>
+        <v>133828836</v>
       </c>
       <c r="B80" t="n">
-        <v>97253</v>
+        <v>83319</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2869</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9354,13 +9354,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>518441</v>
+        <v>518403</v>
       </c>
       <c r="R80" t="n">
-        <v>6897163</v>
+        <v>6897037</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -7227,32 +7227,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133828847</v>
+        <v>133828822</v>
       </c>
       <c r="B61" t="n">
-        <v>83319</v>
+        <v>99140</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518474</v>
+        <v>518264</v>
       </c>
       <c r="R61" t="n">
-        <v>6897109</v>
+        <v>6896807</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7307,7 +7307,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7334,10 +7339,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133828797</v>
+        <v>133828847</v>
       </c>
       <c r="B62" t="n">
-        <v>57958</v>
+        <v>83319</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7345,42 +7350,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518329</v>
+        <v>518474</v>
       </c>
       <c r="R62" t="n">
-        <v>6897013</v>
+        <v>6897109</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7412,7 +7409,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7422,12 +7419,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7454,45 +7446,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133828822</v>
+        <v>133828797</v>
       </c>
       <c r="B63" t="n">
-        <v>99140</v>
+        <v>57958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518264</v>
+        <v>518329</v>
       </c>
       <c r="R63" t="n">
-        <v>6896807</v>
+        <v>6897013</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -3051,32 +3051,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133828824</v>
+        <v>133828845</v>
       </c>
       <c r="B23" t="n">
-        <v>91928</v>
+        <v>99140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518273</v>
+        <v>518477</v>
       </c>
       <c r="R23" t="n">
-        <v>6896829</v>
+        <v>6897110</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,7 +3131,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3158,7 +3163,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133828845</v>
+        <v>133828823</v>
       </c>
       <c r="B24" t="n">
         <v>99140</v>
@@ -3193,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518477</v>
+        <v>518272</v>
       </c>
       <c r="R24" t="n">
-        <v>6897110</v>
+        <v>6896819</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3228,7 +3233,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,12 +3243,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,32 +3275,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133828823</v>
+        <v>133828824</v>
       </c>
       <c r="B25" t="n">
-        <v>99140</v>
+        <v>91928</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3305,10 +3310,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518272</v>
+        <v>518273</v>
       </c>
       <c r="R25" t="n">
-        <v>6896819</v>
+        <v>6896829</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3340,7 +3345,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,12 +3355,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -8886,32 +8886,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133828772</v>
+        <v>133828826</v>
       </c>
       <c r="B76" t="n">
-        <v>99140</v>
+        <v>83311</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>518419</v>
+        <v>518269</v>
       </c>
       <c r="R76" t="n">
-        <v>6897228</v>
+        <v>6896902</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8966,12 +8966,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>7 ex</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8998,10 +8993,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133828826</v>
+        <v>133828815</v>
       </c>
       <c r="B77" t="n">
-        <v>83311</v>
+        <v>80439</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9009,21 +9004,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9033,10 +9028,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>518269</v>
+        <v>518230</v>
       </c>
       <c r="R77" t="n">
-        <v>6896902</v>
+        <v>6896858</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9068,7 +9063,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9078,7 +9073,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9105,32 +9100,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133828815</v>
+        <v>133828772</v>
       </c>
       <c r="B78" t="n">
-        <v>80439</v>
+        <v>99140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9140,10 +9135,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>518230</v>
+        <v>518419</v>
       </c>
       <c r="R78" t="n">
-        <v>6896858</v>
+        <v>6897228</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9175,7 +9170,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9185,7 +9180,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9426,10 +9426,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133828782</v>
+        <v>133828799</v>
       </c>
       <c r="B81" t="n">
-        <v>80439</v>
+        <v>57958</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9437,34 +9437,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>518424</v>
+        <v>518312</v>
       </c>
       <c r="R81" t="n">
-        <v>6897159</v>
+        <v>6896987</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9496,7 +9504,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9506,7 +9514,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9533,32 +9546,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133828786</v>
+        <v>133828782</v>
       </c>
       <c r="B82" t="n">
-        <v>99140</v>
+        <v>80439</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9568,10 +9581,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>518399</v>
+        <v>518424</v>
       </c>
       <c r="R82" t="n">
-        <v>6897137</v>
+        <v>6897159</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9603,7 +9616,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9613,12 +9626,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:33</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>85 ex</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9645,53 +9653,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133828799</v>
+        <v>133828786</v>
       </c>
       <c r="B83" t="n">
-        <v>57958</v>
+        <v>99140</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>518312</v>
+        <v>518399</v>
       </c>
       <c r="R83" t="n">
-        <v>6896987</v>
+        <v>6897137</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9733,12 +9733,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -3051,32 +3051,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133828845</v>
+        <v>133828824</v>
       </c>
       <c r="B23" t="n">
-        <v>99140</v>
+        <v>91928</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518477</v>
+        <v>518273</v>
       </c>
       <c r="R23" t="n">
-        <v>6897110</v>
+        <v>6896829</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,12 +3131,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>50 ex</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3163,7 +3158,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133828823</v>
+        <v>133828845</v>
       </c>
       <c r="B24" t="n">
         <v>99140</v>
@@ -3198,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518272</v>
+        <v>518477</v>
       </c>
       <c r="R24" t="n">
-        <v>6896819</v>
+        <v>6897110</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3233,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3243,12 +3238,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3275,32 +3270,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133828824</v>
+        <v>133828823</v>
       </c>
       <c r="B25" t="n">
-        <v>91928</v>
+        <v>99140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3310,10 +3305,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518273</v>
+        <v>518272</v>
       </c>
       <c r="R25" t="n">
-        <v>6896829</v>
+        <v>6896819</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3345,7 +3340,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3355,7 +3350,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -5033,10 +5033,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133828818</v>
+        <v>133828796</v>
       </c>
       <c r="B41" t="n">
-        <v>57958</v>
+        <v>79091</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5044,45 +5044,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518222</v>
+        <v>518327</v>
       </c>
       <c r="R41" t="n">
-        <v>6896820</v>
+        <v>6897018</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5111,7 +5103,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5121,12 +5113,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5153,7 +5140,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133828792</v>
+        <v>133828818</v>
       </c>
       <c r="B42" t="n">
         <v>57958</v>
@@ -5196,10 +5183,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518356</v>
+        <v>518222</v>
       </c>
       <c r="R42" t="n">
-        <v>6897080</v>
+        <v>6896820</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5231,7 +5218,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5241,7 +5228,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5273,10 +5260,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133828796</v>
+        <v>133828792</v>
       </c>
       <c r="B43" t="n">
-        <v>79091</v>
+        <v>57958</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5284,37 +5271,45 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518327</v>
+        <v>518356</v>
       </c>
       <c r="R43" t="n">
-        <v>6897018</v>
+        <v>6897080</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5343,7 +5338,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5353,7 +5348,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5599,32 +5599,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133828793</v>
+        <v>133828783</v>
       </c>
       <c r="B46" t="n">
-        <v>79366</v>
+        <v>99140</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5634,13 +5634,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518352</v>
+        <v>518406</v>
       </c>
       <c r="R46" t="n">
-        <v>6897090</v>
+        <v>6897153</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5679,7 +5679,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5706,10 +5711,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133828800</v>
+        <v>133828793</v>
       </c>
       <c r="B47" t="n">
-        <v>83311</v>
+        <v>79366</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5717,21 +5722,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5741,10 +5746,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518301</v>
+        <v>518352</v>
       </c>
       <c r="R47" t="n">
-        <v>6896988</v>
+        <v>6897090</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5776,7 +5781,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5786,7 +5791,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5813,10 +5818,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133828816</v>
+        <v>133828800</v>
       </c>
       <c r="B48" t="n">
-        <v>79334</v>
+        <v>83311</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5824,21 +5829,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5848,10 +5853,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518222</v>
+        <v>518301</v>
       </c>
       <c r="R48" t="n">
-        <v>6896862</v>
+        <v>6896988</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5883,7 +5888,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5893,7 +5898,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5920,7 +5925,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133828778</v>
+        <v>133828816</v>
       </c>
       <c r="B49" t="n">
         <v>79334</v>
@@ -5955,10 +5960,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518437</v>
+        <v>518222</v>
       </c>
       <c r="R49" t="n">
-        <v>6897164</v>
+        <v>6896862</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5990,7 +5995,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6000,7 +6005,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6027,32 +6032,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133828783</v>
+        <v>133828778</v>
       </c>
       <c r="B50" t="n">
-        <v>99140</v>
+        <v>79334</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6062,13 +6067,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518406</v>
+        <v>518437</v>
       </c>
       <c r="R50" t="n">
-        <v>6897153</v>
+        <v>6897164</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6097,7 +6102,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6107,12 +6112,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>11 ex</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7227,32 +7227,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133828822</v>
+        <v>133828847</v>
       </c>
       <c r="B61" t="n">
-        <v>99140</v>
+        <v>83319</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518264</v>
+        <v>518474</v>
       </c>
       <c r="R61" t="n">
-        <v>6896807</v>
+        <v>6897109</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7307,12 +7307,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>1 ex</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7339,10 +7334,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133828847</v>
+        <v>133828797</v>
       </c>
       <c r="B62" t="n">
-        <v>83319</v>
+        <v>57958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7350,34 +7345,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518474</v>
+        <v>518329</v>
       </c>
       <c r="R62" t="n">
-        <v>6897109</v>
+        <v>6897013</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7409,7 +7412,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7419,7 +7422,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7446,53 +7454,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133828797</v>
+        <v>133828822</v>
       </c>
       <c r="B63" t="n">
-        <v>57958</v>
+        <v>99140</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518329</v>
+        <v>518264</v>
       </c>
       <c r="R63" t="n">
-        <v>6897013</v>
+        <v>6896807</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9426,10 +9426,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133828799</v>
+        <v>133828782</v>
       </c>
       <c r="B81" t="n">
-        <v>57958</v>
+        <v>80439</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9437,42 +9437,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>518312</v>
+        <v>518424</v>
       </c>
       <c r="R81" t="n">
-        <v>6896987</v>
+        <v>6897159</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9504,7 +9496,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9514,12 +9506,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9546,32 +9533,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133828782</v>
+        <v>133828786</v>
       </c>
       <c r="B82" t="n">
-        <v>80439</v>
+        <v>99140</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9581,10 +9568,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>518424</v>
+        <v>518399</v>
       </c>
       <c r="R82" t="n">
-        <v>6897159</v>
+        <v>6897137</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9616,7 +9603,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9626,7 +9613,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9653,45 +9645,53 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133828786</v>
+        <v>133828799</v>
       </c>
       <c r="B83" t="n">
-        <v>99140</v>
+        <v>57958</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>518399</v>
+        <v>518312</v>
       </c>
       <c r="R83" t="n">
-        <v>6897137</v>
+        <v>6896987</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9733,12 +9733,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>85 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -5599,32 +5599,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133828783</v>
+        <v>133828793</v>
       </c>
       <c r="B46" t="n">
-        <v>99140</v>
+        <v>79366</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5634,13 +5634,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518406</v>
+        <v>518352</v>
       </c>
       <c r="R46" t="n">
-        <v>6897153</v>
+        <v>6897090</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5679,12 +5679,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>11 ex</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5711,10 +5706,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133828793</v>
+        <v>133828800</v>
       </c>
       <c r="B47" t="n">
-        <v>79366</v>
+        <v>83311</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5722,21 +5717,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5746,10 +5741,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518352</v>
+        <v>518301</v>
       </c>
       <c r="R47" t="n">
-        <v>6897090</v>
+        <v>6896988</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5781,7 +5776,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5791,7 +5786,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5818,10 +5813,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133828800</v>
+        <v>133828816</v>
       </c>
       <c r="B48" t="n">
-        <v>83311</v>
+        <v>79334</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5829,21 +5824,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5853,10 +5848,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518301</v>
+        <v>518222</v>
       </c>
       <c r="R48" t="n">
-        <v>6896988</v>
+        <v>6896862</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5888,7 +5883,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5898,7 +5893,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5925,7 +5920,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133828816</v>
+        <v>133828778</v>
       </c>
       <c r="B49" t="n">
         <v>79334</v>
@@ -5960,10 +5955,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518222</v>
+        <v>518437</v>
       </c>
       <c r="R49" t="n">
-        <v>6896862</v>
+        <v>6897164</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5995,7 +5990,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6005,7 +6000,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6032,32 +6027,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133828778</v>
+        <v>133828783</v>
       </c>
       <c r="B50" t="n">
-        <v>79334</v>
+        <v>99140</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6067,13 +6062,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518437</v>
+        <v>518406</v>
       </c>
       <c r="R50" t="n">
-        <v>6897164</v>
+        <v>6897153</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6102,7 +6097,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6112,7 +6107,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7227,32 +7227,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133828847</v>
+        <v>133828822</v>
       </c>
       <c r="B61" t="n">
-        <v>83319</v>
+        <v>99140</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518474</v>
+        <v>518264</v>
       </c>
       <c r="R61" t="n">
-        <v>6897109</v>
+        <v>6896807</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7307,7 +7307,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7334,10 +7339,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133828797</v>
+        <v>133828847</v>
       </c>
       <c r="B62" t="n">
-        <v>57958</v>
+        <v>83319</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7345,42 +7350,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518329</v>
+        <v>518474</v>
       </c>
       <c r="R62" t="n">
-        <v>6897013</v>
+        <v>6897109</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7412,7 +7409,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7422,12 +7419,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7454,45 +7446,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133828822</v>
+        <v>133828797</v>
       </c>
       <c r="B63" t="n">
-        <v>99140</v>
+        <v>57958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518264</v>
+        <v>518329</v>
       </c>
       <c r="R63" t="n">
-        <v>6896807</v>
+        <v>6897013</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133828801</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>133828817</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>133828802</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3051,32 +3051,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133828824</v>
+        <v>133828823</v>
       </c>
       <c r="B23" t="n">
-        <v>91928</v>
+        <v>99168</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518273</v>
+        <v>518272</v>
       </c>
       <c r="R23" t="n">
-        <v>6896829</v>
+        <v>6896819</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,7 +3131,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,7 +3166,7 @@
         <v>133828845</v>
       </c>
       <c r="B24" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3270,32 +3275,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133828823</v>
+        <v>133828824</v>
       </c>
       <c r="B25" t="n">
-        <v>99140</v>
+        <v>91947</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3305,10 +3310,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518272</v>
+        <v>518273</v>
       </c>
       <c r="R25" t="n">
-        <v>6896819</v>
+        <v>6896829</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3340,7 +3345,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,12 +3355,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,32 +3382,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133828789</v>
+        <v>133828841</v>
       </c>
       <c r="B26" t="n">
-        <v>99140</v>
+        <v>83325</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3417,13 +3417,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518446</v>
+        <v>518489</v>
       </c>
       <c r="R26" t="n">
-        <v>6897134</v>
+        <v>6897064</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,12 +3462,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3494,10 +3489,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133828841</v>
+        <v>133828837</v>
       </c>
       <c r="B27" t="n">
-        <v>83311</v>
+        <v>83325</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,10 +3524,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518489</v>
+        <v>518437</v>
       </c>
       <c r="R27" t="n">
-        <v>6897064</v>
+        <v>6897050</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3564,7 +3559,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3574,7 +3569,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3601,32 +3596,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133828837</v>
+        <v>133828789</v>
       </c>
       <c r="B28" t="n">
-        <v>83311</v>
+        <v>99168</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3636,13 +3631,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518437</v>
+        <v>518446</v>
       </c>
       <c r="R28" t="n">
-        <v>6897050</v>
+        <v>6897134</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3671,7 +3666,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3681,7 +3676,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3711,7 +3711,7 @@
         <v>133828848</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3828,10 +3828,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828775</v>
+        <v>133828831</v>
       </c>
       <c r="B30" t="n">
-        <v>83311</v>
+        <v>80453</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3839,21 +3839,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518420</v>
+        <v>518389</v>
       </c>
       <c r="R30" t="n">
-        <v>6897194</v>
+        <v>6897022</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3935,10 +3935,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133828831</v>
+        <v>133828813</v>
       </c>
       <c r="B31" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518389</v>
+        <v>518235</v>
       </c>
       <c r="R31" t="n">
-        <v>6897022</v>
+        <v>6896853</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4042,10 +4042,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828813</v>
+        <v>133828807</v>
       </c>
       <c r="B32" t="n">
-        <v>80439</v>
+        <v>79348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4053,21 +4053,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518235</v>
+        <v>518247</v>
       </c>
       <c r="R32" t="n">
-        <v>6896853</v>
+        <v>6896909</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4149,10 +4149,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133828807</v>
+        <v>133828775</v>
       </c>
       <c r="B33" t="n">
-        <v>79334</v>
+        <v>83325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518247</v>
+        <v>518420</v>
       </c>
       <c r="R33" t="n">
-        <v>6896909</v>
+        <v>6897194</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4259,7 +4259,7 @@
         <v>133828820</v>
       </c>
       <c r="B34" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4363,32 +4363,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133828821</v>
+        <v>133828825</v>
       </c>
       <c r="B35" t="n">
-        <v>80439</v>
+        <v>99168</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518263</v>
+        <v>518279</v>
       </c>
       <c r="R35" t="n">
-        <v>6896809</v>
+        <v>6896843</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4443,7 +4443,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4470,32 +4475,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133828825</v>
+        <v>133828821</v>
       </c>
       <c r="B36" t="n">
-        <v>99140</v>
+        <v>80453</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4505,10 +4510,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518279</v>
+        <v>518263</v>
       </c>
       <c r="R36" t="n">
-        <v>6896843</v>
+        <v>6896809</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4540,7 +4545,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4550,12 +4555,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>1 ex</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4585,7 +4585,7 @@
         <v>133828788</v>
       </c>
       <c r="B37" t="n">
-        <v>79091</v>
+        <v>79105</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4689,53 +4689,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133828840</v>
+        <v>133828829</v>
       </c>
       <c r="B38" t="n">
-        <v>57958</v>
+        <v>99168</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518482</v>
+        <v>518329</v>
       </c>
       <c r="R38" t="n">
-        <v>6897062</v>
+        <v>6896969</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4767,7 +4759,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4777,12 +4769,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4809,10 +4801,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133828829</v>
+        <v>133828790</v>
       </c>
       <c r="B39" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4844,10 +4836,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518329</v>
+        <v>518391</v>
       </c>
       <c r="R39" t="n">
-        <v>6896969</v>
+        <v>6897080</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4879,7 +4871,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4889,12 +4881,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>16 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4921,45 +4913,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133828790</v>
+        <v>133828840</v>
       </c>
       <c r="B40" t="n">
-        <v>99140</v>
+        <v>57965</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518391</v>
+        <v>518482</v>
       </c>
       <c r="R40" t="n">
-        <v>6897080</v>
+        <v>6897062</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>16 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5036,7 +5036,7 @@
         <v>133828796</v>
       </c>
       <c r="B41" t="n">
-        <v>79091</v>
+        <v>79105</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>133828818</v>
       </c>
       <c r="B42" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>133828792</v>
       </c>
       <c r="B43" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5380,32 +5380,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133828811</v>
+        <v>133828805</v>
       </c>
       <c r="B44" t="n">
-        <v>80439</v>
+        <v>99168</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518240</v>
+        <v>518243</v>
       </c>
       <c r="R44" t="n">
-        <v>6896871</v>
+        <v>6896917</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5460,7 +5460,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5487,32 +5492,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133828805</v>
+        <v>133828811</v>
       </c>
       <c r="B45" t="n">
-        <v>99140</v>
+        <v>80453</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5522,10 +5527,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518243</v>
+        <v>518240</v>
       </c>
       <c r="R45" t="n">
-        <v>6896917</v>
+        <v>6896871</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5557,7 +5562,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5567,12 +5572,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5599,32 +5599,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133828793</v>
+        <v>133828783</v>
       </c>
       <c r="B46" t="n">
-        <v>79366</v>
+        <v>99168</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5634,13 +5634,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518352</v>
+        <v>518406</v>
       </c>
       <c r="R46" t="n">
-        <v>6897090</v>
+        <v>6897153</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5679,7 +5679,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5706,10 +5711,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133828800</v>
+        <v>133828778</v>
       </c>
       <c r="B47" t="n">
-        <v>83311</v>
+        <v>79348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5717,21 +5722,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5741,10 +5746,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518301</v>
+        <v>518437</v>
       </c>
       <c r="R47" t="n">
-        <v>6896988</v>
+        <v>6897164</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5776,7 +5781,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5786,7 +5791,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5813,10 +5818,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133828816</v>
+        <v>133828800</v>
       </c>
       <c r="B48" t="n">
-        <v>79334</v>
+        <v>83325</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5824,21 +5829,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5848,10 +5853,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518222</v>
+        <v>518301</v>
       </c>
       <c r="R48" t="n">
-        <v>6896862</v>
+        <v>6896988</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5883,7 +5888,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5893,7 +5898,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5920,10 +5925,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133828778</v>
+        <v>133828816</v>
       </c>
       <c r="B49" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5955,10 +5960,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518437</v>
+        <v>518222</v>
       </c>
       <c r="R49" t="n">
-        <v>6897164</v>
+        <v>6896862</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5990,7 +5995,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6000,7 +6005,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6027,32 +6032,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133828783</v>
+        <v>133828793</v>
       </c>
       <c r="B50" t="n">
-        <v>99140</v>
+        <v>79380</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6062,13 +6067,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518406</v>
+        <v>518352</v>
       </c>
       <c r="R50" t="n">
-        <v>6897153</v>
+        <v>6897090</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6097,7 +6102,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6107,12 +6112,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>11 ex</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6139,32 +6139,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133828773</v>
+        <v>133828833</v>
       </c>
       <c r="B51" t="n">
-        <v>83319</v>
+        <v>80482</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6174,13 +6174,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518414</v>
+        <v>518405</v>
       </c>
       <c r="R51" t="n">
-        <v>6897216</v>
+        <v>6897021</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6246,48 +6246,56 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133828833</v>
+        <v>133828819</v>
       </c>
       <c r="B52" t="n">
-        <v>80468</v>
+        <v>57965</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518405</v>
+        <v>518221</v>
       </c>
       <c r="R52" t="n">
-        <v>6897021</v>
+        <v>6896825</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6316,7 +6324,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6326,7 +6334,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6353,10 +6366,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133828819</v>
+        <v>133828773</v>
       </c>
       <c r="B53" t="n">
-        <v>57958</v>
+        <v>83333</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6364,42 +6377,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518221</v>
+        <v>518414</v>
       </c>
       <c r="R53" t="n">
-        <v>6896825</v>
+        <v>6897216</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6431,7 +6436,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6441,12 +6446,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6476,7 +6476,7 @@
         <v>133828806</v>
       </c>
       <c r="B54" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6580,32 +6580,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133828809</v>
+        <v>133828784</v>
       </c>
       <c r="B55" t="n">
-        <v>80439</v>
+        <v>99168</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518251</v>
+        <v>518400</v>
       </c>
       <c r="R55" t="n">
-        <v>6896886</v>
+        <v>6897160</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6660,7 +6660,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6687,10 +6692,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133828850</v>
+        <v>133828809</v>
       </c>
       <c r="B56" t="n">
-        <v>79334</v>
+        <v>80453</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6698,21 +6703,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6722,10 +6727,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518594</v>
+        <v>518251</v>
       </c>
       <c r="R56" t="n">
-        <v>6897257</v>
+        <v>6896886</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6757,7 +6762,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6767,7 +6772,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6794,32 +6799,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133828784</v>
+        <v>133828850</v>
       </c>
       <c r="B57" t="n">
-        <v>99140</v>
+        <v>79348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6829,10 +6834,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518400</v>
+        <v>518594</v>
       </c>
       <c r="R57" t="n">
-        <v>6897160</v>
+        <v>6897257</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6864,7 +6869,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6874,12 +6879,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>5 ex</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6906,10 +6906,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133828812</v>
+        <v>133828795</v>
       </c>
       <c r="B58" t="n">
-        <v>80440</v>
+        <v>79105</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6917,21 +6917,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6941,10 +6941,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518235</v>
+        <v>518327</v>
       </c>
       <c r="R58" t="n">
-        <v>6896851</v>
+        <v>6897030</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7013,10 +7013,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133828776</v>
+        <v>133828812</v>
       </c>
       <c r="B59" t="n">
-        <v>83311</v>
+        <v>80454</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7024,21 +7024,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518435</v>
+        <v>518235</v>
       </c>
       <c r="R59" t="n">
-        <v>6897176</v>
+        <v>6896851</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7120,10 +7120,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133828795</v>
+        <v>133828776</v>
       </c>
       <c r="B60" t="n">
-        <v>79091</v>
+        <v>83325</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7131,21 +7131,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518327</v>
+        <v>518435</v>
       </c>
       <c r="R60" t="n">
-        <v>6897030</v>
+        <v>6897176</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7230,7 +7230,7 @@
         <v>133828822</v>
       </c>
       <c r="B61" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7339,10 +7339,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133828847</v>
+        <v>133828797</v>
       </c>
       <c r="B62" t="n">
-        <v>83319</v>
+        <v>57965</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7350,34 +7350,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518474</v>
+        <v>518329</v>
       </c>
       <c r="R62" t="n">
-        <v>6897109</v>
+        <v>6897013</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7409,7 +7417,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7419,7 +7427,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7446,10 +7459,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133828797</v>
+        <v>133828847</v>
       </c>
       <c r="B63" t="n">
-        <v>57958</v>
+        <v>83333</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7457,42 +7470,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518329</v>
+        <v>518474</v>
       </c>
       <c r="R63" t="n">
-        <v>6897013</v>
+        <v>6897109</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7524,7 +7529,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7534,12 +7539,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7566,45 +7566,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133828779</v>
+        <v>133828839</v>
       </c>
       <c r="B64" t="n">
-        <v>91891</v>
+        <v>57965</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518437</v>
+        <v>518455</v>
       </c>
       <c r="R64" t="n">
-        <v>6897164</v>
+        <v>6897046</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7636,7 +7644,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7646,7 +7654,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7673,53 +7686,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133828839</v>
+        <v>133828779</v>
       </c>
       <c r="B65" t="n">
-        <v>57958</v>
+        <v>91910</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518455</v>
+        <v>518437</v>
       </c>
       <c r="R65" t="n">
-        <v>6897046</v>
+        <v>6897164</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7751,7 +7756,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7761,12 +7766,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7796,7 +7796,7 @@
         <v>133828851</v>
       </c>
       <c r="B66" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>133828808</v>
       </c>
       <c r="B67" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>133828798</v>
       </c>
       <c r="B68" t="n">
-        <v>83302</v>
+        <v>83316</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>133828777</v>
       </c>
       <c r="B69" t="n">
-        <v>83302</v>
+        <v>83316</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>133828827</v>
       </c>
       <c r="B70" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8346,10 +8346,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133828787</v>
+        <v>133828849</v>
       </c>
       <c r="B71" t="n">
-        <v>83311</v>
+        <v>80453</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8357,21 +8357,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518402</v>
+        <v>518564</v>
       </c>
       <c r="R71" t="n">
-        <v>6897136</v>
+        <v>6897207</v>
       </c>
       <c r="S71" t="n">
         <v>6</v>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8453,32 +8453,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133828849</v>
+        <v>133828803</v>
       </c>
       <c r="B72" t="n">
-        <v>80439</v>
+        <v>99168</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8488,13 +8488,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>518564</v>
+        <v>518221</v>
       </c>
       <c r="R72" t="n">
-        <v>6897207</v>
+        <v>6896911</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8533,7 +8533,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8563,7 +8568,7 @@
         <v>133828843</v>
       </c>
       <c r="B73" t="n">
-        <v>80468</v>
+        <v>80482</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8667,32 +8672,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133828771</v>
+        <v>133828787</v>
       </c>
       <c r="B74" t="n">
-        <v>80468</v>
+        <v>83325</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8702,13 +8707,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518411</v>
+        <v>518402</v>
       </c>
       <c r="R74" t="n">
-        <v>6897234</v>
+        <v>6897136</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8737,7 +8742,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8747,7 +8752,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8774,32 +8779,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133828803</v>
+        <v>133828771</v>
       </c>
       <c r="B75" t="n">
-        <v>99140</v>
+        <v>80482</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8809,10 +8814,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>518221</v>
+        <v>518411</v>
       </c>
       <c r="R75" t="n">
-        <v>6896911</v>
+        <v>6897234</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8844,7 +8849,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8854,12 +8859,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8889,7 +8889,7 @@
         <v>133828826</v>
       </c>
       <c r="B76" t="n">
-        <v>83311</v>
+        <v>83325</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8993,32 +8993,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133828815</v>
+        <v>133828772</v>
       </c>
       <c r="B77" t="n">
-        <v>80439</v>
+        <v>99168</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>518230</v>
+        <v>518419</v>
       </c>
       <c r="R77" t="n">
-        <v>6896858</v>
+        <v>6897228</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9073,7 +9073,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9100,32 +9105,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133828772</v>
+        <v>133828815</v>
       </c>
       <c r="B78" t="n">
-        <v>99140</v>
+        <v>80453</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9135,10 +9140,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>518419</v>
+        <v>518230</v>
       </c>
       <c r="R78" t="n">
-        <v>6897228</v>
+        <v>6896858</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9170,7 +9175,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9180,12 +9185,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>7 ex</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9212,32 +9212,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133828780</v>
+        <v>133828836</v>
       </c>
       <c r="B79" t="n">
-        <v>97253</v>
+        <v>83333</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2869</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9247,13 +9247,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>518441</v>
+        <v>518403</v>
       </c>
       <c r="R79" t="n">
-        <v>6897163</v>
+        <v>6897037</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9319,32 +9319,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133828836</v>
+        <v>133828780</v>
       </c>
       <c r="B80" t="n">
-        <v>83319</v>
+        <v>97281</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>2869</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9354,13 +9354,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>518403</v>
+        <v>518441</v>
       </c>
       <c r="R80" t="n">
-        <v>6897037</v>
+        <v>6897163</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9426,32 +9426,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133828782</v>
+        <v>133828786</v>
       </c>
       <c r="B81" t="n">
-        <v>80439</v>
+        <v>99168</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>518424</v>
+        <v>518399</v>
       </c>
       <c r="R81" t="n">
-        <v>6897159</v>
+        <v>6897137</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9506,7 +9506,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9533,32 +9538,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133828786</v>
+        <v>133828782</v>
       </c>
       <c r="B82" t="n">
-        <v>99140</v>
+        <v>80453</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9568,10 +9573,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>518399</v>
+        <v>518424</v>
       </c>
       <c r="R82" t="n">
-        <v>6897137</v>
+        <v>6897159</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9603,7 +9608,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9613,12 +9618,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:33</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>85 ex</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9648,7 +9648,7 @@
         <v>133828799</v>
       </c>
       <c r="B83" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9765,32 +9765,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133828814</v>
+        <v>133828791</v>
       </c>
       <c r="B84" t="n">
-        <v>99140</v>
+        <v>83325</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518236</v>
+        <v>518371</v>
       </c>
       <c r="R84" t="n">
-        <v>6896855</v>
+        <v>6897086</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9845,12 +9845,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>45 ex</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9877,32 +9872,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133828830</v>
+        <v>133828781</v>
       </c>
       <c r="B85" t="n">
-        <v>99140</v>
+        <v>83325</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9912,10 +9907,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518373</v>
+        <v>518427</v>
       </c>
       <c r="R85" t="n">
-        <v>6897009</v>
+        <v>6897159</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9947,7 +9942,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9957,12 +9952,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>9 ex</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9989,32 +9979,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133828791</v>
+        <v>133828830</v>
       </c>
       <c r="B86" t="n">
-        <v>83311</v>
+        <v>99168</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10024,10 +10014,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518371</v>
+        <v>518373</v>
       </c>
       <c r="R86" t="n">
-        <v>6897086</v>
+        <v>6897009</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10059,7 +10049,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10069,7 +10059,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10096,32 +10091,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133828781</v>
+        <v>133828814</v>
       </c>
       <c r="B87" t="n">
-        <v>83311</v>
+        <v>99168</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10131,10 +10126,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518427</v>
+        <v>518236</v>
       </c>
       <c r="R87" t="n">
-        <v>6897159</v>
+        <v>6896855</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10166,7 +10161,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10176,7 +10171,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10206,7 +10206,7 @@
         <v>133828835</v>
       </c>
       <c r="B88" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>133828838</v>
       </c>
       <c r="B89" t="n">
-        <v>79091</v>
+        <v>79105</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10417,32 +10417,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133828844</v>
+        <v>133828810</v>
       </c>
       <c r="B90" t="n">
-        <v>80439</v>
+        <v>80482</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10452,10 +10452,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>518502</v>
+        <v>518240</v>
       </c>
       <c r="R90" t="n">
-        <v>6897113</v>
+        <v>6896871</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10524,10 +10524,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133828834</v>
+        <v>133828844</v>
       </c>
       <c r="B91" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>518405</v>
+        <v>518502</v>
       </c>
       <c r="R91" t="n">
-        <v>6897020</v>
+        <v>6897113</v>
       </c>
       <c r="S91" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10631,32 +10631,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133828810</v>
+        <v>133828834</v>
       </c>
       <c r="B92" t="n">
-        <v>80468</v>
+        <v>80453</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10666,13 +10666,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>518240</v>
+        <v>518405</v>
       </c>
       <c r="R92" t="n">
-        <v>6896871</v>
+        <v>6897020</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10741,7 +10741,7 @@
         <v>133828804</v>
       </c>
       <c r="B93" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>133828794</v>
       </c>
       <c r="B94" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10952,32 +10952,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133828785</v>
+        <v>133828842</v>
       </c>
       <c r="B95" t="n">
-        <v>80343</v>
+        <v>79105</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>518394</v>
+        <v>518539</v>
       </c>
       <c r="R95" t="n">
-        <v>6897139</v>
+        <v>6897099</v>
       </c>
       <c r="S95" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11059,32 +11059,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133828842</v>
+        <v>133828785</v>
       </c>
       <c r="B96" t="n">
-        <v>79091</v>
+        <v>80357</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11094,13 +11094,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>518539</v>
+        <v>518394</v>
       </c>
       <c r="R96" t="n">
-        <v>6897099</v>
+        <v>6897139</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11169,7 +11169,7 @@
         <v>133828852</v>
       </c>
       <c r="B97" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -3051,7 +3051,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133828823</v>
+        <v>133828845</v>
       </c>
       <c r="B23" t="n">
         <v>99168</v>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518272</v>
+        <v>518477</v>
       </c>
       <c r="R23" t="n">
-        <v>6896819</v>
+        <v>6897110</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3163,32 +3163,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133828845</v>
+        <v>133828824</v>
       </c>
       <c r="B24" t="n">
-        <v>99168</v>
+        <v>91947</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518477</v>
+        <v>518273</v>
       </c>
       <c r="R24" t="n">
-        <v>6897110</v>
+        <v>6896829</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3243,12 +3243,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>50 ex</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3275,32 +3270,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133828824</v>
+        <v>133828823</v>
       </c>
       <c r="B25" t="n">
-        <v>91947</v>
+        <v>99168</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3310,10 +3305,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518273</v>
+        <v>518272</v>
       </c>
       <c r="R25" t="n">
-        <v>6896829</v>
+        <v>6896819</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3345,7 +3340,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3355,7 +3350,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,10 +3382,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133828841</v>
+        <v>133828848</v>
       </c>
       <c r="B26" t="n">
-        <v>83325</v>
+        <v>57965</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3393,34 +3393,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518489</v>
+        <v>518510</v>
       </c>
       <c r="R26" t="n">
-        <v>6897064</v>
+        <v>6897194</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3452,7 +3460,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,7 +3470,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3489,7 +3502,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133828837</v>
+        <v>133828841</v>
       </c>
       <c r="B27" t="n">
         <v>83325</v>
@@ -3524,10 +3537,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518437</v>
+        <v>518489</v>
       </c>
       <c r="R27" t="n">
-        <v>6897050</v>
+        <v>6897064</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3559,7 +3572,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3569,7 +3582,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3596,32 +3609,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133828789</v>
+        <v>133828837</v>
       </c>
       <c r="B28" t="n">
-        <v>99168</v>
+        <v>83325</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3631,13 +3644,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518446</v>
+        <v>518437</v>
       </c>
       <c r="R28" t="n">
-        <v>6897134</v>
+        <v>6897050</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3666,7 +3679,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3676,12 +3689,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3708,56 +3716,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133828848</v>
+        <v>133828789</v>
       </c>
       <c r="B29" t="n">
-        <v>57965</v>
+        <v>99168</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518510</v>
+        <v>518446</v>
       </c>
       <c r="R29" t="n">
-        <v>6897194</v>
+        <v>6897134</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3828,7 +3828,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828831</v>
+        <v>133828820</v>
       </c>
       <c r="B30" t="n">
         <v>80453</v>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518389</v>
+        <v>518236</v>
       </c>
       <c r="R30" t="n">
-        <v>6897022</v>
+        <v>6896830</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3935,7 +3935,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133828813</v>
+        <v>133828831</v>
       </c>
       <c r="B31" t="n">
         <v>80453</v>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518235</v>
+        <v>518389</v>
       </c>
       <c r="R31" t="n">
-        <v>6896853</v>
+        <v>6897022</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4042,10 +4042,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828807</v>
+        <v>133828813</v>
       </c>
       <c r="B32" t="n">
-        <v>79348</v>
+        <v>80453</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4053,21 +4053,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518247</v>
+        <v>518235</v>
       </c>
       <c r="R32" t="n">
-        <v>6896909</v>
+        <v>6896853</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4149,10 +4149,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133828775</v>
+        <v>133828807</v>
       </c>
       <c r="B33" t="n">
-        <v>83325</v>
+        <v>79348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518420</v>
+        <v>518247</v>
       </c>
       <c r="R33" t="n">
-        <v>6897194</v>
+        <v>6896909</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,10 +4256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133828820</v>
+        <v>133828775</v>
       </c>
       <c r="B34" t="n">
-        <v>80453</v>
+        <v>83325</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518236</v>
+        <v>518420</v>
       </c>
       <c r="R34" t="n">
-        <v>6896830</v>
+        <v>6897194</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5380,32 +5380,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133828805</v>
+        <v>133828811</v>
       </c>
       <c r="B44" t="n">
-        <v>99168</v>
+        <v>80453</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518243</v>
+        <v>518240</v>
       </c>
       <c r="R44" t="n">
-        <v>6896917</v>
+        <v>6896871</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5460,12 +5460,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5492,32 +5487,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133828811</v>
+        <v>133828805</v>
       </c>
       <c r="B45" t="n">
-        <v>80453</v>
+        <v>99168</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5527,10 +5522,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518240</v>
+        <v>518243</v>
       </c>
       <c r="R45" t="n">
-        <v>6896871</v>
+        <v>6896917</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5562,7 +5557,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5572,7 +5567,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5599,32 +5599,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133828783</v>
+        <v>133828816</v>
       </c>
       <c r="B46" t="n">
-        <v>99168</v>
+        <v>79348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5634,13 +5634,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518406</v>
+        <v>518222</v>
       </c>
       <c r="R46" t="n">
-        <v>6897153</v>
+        <v>6896862</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5679,12 +5679,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>11 ex</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5711,10 +5706,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133828778</v>
+        <v>133828793</v>
       </c>
       <c r="B47" t="n">
-        <v>79348</v>
+        <v>79380</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5722,21 +5717,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5746,10 +5741,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518437</v>
+        <v>518352</v>
       </c>
       <c r="R47" t="n">
-        <v>6897164</v>
+        <v>6897090</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5781,7 +5776,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5791,7 +5786,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5818,32 +5813,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133828800</v>
+        <v>133828783</v>
       </c>
       <c r="B48" t="n">
-        <v>83325</v>
+        <v>99168</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5853,13 +5848,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518301</v>
+        <v>518406</v>
       </c>
       <c r="R48" t="n">
-        <v>6896988</v>
+        <v>6897153</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5888,7 +5883,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5898,7 +5893,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5925,7 +5925,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133828816</v>
+        <v>133828778</v>
       </c>
       <c r="B49" t="n">
         <v>79348</v>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518222</v>
+        <v>518437</v>
       </c>
       <c r="R49" t="n">
-        <v>6896862</v>
+        <v>6897164</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6032,10 +6032,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133828793</v>
+        <v>133828800</v>
       </c>
       <c r="B50" t="n">
-        <v>79380</v>
+        <v>83325</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6043,21 +6043,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518352</v>
+        <v>518301</v>
       </c>
       <c r="R50" t="n">
-        <v>6897090</v>
+        <v>6896988</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6139,32 +6139,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133828833</v>
+        <v>133828773</v>
       </c>
       <c r="B51" t="n">
-        <v>80482</v>
+        <v>83333</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6174,13 +6174,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518405</v>
+        <v>518414</v>
       </c>
       <c r="R51" t="n">
-        <v>6897021</v>
+        <v>6897216</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6366,32 +6366,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133828773</v>
+        <v>133828833</v>
       </c>
       <c r="B53" t="n">
-        <v>83333</v>
+        <v>80482</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6401,13 +6401,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518414</v>
+        <v>518405</v>
       </c>
       <c r="R53" t="n">
-        <v>6897216</v>
+        <v>6897021</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7566,53 +7566,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133828839</v>
+        <v>133828851</v>
       </c>
       <c r="B64" t="n">
-        <v>57965</v>
+        <v>99168</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518455</v>
+        <v>518585</v>
       </c>
       <c r="R64" t="n">
-        <v>6897046</v>
+        <v>6897256</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7644,7 +7636,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7654,12 +7646,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7686,45 +7678,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133828779</v>
+        <v>133828839</v>
       </c>
       <c r="B65" t="n">
-        <v>91910</v>
+        <v>57965</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518437</v>
+        <v>518455</v>
       </c>
       <c r="R65" t="n">
-        <v>6897164</v>
+        <v>6897046</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7756,7 +7756,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7766,7 +7766,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7793,32 +7798,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133828851</v>
+        <v>133828779</v>
       </c>
       <c r="B66" t="n">
-        <v>99168</v>
+        <v>91910</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7828,10 +7833,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518585</v>
+        <v>518437</v>
       </c>
       <c r="R66" t="n">
-        <v>6897256</v>
+        <v>6897164</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7863,7 +7868,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7873,12 +7878,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8453,32 +8453,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133828803</v>
+        <v>133828787</v>
       </c>
       <c r="B72" t="n">
-        <v>99168</v>
+        <v>83325</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8488,13 +8488,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>518221</v>
+        <v>518402</v>
       </c>
       <c r="R72" t="n">
-        <v>6896911</v>
+        <v>6897136</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8533,12 +8533,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8565,32 +8560,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133828843</v>
+        <v>133828803</v>
       </c>
       <c r="B73" t="n">
-        <v>80482</v>
+        <v>99168</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8600,10 +8595,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>518502</v>
+        <v>518221</v>
       </c>
       <c r="R73" t="n">
-        <v>6897111</v>
+        <v>6896911</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8635,7 +8630,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8645,7 +8640,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8672,32 +8672,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133828787</v>
+        <v>133828843</v>
       </c>
       <c r="B74" t="n">
-        <v>83325</v>
+        <v>80482</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518402</v>
+        <v>518502</v>
       </c>
       <c r="R74" t="n">
-        <v>6897136</v>
+        <v>6897111</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9765,10 +9765,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133828791</v>
+        <v>133828835</v>
       </c>
       <c r="B84" t="n">
-        <v>83325</v>
+        <v>80453</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9776,21 +9776,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518371</v>
+        <v>518407</v>
       </c>
       <c r="R84" t="n">
-        <v>6897086</v>
+        <v>6897030</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9979,32 +9979,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133828830</v>
+        <v>133828791</v>
       </c>
       <c r="B86" t="n">
-        <v>99168</v>
+        <v>83325</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10014,10 +10014,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518373</v>
+        <v>518371</v>
       </c>
       <c r="R86" t="n">
-        <v>6897009</v>
+        <v>6897086</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10059,12 +10059,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>9 ex</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10091,7 +10086,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133828814</v>
+        <v>133828830</v>
       </c>
       <c r="B87" t="n">
         <v>99168</v>
@@ -10126,10 +10121,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518236</v>
+        <v>518373</v>
       </c>
       <c r="R87" t="n">
-        <v>6896855</v>
+        <v>6897009</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10161,7 +10156,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10171,12 +10166,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10203,32 +10198,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133828835</v>
+        <v>133828814</v>
       </c>
       <c r="B88" t="n">
-        <v>80453</v>
+        <v>99168</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10238,10 +10233,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>518407</v>
+        <v>518236</v>
       </c>
       <c r="R88" t="n">
-        <v>6897030</v>
+        <v>6896855</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10273,7 +10268,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10283,7 +10278,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10310,10 +10310,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133828838</v>
+        <v>133828844</v>
       </c>
       <c r="B89" t="n">
-        <v>79105</v>
+        <v>80453</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10321,21 +10321,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10345,10 +10345,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>518440</v>
+        <v>518502</v>
       </c>
       <c r="R89" t="n">
-        <v>6897045</v>
+        <v>6897113</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10417,32 +10417,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133828810</v>
+        <v>133828834</v>
       </c>
       <c r="B90" t="n">
-        <v>80482</v>
+        <v>80453</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10452,13 +10452,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>518240</v>
+        <v>518405</v>
       </c>
       <c r="R90" t="n">
-        <v>6896871</v>
+        <v>6897020</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10524,32 +10524,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133828844</v>
+        <v>133828810</v>
       </c>
       <c r="B91" t="n">
-        <v>80453</v>
+        <v>80482</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10559,10 +10559,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>518502</v>
+        <v>518240</v>
       </c>
       <c r="R91" t="n">
-        <v>6897113</v>
+        <v>6896871</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10631,10 +10631,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133828834</v>
+        <v>133828838</v>
       </c>
       <c r="B92" t="n">
-        <v>80453</v>
+        <v>79105</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10642,21 +10642,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10666,13 +10666,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>518405</v>
+        <v>518440</v>
       </c>
       <c r="R92" t="n">
-        <v>6897020</v>
+        <v>6897045</v>
       </c>
       <c r="S92" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10952,32 +10952,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133828842</v>
+        <v>133828785</v>
       </c>
       <c r="B95" t="n">
-        <v>79105</v>
+        <v>80357</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>518539</v>
+        <v>518394</v>
       </c>
       <c r="R95" t="n">
-        <v>6897099</v>
+        <v>6897139</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11059,32 +11059,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133828785</v>
+        <v>133828842</v>
       </c>
       <c r="B96" t="n">
-        <v>80357</v>
+        <v>79105</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11094,13 +11094,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>518394</v>
+        <v>518539</v>
       </c>
       <c r="R96" t="n">
-        <v>6897139</v>
+        <v>6897099</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD96" t="b">

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133828801</v>
       </c>
       <c r="B2" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>133828817</v>
       </c>
       <c r="B3" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>133828802</v>
       </c>
       <c r="B4" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>133828845</v>
       </c>
       <c r="B23" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,32 +3163,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133828824</v>
+        <v>133828823</v>
       </c>
       <c r="B24" t="n">
-        <v>91947</v>
+        <v>99178</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518273</v>
+        <v>518272</v>
       </c>
       <c r="R24" t="n">
-        <v>6896829</v>
+        <v>6896819</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3243,7 +3243,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,32 +3275,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133828823</v>
+        <v>133828824</v>
       </c>
       <c r="B25" t="n">
-        <v>99168</v>
+        <v>91957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3305,10 +3310,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518272</v>
+        <v>518273</v>
       </c>
       <c r="R25" t="n">
-        <v>6896819</v>
+        <v>6896829</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3340,7 +3345,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,12 +3355,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,10 +3382,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133828848</v>
+        <v>133828841</v>
       </c>
       <c r="B26" t="n">
-        <v>57965</v>
+        <v>83335</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3393,42 +3393,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518510</v>
+        <v>518489</v>
       </c>
       <c r="R26" t="n">
-        <v>6897194</v>
+        <v>6897064</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3460,7 +3452,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3470,12 +3462,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3502,10 +3489,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133828841</v>
+        <v>133828848</v>
       </c>
       <c r="B27" t="n">
-        <v>83325</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3513,34 +3500,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518489</v>
+        <v>518510</v>
       </c>
       <c r="R27" t="n">
-        <v>6897064</v>
+        <v>6897194</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3572,7 +3567,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3582,7 +3577,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3612,7 +3612,7 @@
         <v>133828837</v>
       </c>
       <c r="B28" t="n">
-        <v>83325</v>
+        <v>83335</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>133828789</v>
       </c>
       <c r="B29" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3828,10 +3828,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828820</v>
+        <v>133828831</v>
       </c>
       <c r="B30" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518236</v>
+        <v>518389</v>
       </c>
       <c r="R30" t="n">
-        <v>6896830</v>
+        <v>6897022</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3935,10 +3935,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133828831</v>
+        <v>133828813</v>
       </c>
       <c r="B31" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518389</v>
+        <v>518235</v>
       </c>
       <c r="R31" t="n">
-        <v>6897022</v>
+        <v>6896853</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4042,10 +4042,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828813</v>
+        <v>133828807</v>
       </c>
       <c r="B32" t="n">
-        <v>80453</v>
+        <v>79358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4053,21 +4053,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518235</v>
+        <v>518247</v>
       </c>
       <c r="R32" t="n">
-        <v>6896853</v>
+        <v>6896909</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4149,10 +4149,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133828807</v>
+        <v>133828775</v>
       </c>
       <c r="B33" t="n">
-        <v>79348</v>
+        <v>83335</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518247</v>
+        <v>518420</v>
       </c>
       <c r="R33" t="n">
-        <v>6896909</v>
+        <v>6897194</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,10 +4256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133828775</v>
+        <v>133828820</v>
       </c>
       <c r="B34" t="n">
-        <v>83325</v>
+        <v>80473</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518420</v>
+        <v>518236</v>
       </c>
       <c r="R34" t="n">
-        <v>6897194</v>
+        <v>6896830</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4366,7 +4366,7 @@
         <v>133828825</v>
       </c>
       <c r="B35" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>133828821</v>
       </c>
       <c r="B36" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>133828788</v>
       </c>
       <c r="B37" t="n">
-        <v>79105</v>
+        <v>79115</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>133828829</v>
       </c>
       <c r="B38" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>133828790</v>
       </c>
       <c r="B39" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>133828840</v>
       </c>
       <c r="B40" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>133828796</v>
       </c>
       <c r="B41" t="n">
-        <v>79105</v>
+        <v>79115</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>133828818</v>
       </c>
       <c r="B42" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>133828792</v>
       </c>
       <c r="B43" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5380,32 +5380,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133828811</v>
+        <v>133828805</v>
       </c>
       <c r="B44" t="n">
-        <v>80453</v>
+        <v>99178</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518240</v>
+        <v>518243</v>
       </c>
       <c r="R44" t="n">
-        <v>6896871</v>
+        <v>6896917</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5460,7 +5460,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5487,32 +5492,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133828805</v>
+        <v>133828811</v>
       </c>
       <c r="B45" t="n">
-        <v>99168</v>
+        <v>80473</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5522,10 +5527,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518243</v>
+        <v>518240</v>
       </c>
       <c r="R45" t="n">
-        <v>6896917</v>
+        <v>6896871</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5557,7 +5562,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5567,12 +5572,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5602,7 +5602,7 @@
         <v>133828816</v>
       </c>
       <c r="B46" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>133828793</v>
       </c>
       <c r="B47" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>133828783</v>
       </c>
       <c r="B48" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>133828778</v>
       </c>
       <c r="B49" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>133828800</v>
       </c>
       <c r="B50" t="n">
-        <v>83325</v>
+        <v>83335</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6139,10 +6139,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133828773</v>
+        <v>133828819</v>
       </c>
       <c r="B51" t="n">
-        <v>83333</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6150,34 +6150,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518414</v>
+        <v>518221</v>
       </c>
       <c r="R51" t="n">
-        <v>6897216</v>
+        <v>6896825</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6209,7 +6217,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6219,7 +6227,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6246,10 +6259,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133828819</v>
+        <v>133828773</v>
       </c>
       <c r="B52" t="n">
-        <v>57965</v>
+        <v>83343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6257,42 +6270,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518221</v>
+        <v>518414</v>
       </c>
       <c r="R52" t="n">
-        <v>6896825</v>
+        <v>6897216</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6324,7 +6329,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6334,12 +6339,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6369,7 +6369,7 @@
         <v>133828833</v>
       </c>
       <c r="B53" t="n">
-        <v>80482</v>
+        <v>80478</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>133828806</v>
       </c>
       <c r="B54" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>133828784</v>
       </c>
       <c r="B55" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>133828809</v>
       </c>
       <c r="B56" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>133828850</v>
       </c>
       <c r="B57" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>133828795</v>
       </c>
       <c r="B58" t="n">
-        <v>79105</v>
+        <v>79115</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>133828812</v>
       </c>
       <c r="B59" t="n">
-        <v>80454</v>
+        <v>80474</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>133828776</v>
       </c>
       <c r="B60" t="n">
-        <v>83325</v>
+        <v>83335</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7227,32 +7227,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133828822</v>
+        <v>133828847</v>
       </c>
       <c r="B61" t="n">
-        <v>99168</v>
+        <v>83343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518264</v>
+        <v>518474</v>
       </c>
       <c r="R61" t="n">
-        <v>6896807</v>
+        <v>6897109</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7307,12 +7307,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>1 ex</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7339,53 +7334,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133828797</v>
+        <v>133828822</v>
       </c>
       <c r="B62" t="n">
-        <v>57965</v>
+        <v>99178</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518329</v>
+        <v>518264</v>
       </c>
       <c r="R62" t="n">
-        <v>6897013</v>
+        <v>6896807</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7417,7 +7404,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7427,12 +7414,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7459,10 +7446,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133828847</v>
+        <v>133828797</v>
       </c>
       <c r="B63" t="n">
-        <v>83333</v>
+        <v>57975</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7470,34 +7457,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518474</v>
+        <v>518329</v>
       </c>
       <c r="R63" t="n">
-        <v>6897109</v>
+        <v>6897013</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7529,7 +7524,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7539,7 +7534,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7569,7 +7569,7 @@
         <v>133828851</v>
       </c>
       <c r="B64" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>133828839</v>
       </c>
       <c r="B65" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>133828779</v>
       </c>
       <c r="B66" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>133828808</v>
       </c>
       <c r="B67" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>133828798</v>
       </c>
       <c r="B68" t="n">
-        <v>83316</v>
+        <v>83326</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>133828777</v>
       </c>
       <c r="B69" t="n">
-        <v>83316</v>
+        <v>83326</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>133828827</v>
       </c>
       <c r="B70" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>133828849</v>
       </c>
       <c r="B71" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8453,32 +8453,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133828787</v>
+        <v>133828803</v>
       </c>
       <c r="B72" t="n">
-        <v>83325</v>
+        <v>99178</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8488,13 +8488,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>518402</v>
+        <v>518221</v>
       </c>
       <c r="R72" t="n">
-        <v>6897136</v>
+        <v>6896911</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8533,7 +8533,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8560,32 +8565,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133828803</v>
+        <v>133828843</v>
       </c>
       <c r="B73" t="n">
-        <v>99168</v>
+        <v>80478</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8595,10 +8600,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>518221</v>
+        <v>518502</v>
       </c>
       <c r="R73" t="n">
-        <v>6896911</v>
+        <v>6897111</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8630,7 +8635,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8640,12 +8645,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8672,32 +8672,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133828843</v>
+        <v>133828787</v>
       </c>
       <c r="B74" t="n">
-        <v>80482</v>
+        <v>83335</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518502</v>
+        <v>518402</v>
       </c>
       <c r="R74" t="n">
-        <v>6897111</v>
+        <v>6897136</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8782,7 +8782,7 @@
         <v>133828771</v>
       </c>
       <c r="B75" t="n">
-        <v>80482</v>
+        <v>80478</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>133828826</v>
       </c>
       <c r="B76" t="n">
-        <v>83325</v>
+        <v>83335</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>133828772</v>
       </c>
       <c r="B77" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>133828815</v>
       </c>
       <c r="B78" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>133828836</v>
       </c>
       <c r="B79" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>133828780</v>
       </c>
       <c r="B80" t="n">
-        <v>97281</v>
+        <v>97291</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>133828786</v>
       </c>
       <c r="B81" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>133828782</v>
       </c>
       <c r="B82" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>133828799</v>
       </c>
       <c r="B83" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9765,10 +9765,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133828835</v>
+        <v>133828791</v>
       </c>
       <c r="B84" t="n">
-        <v>80453</v>
+        <v>83335</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9776,21 +9776,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518407</v>
+        <v>518371</v>
       </c>
       <c r="R84" t="n">
-        <v>6897030</v>
+        <v>6897086</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9872,10 +9872,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133828781</v>
+        <v>133828835</v>
       </c>
       <c r="B85" t="n">
-        <v>83325</v>
+        <v>80473</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9883,21 +9883,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9907,10 +9907,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518427</v>
+        <v>518407</v>
       </c>
       <c r="R85" t="n">
-        <v>6897159</v>
+        <v>6897030</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9979,10 +9979,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133828791</v>
+        <v>133828781</v>
       </c>
       <c r="B86" t="n">
-        <v>83325</v>
+        <v>83335</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10014,10 +10014,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518371</v>
+        <v>518427</v>
       </c>
       <c r="R86" t="n">
-        <v>6897086</v>
+        <v>6897159</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10089,7 +10089,7 @@
         <v>133828830</v>
       </c>
       <c r="B87" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>133828814</v>
       </c>
       <c r="B88" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10310,10 +10310,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133828844</v>
+        <v>133828838</v>
       </c>
       <c r="B89" t="n">
-        <v>80453</v>
+        <v>79115</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10321,21 +10321,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10345,10 +10345,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>518502</v>
+        <v>518440</v>
       </c>
       <c r="R89" t="n">
-        <v>6897113</v>
+        <v>6897045</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10417,10 +10417,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133828834</v>
+        <v>133828844</v>
       </c>
       <c r="B90" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10452,13 +10452,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>518405</v>
+        <v>518502</v>
       </c>
       <c r="R90" t="n">
-        <v>6897020</v>
+        <v>6897113</v>
       </c>
       <c r="S90" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10524,32 +10524,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133828810</v>
+        <v>133828834</v>
       </c>
       <c r="B91" t="n">
-        <v>80482</v>
+        <v>80473</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>518240</v>
+        <v>518405</v>
       </c>
       <c r="R91" t="n">
-        <v>6896871</v>
+        <v>6897020</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10631,32 +10631,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133828838</v>
+        <v>133828810</v>
       </c>
       <c r="B92" t="n">
-        <v>79105</v>
+        <v>80478</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10666,10 +10666,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>518440</v>
+        <v>518240</v>
       </c>
       <c r="R92" t="n">
-        <v>6897045</v>
+        <v>6896871</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10741,7 +10741,7 @@
         <v>133828804</v>
       </c>
       <c r="B93" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>133828794</v>
       </c>
       <c r="B94" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>133828785</v>
       </c>
       <c r="B95" t="n">
-        <v>80357</v>
+        <v>80367</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>133828842</v>
       </c>
       <c r="B96" t="n">
-        <v>79105</v>
+        <v>79115</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>133828852</v>
       </c>
       <c r="B97" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -3051,7 +3051,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133828845</v>
+        <v>133828823</v>
       </c>
       <c r="B23" t="n">
         <v>99178</v>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518477</v>
+        <v>518272</v>
       </c>
       <c r="R23" t="n">
-        <v>6897110</v>
+        <v>6896819</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3163,7 +3163,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133828823</v>
+        <v>133828845</v>
       </c>
       <c r="B24" t="n">
         <v>99178</v>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518272</v>
+        <v>518477</v>
       </c>
       <c r="R24" t="n">
-        <v>6896819</v>
+        <v>6897110</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3382,10 +3382,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133828841</v>
+        <v>133828848</v>
       </c>
       <c r="B26" t="n">
-        <v>83335</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3393,34 +3393,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518489</v>
+        <v>518510</v>
       </c>
       <c r="R26" t="n">
-        <v>6897064</v>
+        <v>6897194</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3452,7 +3460,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,7 +3470,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3489,10 +3502,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133828848</v>
+        <v>133828837</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>83335</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3500,42 +3513,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518510</v>
+        <v>518437</v>
       </c>
       <c r="R27" t="n">
-        <v>6897194</v>
+        <v>6897050</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3567,7 +3572,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3577,12 +3582,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3609,7 +3609,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133828837</v>
+        <v>133828841</v>
       </c>
       <c r="B28" t="n">
         <v>83335</v>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518437</v>
+        <v>518489</v>
       </c>
       <c r="R28" t="n">
-        <v>6897050</v>
+        <v>6897064</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4149,10 +4149,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133828775</v>
+        <v>133828820</v>
       </c>
       <c r="B33" t="n">
-        <v>83335</v>
+        <v>80473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518420</v>
+        <v>518236</v>
       </c>
       <c r="R33" t="n">
-        <v>6897194</v>
+        <v>6896830</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,32 +4256,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133828820</v>
+        <v>133828825</v>
       </c>
       <c r="B34" t="n">
-        <v>80473</v>
+        <v>99178</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518236</v>
+        <v>518279</v>
       </c>
       <c r="R34" t="n">
-        <v>6896830</v>
+        <v>6896843</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,7 +4336,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4363,32 +4368,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133828825</v>
+        <v>133828775</v>
       </c>
       <c r="B35" t="n">
-        <v>99178</v>
+        <v>83335</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4398,10 +4403,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518279</v>
+        <v>518420</v>
       </c>
       <c r="R35" t="n">
-        <v>6896843</v>
+        <v>6897194</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4433,7 +4438,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4443,12 +4448,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1 ex</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5033,10 +5033,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133828796</v>
+        <v>133828818</v>
       </c>
       <c r="B41" t="n">
-        <v>79115</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5044,37 +5044,45 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518327</v>
+        <v>518222</v>
       </c>
       <c r="R41" t="n">
-        <v>6897018</v>
+        <v>6896820</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5103,7 +5111,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5113,7 +5121,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5140,7 +5153,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133828818</v>
+        <v>133828792</v>
       </c>
       <c r="B42" t="n">
         <v>57975</v>
@@ -5183,10 +5196,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518222</v>
+        <v>518356</v>
       </c>
       <c r="R42" t="n">
-        <v>6896820</v>
+        <v>6897080</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5218,7 +5231,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5228,7 +5241,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5260,10 +5273,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133828792</v>
+        <v>133828796</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>79115</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5271,45 +5284,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518356</v>
+        <v>518327</v>
       </c>
       <c r="R43" t="n">
-        <v>6897080</v>
+        <v>6897018</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5338,7 +5343,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5348,12 +5353,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5380,32 +5380,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133828805</v>
+        <v>133828811</v>
       </c>
       <c r="B44" t="n">
-        <v>99178</v>
+        <v>80473</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518243</v>
+        <v>518240</v>
       </c>
       <c r="R44" t="n">
-        <v>6896917</v>
+        <v>6896871</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5460,12 +5460,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5492,32 +5487,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133828811</v>
+        <v>133828805</v>
       </c>
       <c r="B45" t="n">
-        <v>80473</v>
+        <v>99178</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5527,10 +5522,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518240</v>
+        <v>518243</v>
       </c>
       <c r="R45" t="n">
-        <v>6896871</v>
+        <v>6896917</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5562,7 +5557,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5572,7 +5567,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6139,10 +6139,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133828819</v>
+        <v>133828773</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>83343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6150,42 +6150,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518221</v>
+        <v>518414</v>
       </c>
       <c r="R51" t="n">
-        <v>6896825</v>
+        <v>6897216</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6217,7 +6209,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6227,12 +6219,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6259,32 +6246,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133828773</v>
+        <v>133828833</v>
       </c>
       <c r="B52" t="n">
-        <v>83343</v>
+        <v>80478</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6294,13 +6281,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518414</v>
+        <v>518405</v>
       </c>
       <c r="R52" t="n">
-        <v>6897216</v>
+        <v>6897021</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6329,7 +6316,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6339,7 +6326,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6366,48 +6353,56 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133828833</v>
+        <v>133828819</v>
       </c>
       <c r="B53" t="n">
-        <v>80478</v>
+        <v>57975</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518405</v>
+        <v>518221</v>
       </c>
       <c r="R53" t="n">
-        <v>6897021</v>
+        <v>6896825</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6436,7 +6431,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6446,7 +6441,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7013,10 +7013,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133828812</v>
+        <v>133828776</v>
       </c>
       <c r="B59" t="n">
-        <v>80474</v>
+        <v>83335</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7024,21 +7024,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518235</v>
+        <v>518435</v>
       </c>
       <c r="R59" t="n">
-        <v>6896851</v>
+        <v>6897176</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7120,10 +7120,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133828776</v>
+        <v>133828812</v>
       </c>
       <c r="B60" t="n">
-        <v>83335</v>
+        <v>80474</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7131,21 +7131,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518435</v>
+        <v>518235</v>
       </c>
       <c r="R60" t="n">
-        <v>6897176</v>
+        <v>6896851</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -9765,7 +9765,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133828791</v>
+        <v>133828781</v>
       </c>
       <c r="B84" t="n">
         <v>83335</v>
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518371</v>
+        <v>518427</v>
       </c>
       <c r="R84" t="n">
-        <v>6897086</v>
+        <v>6897159</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9872,32 +9872,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133828835</v>
+        <v>133828814</v>
       </c>
       <c r="B85" t="n">
-        <v>80473</v>
+        <v>99178</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9907,10 +9907,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518407</v>
+        <v>518236</v>
       </c>
       <c r="R85" t="n">
-        <v>6897030</v>
+        <v>6896855</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9952,7 +9952,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9979,10 +9984,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133828781</v>
+        <v>133828835</v>
       </c>
       <c r="B86" t="n">
-        <v>83335</v>
+        <v>80473</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9990,21 +9995,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10014,10 +10019,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518427</v>
+        <v>518407</v>
       </c>
       <c r="R86" t="n">
-        <v>6897159</v>
+        <v>6897030</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10049,7 +10054,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10059,7 +10064,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10086,32 +10091,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133828830</v>
+        <v>133828791</v>
       </c>
       <c r="B87" t="n">
-        <v>99178</v>
+        <v>83335</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10121,10 +10126,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518373</v>
+        <v>518371</v>
       </c>
       <c r="R87" t="n">
-        <v>6897009</v>
+        <v>6897086</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10156,7 +10161,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10166,12 +10171,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>9 ex</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10198,7 +10198,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133828814</v>
+        <v>133828830</v>
       </c>
       <c r="B88" t="n">
         <v>99178</v>
@@ -10233,10 +10233,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>518236</v>
+        <v>518373</v>
       </c>
       <c r="R88" t="n">
-        <v>6896855</v>
+        <v>6897009</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10278,12 +10278,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10310,32 +10310,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133828838</v>
+        <v>133828810</v>
       </c>
       <c r="B89" t="n">
-        <v>79115</v>
+        <v>80478</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10345,10 +10345,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>518440</v>
+        <v>518240</v>
       </c>
       <c r="R89" t="n">
-        <v>6897045</v>
+        <v>6896871</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10417,7 +10417,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133828844</v>
+        <v>133828804</v>
       </c>
       <c r="B90" t="n">
         <v>80473</v>
@@ -10452,10 +10452,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>518502</v>
+        <v>518231</v>
       </c>
       <c r="R90" t="n">
-        <v>6897113</v>
+        <v>6896913</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10524,10 +10524,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133828834</v>
+        <v>133828838</v>
       </c>
       <c r="B91" t="n">
-        <v>80473</v>
+        <v>79115</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10535,21 +10535,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>518405</v>
+        <v>518440</v>
       </c>
       <c r="R91" t="n">
-        <v>6897020</v>
+        <v>6897045</v>
       </c>
       <c r="S91" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10631,32 +10631,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133828810</v>
+        <v>133828844</v>
       </c>
       <c r="B92" t="n">
-        <v>80478</v>
+        <v>80473</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10666,10 +10666,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>518240</v>
+        <v>518502</v>
       </c>
       <c r="R92" t="n">
-        <v>6896871</v>
+        <v>6897113</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10738,7 +10738,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133828804</v>
+        <v>133828834</v>
       </c>
       <c r="B93" t="n">
         <v>80473</v>
@@ -10773,13 +10773,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>518231</v>
+        <v>518405</v>
       </c>
       <c r="R93" t="n">
-        <v>6896913</v>
+        <v>6897020</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10952,32 +10952,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133828785</v>
+        <v>133828842</v>
       </c>
       <c r="B95" t="n">
-        <v>80367</v>
+        <v>79115</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>518394</v>
+        <v>518539</v>
       </c>
       <c r="R95" t="n">
-        <v>6897139</v>
+        <v>6897099</v>
       </c>
       <c r="S95" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11059,10 +11059,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133828842</v>
+        <v>133828852</v>
       </c>
       <c r="B96" t="n">
-        <v>79115</v>
+        <v>80473</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11070,21 +11070,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>518539</v>
+        <v>518557</v>
       </c>
       <c r="R96" t="n">
-        <v>6897099</v>
+        <v>6897217</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11166,32 +11166,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133828852</v>
+        <v>133828785</v>
       </c>
       <c r="B97" t="n">
-        <v>80473</v>
+        <v>80367</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11201,13 +11201,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>518557</v>
+        <v>518394</v>
       </c>
       <c r="R97" t="n">
-        <v>6897217</v>
+        <v>6897139</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -3051,7 +3051,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133828823</v>
+        <v>133828845</v>
       </c>
       <c r="B23" t="n">
         <v>99178</v>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518272</v>
+        <v>518477</v>
       </c>
       <c r="R23" t="n">
-        <v>6896819</v>
+        <v>6897110</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3163,7 +3163,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133828845</v>
+        <v>133828823</v>
       </c>
       <c r="B24" t="n">
         <v>99178</v>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518477</v>
+        <v>518272</v>
       </c>
       <c r="R24" t="n">
-        <v>6897110</v>
+        <v>6896819</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3382,10 +3382,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133828848</v>
+        <v>133828841</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>83335</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3393,42 +3393,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518510</v>
+        <v>518489</v>
       </c>
       <c r="R26" t="n">
-        <v>6897194</v>
+        <v>6897064</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3460,7 +3452,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3470,12 +3462,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3502,10 +3489,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133828837</v>
+        <v>133828848</v>
       </c>
       <c r="B27" t="n">
-        <v>83335</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3513,34 +3500,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518437</v>
+        <v>518510</v>
       </c>
       <c r="R27" t="n">
-        <v>6897050</v>
+        <v>6897194</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3572,7 +3567,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3582,7 +3577,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3609,7 +3609,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133828841</v>
+        <v>133828837</v>
       </c>
       <c r="B28" t="n">
         <v>83335</v>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518489</v>
+        <v>518437</v>
       </c>
       <c r="R28" t="n">
-        <v>6897064</v>
+        <v>6897050</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4149,10 +4149,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133828820</v>
+        <v>133828775</v>
       </c>
       <c r="B33" t="n">
-        <v>80473</v>
+        <v>83335</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518236</v>
+        <v>518420</v>
       </c>
       <c r="R33" t="n">
-        <v>6896830</v>
+        <v>6897194</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,32 +4256,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133828825</v>
+        <v>133828820</v>
       </c>
       <c r="B34" t="n">
-        <v>99178</v>
+        <v>80473</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518279</v>
+        <v>518236</v>
       </c>
       <c r="R34" t="n">
-        <v>6896843</v>
+        <v>6896830</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,12 +4336,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>1 ex</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4368,32 +4363,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133828775</v>
+        <v>133828825</v>
       </c>
       <c r="B35" t="n">
-        <v>83335</v>
+        <v>99178</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4403,10 +4398,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518420</v>
+        <v>518279</v>
       </c>
       <c r="R35" t="n">
-        <v>6897194</v>
+        <v>6896843</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4438,7 +4433,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4448,7 +4443,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5033,10 +5033,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133828818</v>
+        <v>133828796</v>
       </c>
       <c r="B41" t="n">
-        <v>57975</v>
+        <v>79115</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5044,45 +5044,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518222</v>
+        <v>518327</v>
       </c>
       <c r="R41" t="n">
-        <v>6896820</v>
+        <v>6897018</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5111,7 +5103,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5121,12 +5113,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5153,7 +5140,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133828792</v>
+        <v>133828818</v>
       </c>
       <c r="B42" t="n">
         <v>57975</v>
@@ -5196,10 +5183,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518356</v>
+        <v>518222</v>
       </c>
       <c r="R42" t="n">
-        <v>6897080</v>
+        <v>6896820</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5231,7 +5218,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5241,7 +5228,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5273,10 +5260,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133828796</v>
+        <v>133828792</v>
       </c>
       <c r="B43" t="n">
-        <v>79115</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5284,37 +5271,45 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518327</v>
+        <v>518356</v>
       </c>
       <c r="R43" t="n">
-        <v>6897018</v>
+        <v>6897080</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5343,7 +5338,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5353,7 +5348,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5380,32 +5380,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133828811</v>
+        <v>133828805</v>
       </c>
       <c r="B44" t="n">
-        <v>80473</v>
+        <v>99178</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518240</v>
+        <v>518243</v>
       </c>
       <c r="R44" t="n">
-        <v>6896871</v>
+        <v>6896917</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5460,7 +5460,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5487,32 +5492,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133828805</v>
+        <v>133828811</v>
       </c>
       <c r="B45" t="n">
-        <v>99178</v>
+        <v>80473</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5522,10 +5527,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518243</v>
+        <v>518240</v>
       </c>
       <c r="R45" t="n">
-        <v>6896917</v>
+        <v>6896871</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5557,7 +5562,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5567,12 +5572,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6139,10 +6139,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133828773</v>
+        <v>133828819</v>
       </c>
       <c r="B51" t="n">
-        <v>83343</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6150,34 +6150,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518414</v>
+        <v>518221</v>
       </c>
       <c r="R51" t="n">
-        <v>6897216</v>
+        <v>6896825</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6209,7 +6217,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6219,7 +6227,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6246,32 +6259,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133828833</v>
+        <v>133828773</v>
       </c>
       <c r="B52" t="n">
-        <v>80478</v>
+        <v>83343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6281,13 +6294,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518405</v>
+        <v>518414</v>
       </c>
       <c r="R52" t="n">
-        <v>6897021</v>
+        <v>6897216</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6316,7 +6329,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6326,7 +6339,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6353,56 +6366,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133828819</v>
+        <v>133828833</v>
       </c>
       <c r="B53" t="n">
-        <v>57975</v>
+        <v>80478</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518221</v>
+        <v>518405</v>
       </c>
       <c r="R53" t="n">
-        <v>6896825</v>
+        <v>6897021</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6431,7 +6436,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6441,12 +6446,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7013,10 +7013,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133828776</v>
+        <v>133828812</v>
       </c>
       <c r="B59" t="n">
-        <v>83335</v>
+        <v>80474</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7024,21 +7024,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518435</v>
+        <v>518235</v>
       </c>
       <c r="R59" t="n">
-        <v>6897176</v>
+        <v>6896851</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7120,10 +7120,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133828812</v>
+        <v>133828776</v>
       </c>
       <c r="B60" t="n">
-        <v>80474</v>
+        <v>83335</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7131,21 +7131,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518235</v>
+        <v>518435</v>
       </c>
       <c r="R60" t="n">
-        <v>6896851</v>
+        <v>6897176</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8346,32 +8346,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133828849</v>
+        <v>133828843</v>
       </c>
       <c r="B71" t="n">
-        <v>80473</v>
+        <v>80478</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518564</v>
+        <v>518502</v>
       </c>
       <c r="R71" t="n">
-        <v>6897207</v>
+        <v>6897111</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8453,32 +8453,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133828803</v>
+        <v>133828787</v>
       </c>
       <c r="B72" t="n">
-        <v>99178</v>
+        <v>83335</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8488,13 +8488,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>518221</v>
+        <v>518402</v>
       </c>
       <c r="R72" t="n">
-        <v>6896911</v>
+        <v>6897136</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8533,12 +8533,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8565,32 +8560,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133828843</v>
+        <v>133828849</v>
       </c>
       <c r="B73" t="n">
-        <v>80478</v>
+        <v>80473</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8600,13 +8595,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>518502</v>
+        <v>518564</v>
       </c>
       <c r="R73" t="n">
-        <v>6897111</v>
+        <v>6897207</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8635,7 +8630,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8645,7 +8640,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8672,32 +8667,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133828787</v>
+        <v>133828803</v>
       </c>
       <c r="B74" t="n">
-        <v>83335</v>
+        <v>99178</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8707,13 +8702,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518402</v>
+        <v>518221</v>
       </c>
       <c r="R74" t="n">
-        <v>6897136</v>
+        <v>6896911</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8742,7 +8737,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8752,7 +8747,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9765,32 +9765,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133828781</v>
+        <v>133828814</v>
       </c>
       <c r="B84" t="n">
-        <v>83335</v>
+        <v>99178</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518427</v>
+        <v>518236</v>
       </c>
       <c r="R84" t="n">
-        <v>6897159</v>
+        <v>6896855</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9845,7 +9845,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9872,32 +9877,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133828814</v>
+        <v>133828791</v>
       </c>
       <c r="B85" t="n">
-        <v>99178</v>
+        <v>83335</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9907,10 +9912,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518236</v>
+        <v>518371</v>
       </c>
       <c r="R85" t="n">
-        <v>6896855</v>
+        <v>6897086</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9942,7 +9947,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9952,12 +9957,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>45 ex</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10091,7 +10091,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133828791</v>
+        <v>133828781</v>
       </c>
       <c r="B87" t="n">
         <v>83335</v>
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518371</v>
+        <v>518427</v>
       </c>
       <c r="R87" t="n">
-        <v>6897086</v>
+        <v>6897159</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10310,32 +10310,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133828810</v>
+        <v>133828838</v>
       </c>
       <c r="B89" t="n">
-        <v>80478</v>
+        <v>79115</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10345,10 +10345,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>518240</v>
+        <v>518440</v>
       </c>
       <c r="R89" t="n">
-        <v>6896871</v>
+        <v>6897045</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10417,7 +10417,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133828804</v>
+        <v>133828844</v>
       </c>
       <c r="B90" t="n">
         <v>80473</v>
@@ -10452,10 +10452,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>518231</v>
+        <v>518502</v>
       </c>
       <c r="R90" t="n">
-        <v>6896913</v>
+        <v>6897113</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10524,10 +10524,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133828838</v>
+        <v>133828834</v>
       </c>
       <c r="B91" t="n">
-        <v>79115</v>
+        <v>80473</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10535,21 +10535,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>518440</v>
+        <v>518405</v>
       </c>
       <c r="R91" t="n">
-        <v>6897045</v>
+        <v>6897020</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10631,32 +10631,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133828844</v>
+        <v>133828810</v>
       </c>
       <c r="B92" t="n">
-        <v>80473</v>
+        <v>80478</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10666,10 +10666,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>518502</v>
+        <v>518240</v>
       </c>
       <c r="R92" t="n">
-        <v>6897113</v>
+        <v>6896871</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10738,7 +10738,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133828834</v>
+        <v>133828804</v>
       </c>
       <c r="B93" t="n">
         <v>80473</v>
@@ -10773,13 +10773,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>518405</v>
+        <v>518231</v>
       </c>
       <c r="R93" t="n">
-        <v>6897020</v>
+        <v>6896913</v>
       </c>
       <c r="S93" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10952,32 +10952,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133828842</v>
+        <v>133828785</v>
       </c>
       <c r="B95" t="n">
-        <v>79115</v>
+        <v>80367</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>518539</v>
+        <v>518394</v>
       </c>
       <c r="R95" t="n">
-        <v>6897099</v>
+        <v>6897139</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11059,10 +11059,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133828852</v>
+        <v>133828842</v>
       </c>
       <c r="B96" t="n">
-        <v>80473</v>
+        <v>79115</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11070,21 +11070,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>518557</v>
+        <v>518539</v>
       </c>
       <c r="R96" t="n">
-        <v>6897217</v>
+        <v>6897099</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11166,32 +11166,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133828785</v>
+        <v>133828852</v>
       </c>
       <c r="B97" t="n">
-        <v>80367</v>
+        <v>80473</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11201,13 +11201,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>518394</v>
+        <v>518557</v>
       </c>
       <c r="R97" t="n">
-        <v>6897139</v>
+        <v>6897217</v>
       </c>
       <c r="S97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -8346,32 +8346,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133828843</v>
+        <v>133828849</v>
       </c>
       <c r="B71" t="n">
-        <v>80478</v>
+        <v>80473</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518502</v>
+        <v>518564</v>
       </c>
       <c r="R71" t="n">
-        <v>6897111</v>
+        <v>6897207</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8453,32 +8453,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133828787</v>
+        <v>133828803</v>
       </c>
       <c r="B72" t="n">
-        <v>83335</v>
+        <v>99178</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8488,13 +8488,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>518402</v>
+        <v>518221</v>
       </c>
       <c r="R72" t="n">
-        <v>6897136</v>
+        <v>6896911</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8533,7 +8533,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8560,32 +8565,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133828849</v>
+        <v>133828843</v>
       </c>
       <c r="B73" t="n">
-        <v>80473</v>
+        <v>80478</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8595,13 +8600,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>518564</v>
+        <v>518502</v>
       </c>
       <c r="R73" t="n">
-        <v>6897207</v>
+        <v>6897111</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8630,7 +8635,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8640,7 +8645,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8667,32 +8672,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133828803</v>
+        <v>133828787</v>
       </c>
       <c r="B74" t="n">
-        <v>99178</v>
+        <v>83335</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8702,13 +8707,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518221</v>
+        <v>518402</v>
       </c>
       <c r="R74" t="n">
-        <v>6896911</v>
+        <v>6897136</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8737,7 +8742,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8747,12 +8752,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9765,32 +9765,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133828814</v>
+        <v>133828791</v>
       </c>
       <c r="B84" t="n">
-        <v>99178</v>
+        <v>83335</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518236</v>
+        <v>518371</v>
       </c>
       <c r="R84" t="n">
-        <v>6896855</v>
+        <v>6897086</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9845,12 +9845,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>45 ex</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9877,10 +9872,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133828791</v>
+        <v>133828835</v>
       </c>
       <c r="B85" t="n">
-        <v>83335</v>
+        <v>80473</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9888,21 +9883,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9912,10 +9907,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518371</v>
+        <v>518407</v>
       </c>
       <c r="R85" t="n">
-        <v>6897086</v>
+        <v>6897030</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9947,7 +9942,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9957,7 +9952,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9984,10 +9979,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133828835</v>
+        <v>133828781</v>
       </c>
       <c r="B86" t="n">
-        <v>80473</v>
+        <v>83335</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9995,21 +9990,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10019,10 +10014,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518407</v>
+        <v>518427</v>
       </c>
       <c r="R86" t="n">
-        <v>6897030</v>
+        <v>6897159</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10054,7 +10049,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10064,7 +10059,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10091,32 +10086,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133828781</v>
+        <v>133828830</v>
       </c>
       <c r="B87" t="n">
-        <v>83335</v>
+        <v>99178</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10126,10 +10121,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518427</v>
+        <v>518373</v>
       </c>
       <c r="R87" t="n">
-        <v>6897159</v>
+        <v>6897009</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10161,7 +10156,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10171,7 +10166,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10198,7 +10198,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133828830</v>
+        <v>133828814</v>
       </c>
       <c r="B88" t="n">
         <v>99178</v>
@@ -10233,10 +10233,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>518373</v>
+        <v>518236</v>
       </c>
       <c r="R88" t="n">
-        <v>6897009</v>
+        <v>6896855</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10278,12 +10278,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -3054,7 +3054,7 @@
         <v>133828845</v>
       </c>
       <c r="B23" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>133828823</v>
       </c>
       <c r="B24" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>133828824</v>
       </c>
       <c r="B25" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>133828841</v>
       </c>
       <c r="B26" t="n">
-        <v>83335</v>
+        <v>83336</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3489,10 +3489,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133828848</v>
+        <v>133828837</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>83336</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3500,42 +3500,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518510</v>
+        <v>518437</v>
       </c>
       <c r="R27" t="n">
-        <v>6897194</v>
+        <v>6897050</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3567,7 +3559,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3577,12 +3569,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3609,32 +3596,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133828837</v>
+        <v>133828789</v>
       </c>
       <c r="B28" t="n">
-        <v>83335</v>
+        <v>99180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3644,13 +3631,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518437</v>
+        <v>518446</v>
       </c>
       <c r="R28" t="n">
-        <v>6897050</v>
+        <v>6897134</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3679,7 +3666,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3689,7 +3676,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3716,48 +3708,56 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133828789</v>
+        <v>133828848</v>
       </c>
       <c r="B29" t="n">
-        <v>99178</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518446</v>
+        <v>518510</v>
       </c>
       <c r="R29" t="n">
-        <v>6897134</v>
+        <v>6897194</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,7 +3831,7 @@
         <v>133828831</v>
       </c>
       <c r="B30" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133828813</v>
+        <v>133828775</v>
       </c>
       <c r="B31" t="n">
-        <v>80473</v>
+        <v>83336</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3946,21 +3946,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518235</v>
+        <v>518420</v>
       </c>
       <c r="R31" t="n">
-        <v>6896853</v>
+        <v>6897194</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4042,10 +4042,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828807</v>
+        <v>133828813</v>
       </c>
       <c r="B32" t="n">
-        <v>79358</v>
+        <v>80474</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4053,21 +4053,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518247</v>
+        <v>518235</v>
       </c>
       <c r="R32" t="n">
-        <v>6896909</v>
+        <v>6896853</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4149,10 +4149,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133828775</v>
+        <v>133828807</v>
       </c>
       <c r="B33" t="n">
-        <v>83335</v>
+        <v>79359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518420</v>
+        <v>518247</v>
       </c>
       <c r="R33" t="n">
-        <v>6897194</v>
+        <v>6896909</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4259,7 +4259,7 @@
         <v>133828820</v>
       </c>
       <c r="B34" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>133828825</v>
       </c>
       <c r="B35" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>133828821</v>
       </c>
       <c r="B36" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4582,10 +4582,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133828788</v>
+        <v>133828840</v>
       </c>
       <c r="B37" t="n">
-        <v>79115</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4593,34 +4593,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518403</v>
+        <v>518482</v>
       </c>
       <c r="R37" t="n">
-        <v>6897135</v>
+        <v>6897062</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4652,7 +4660,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4662,7 +4670,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4689,32 +4702,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133828829</v>
+        <v>133828788</v>
       </c>
       <c r="B38" t="n">
-        <v>99178</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4724,10 +4737,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518329</v>
+        <v>518403</v>
       </c>
       <c r="R38" t="n">
-        <v>6896969</v>
+        <v>6897135</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4759,7 +4772,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4769,12 +4782,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4801,10 +4809,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133828790</v>
+        <v>133828829</v>
       </c>
       <c r="B39" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4836,10 +4844,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518391</v>
+        <v>518329</v>
       </c>
       <c r="R39" t="n">
-        <v>6897080</v>
+        <v>6896969</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4871,7 +4879,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4881,12 +4889,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>16 ex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4913,53 +4921,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133828840</v>
+        <v>133828790</v>
       </c>
       <c r="B40" t="n">
-        <v>57975</v>
+        <v>99180</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518482</v>
+        <v>518391</v>
       </c>
       <c r="R40" t="n">
-        <v>6897062</v>
+        <v>6897080</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>16 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5036,7 +5036,7 @@
         <v>133828796</v>
       </c>
       <c r="B41" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5380,32 +5380,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133828805</v>
+        <v>133828811</v>
       </c>
       <c r="B44" t="n">
-        <v>99178</v>
+        <v>80474</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518243</v>
+        <v>518240</v>
       </c>
       <c r="R44" t="n">
-        <v>6896917</v>
+        <v>6896871</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5460,12 +5460,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5492,32 +5487,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133828811</v>
+        <v>133828805</v>
       </c>
       <c r="B45" t="n">
-        <v>80473</v>
+        <v>99180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5527,10 +5522,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518240</v>
+        <v>518243</v>
       </c>
       <c r="R45" t="n">
-        <v>6896871</v>
+        <v>6896917</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5562,7 +5557,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5572,7 +5567,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5602,7 +5602,7 @@
         <v>133828816</v>
       </c>
       <c r="B46" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5706,10 +5706,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133828793</v>
+        <v>133828800</v>
       </c>
       <c r="B47" t="n">
-        <v>79390</v>
+        <v>83336</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5717,21 +5717,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518352</v>
+        <v>518301</v>
       </c>
       <c r="R47" t="n">
-        <v>6897090</v>
+        <v>6896988</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5813,32 +5813,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133828783</v>
+        <v>133828793</v>
       </c>
       <c r="B48" t="n">
-        <v>99178</v>
+        <v>79391</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5848,13 +5848,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518406</v>
+        <v>518352</v>
       </c>
       <c r="R48" t="n">
-        <v>6897153</v>
+        <v>6897090</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5893,12 +5893,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>11 ex</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5925,32 +5920,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133828778</v>
+        <v>133828783</v>
       </c>
       <c r="B49" t="n">
-        <v>79358</v>
+        <v>99180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5960,13 +5955,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518437</v>
+        <v>518406</v>
       </c>
       <c r="R49" t="n">
-        <v>6897164</v>
+        <v>6897153</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5995,7 +5990,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6005,7 +6000,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6032,10 +6032,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133828800</v>
+        <v>133828778</v>
       </c>
       <c r="B50" t="n">
-        <v>83335</v>
+        <v>79359</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6043,21 +6043,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518301</v>
+        <v>518437</v>
       </c>
       <c r="R50" t="n">
-        <v>6896988</v>
+        <v>6897164</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6139,10 +6139,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133828819</v>
+        <v>133828773</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>83344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6150,42 +6150,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518221</v>
+        <v>518414</v>
       </c>
       <c r="R51" t="n">
-        <v>6896825</v>
+        <v>6897216</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6217,7 +6209,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6227,12 +6219,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6259,32 +6246,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133828773</v>
+        <v>133828833</v>
       </c>
       <c r="B52" t="n">
-        <v>83343</v>
+        <v>80479</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6294,13 +6281,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518414</v>
+        <v>518405</v>
       </c>
       <c r="R52" t="n">
-        <v>6897216</v>
+        <v>6897021</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6329,7 +6316,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6339,7 +6326,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6366,48 +6353,56 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133828833</v>
+        <v>133828819</v>
       </c>
       <c r="B53" t="n">
-        <v>80478</v>
+        <v>57975</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518405</v>
+        <v>518221</v>
       </c>
       <c r="R53" t="n">
-        <v>6897021</v>
+        <v>6896825</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6436,7 +6431,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6446,7 +6441,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6476,7 +6476,7 @@
         <v>133828806</v>
       </c>
       <c r="B54" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>133828784</v>
       </c>
       <c r="B55" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>133828809</v>
       </c>
       <c r="B56" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>133828850</v>
       </c>
       <c r="B57" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>133828795</v>
       </c>
       <c r="B58" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>133828812</v>
       </c>
       <c r="B59" t="n">
-        <v>80474</v>
+        <v>80475</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>133828776</v>
       </c>
       <c r="B60" t="n">
-        <v>83335</v>
+        <v>83336</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>133828847</v>
       </c>
       <c r="B61" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>133828822</v>
       </c>
       <c r="B62" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>133828851</v>
       </c>
       <c r="B64" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>133828779</v>
       </c>
       <c r="B66" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>133828808</v>
       </c>
       <c r="B67" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>133828798</v>
       </c>
       <c r="B68" t="n">
-        <v>83326</v>
+        <v>83327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>133828777</v>
       </c>
       <c r="B69" t="n">
-        <v>83326</v>
+        <v>83327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>133828849</v>
       </c>
       <c r="B71" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>133828803</v>
       </c>
       <c r="B72" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>133828843</v>
       </c>
       <c r="B73" t="n">
-        <v>80478</v>
+        <v>80479</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>133828787</v>
       </c>
       <c r="B74" t="n">
-        <v>83335</v>
+        <v>83336</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>133828771</v>
       </c>
       <c r="B75" t="n">
-        <v>80478</v>
+        <v>80479</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>133828826</v>
       </c>
       <c r="B76" t="n">
-        <v>83335</v>
+        <v>83336</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>133828772</v>
       </c>
       <c r="B77" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>133828815</v>
       </c>
       <c r="B78" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>133828836</v>
       </c>
       <c r="B79" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>133828780</v>
       </c>
       <c r="B80" t="n">
-        <v>97291</v>
+        <v>97293</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>133828786</v>
       </c>
       <c r="B81" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>133828782</v>
       </c>
       <c r="B82" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9765,10 +9765,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133828791</v>
+        <v>133828835</v>
       </c>
       <c r="B84" t="n">
-        <v>83335</v>
+        <v>80474</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9776,21 +9776,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518371</v>
+        <v>518407</v>
       </c>
       <c r="R84" t="n">
-        <v>6897086</v>
+        <v>6897030</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9872,10 +9872,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133828835</v>
+        <v>133828781</v>
       </c>
       <c r="B85" t="n">
-        <v>80473</v>
+        <v>83336</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9883,21 +9883,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9907,10 +9907,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518407</v>
+        <v>518427</v>
       </c>
       <c r="R85" t="n">
-        <v>6897030</v>
+        <v>6897159</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9979,10 +9979,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133828781</v>
+        <v>133828791</v>
       </c>
       <c r="B86" t="n">
-        <v>83335</v>
+        <v>83336</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10014,10 +10014,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518427</v>
+        <v>518371</v>
       </c>
       <c r="R86" t="n">
-        <v>6897159</v>
+        <v>6897086</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10089,7 +10089,7 @@
         <v>133828830</v>
       </c>
       <c r="B87" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>133828814</v>
       </c>
       <c r="B88" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10310,32 +10310,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133828838</v>
+        <v>133828810</v>
       </c>
       <c r="B89" t="n">
-        <v>79115</v>
+        <v>80479</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10345,10 +10345,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>518440</v>
+        <v>518240</v>
       </c>
       <c r="R89" t="n">
-        <v>6897045</v>
+        <v>6896871</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10417,10 +10417,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133828844</v>
+        <v>133828804</v>
       </c>
       <c r="B90" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10452,10 +10452,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>518502</v>
+        <v>518231</v>
       </c>
       <c r="R90" t="n">
-        <v>6897113</v>
+        <v>6896913</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10524,10 +10524,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133828834</v>
+        <v>133828838</v>
       </c>
       <c r="B91" t="n">
-        <v>80473</v>
+        <v>79116</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10535,21 +10535,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>518405</v>
+        <v>518440</v>
       </c>
       <c r="R91" t="n">
-        <v>6897020</v>
+        <v>6897045</v>
       </c>
       <c r="S91" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10631,32 +10631,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133828810</v>
+        <v>133828844</v>
       </c>
       <c r="B92" t="n">
-        <v>80478</v>
+        <v>80474</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10666,10 +10666,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>518240</v>
+        <v>518502</v>
       </c>
       <c r="R92" t="n">
-        <v>6896871</v>
+        <v>6897113</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10738,10 +10738,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133828804</v>
+        <v>133828834</v>
       </c>
       <c r="B93" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10773,13 +10773,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>518231</v>
+        <v>518405</v>
       </c>
       <c r="R93" t="n">
-        <v>6896913</v>
+        <v>6897020</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10848,7 +10848,7 @@
         <v>133828794</v>
       </c>
       <c r="B94" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>133828785</v>
       </c>
       <c r="B95" t="n">
-        <v>80367</v>
+        <v>80368</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11059,10 +11059,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133828842</v>
+        <v>133828852</v>
       </c>
       <c r="B96" t="n">
-        <v>79115</v>
+        <v>80474</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11070,21 +11070,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>518539</v>
+        <v>518557</v>
       </c>
       <c r="R96" t="n">
-        <v>6897099</v>
+        <v>6897217</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11166,10 +11166,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133828852</v>
+        <v>133828842</v>
       </c>
       <c r="B97" t="n">
-        <v>80473</v>
+        <v>79116</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11177,21 +11177,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11201,10 +11201,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>518557</v>
+        <v>518539</v>
       </c>
       <c r="R97" t="n">
-        <v>6897217</v>
+        <v>6897099</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -3158,7 +3158,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133828823</v>
+        <v>133828845</v>
       </c>
       <c r="B24" t="n">
         <v>99181</v>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518272</v>
+        <v>518477</v>
       </c>
       <c r="R24" t="n">
-        <v>6896819</v>
+        <v>6897110</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,7 +3270,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133828845</v>
+        <v>133828823</v>
       </c>
       <c r="B25" t="n">
         <v>99181</v>
@@ -3305,10 +3305,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518477</v>
+        <v>518272</v>
       </c>
       <c r="R25" t="n">
-        <v>6897110</v>
+        <v>6896819</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,10 +3382,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133828848</v>
+        <v>133828837</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>83336</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3393,42 +3393,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518510</v>
+        <v>518437</v>
       </c>
       <c r="R26" t="n">
-        <v>6897194</v>
+        <v>6897050</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3460,7 +3452,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3470,12 +3462,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3502,32 +3489,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133828789</v>
+        <v>133828841</v>
       </c>
       <c r="B27" t="n">
-        <v>99181</v>
+        <v>83336</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3537,13 +3524,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518446</v>
+        <v>518489</v>
       </c>
       <c r="R27" t="n">
-        <v>6897134</v>
+        <v>6897064</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3572,7 +3559,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3582,12 +3569,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3614,10 +3596,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133828841</v>
+        <v>133828848</v>
       </c>
       <c r="B28" t="n">
-        <v>83336</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3625,34 +3607,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518489</v>
+        <v>518510</v>
       </c>
       <c r="R28" t="n">
-        <v>6897064</v>
+        <v>6897194</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3684,7 +3674,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,7 +3684,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3721,32 +3716,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133828837</v>
+        <v>133828789</v>
       </c>
       <c r="B29" t="n">
-        <v>83336</v>
+        <v>99181</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3756,13 +3751,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518437</v>
+        <v>518446</v>
       </c>
       <c r="R29" t="n">
-        <v>6897050</v>
+        <v>6897134</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3791,7 +3786,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3801,7 +3796,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3828,10 +3828,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828807</v>
+        <v>133828813</v>
       </c>
       <c r="B30" t="n">
-        <v>79359</v>
+        <v>80474</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3839,21 +3839,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518247</v>
+        <v>518235</v>
       </c>
       <c r="R30" t="n">
-        <v>6896909</v>
+        <v>6896853</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4042,7 +4042,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828813</v>
+        <v>133828831</v>
       </c>
       <c r="B32" t="n">
         <v>80474</v>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518235</v>
+        <v>518389</v>
       </c>
       <c r="R32" t="n">
-        <v>6896853</v>
+        <v>6897022</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4149,32 +4149,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133828825</v>
+        <v>133828807</v>
       </c>
       <c r="B33" t="n">
-        <v>99181</v>
+        <v>79359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518279</v>
+        <v>518247</v>
       </c>
       <c r="R33" t="n">
-        <v>6896843</v>
+        <v>6896909</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4229,12 +4229,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1 ex</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4261,7 +4256,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133828831</v>
+        <v>133828820</v>
       </c>
       <c r="B34" t="n">
         <v>80474</v>
@@ -4296,10 +4291,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518389</v>
+        <v>518236</v>
       </c>
       <c r="R34" t="n">
-        <v>6897022</v>
+        <v>6896830</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4331,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4341,7 +4336,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4475,32 +4470,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133828820</v>
+        <v>133828825</v>
       </c>
       <c r="B36" t="n">
-        <v>80474</v>
+        <v>99181</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4510,10 +4505,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518236</v>
+        <v>518279</v>
       </c>
       <c r="R36" t="n">
-        <v>6896830</v>
+        <v>6896843</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4545,7 +4540,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4555,7 +4550,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4582,32 +4582,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133828829</v>
+        <v>133828788</v>
       </c>
       <c r="B37" t="n">
-        <v>99181</v>
+        <v>79116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518329</v>
+        <v>518403</v>
       </c>
       <c r="R37" t="n">
-        <v>6896969</v>
+        <v>6897135</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4662,12 +4662,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4694,53 +4689,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133828840</v>
+        <v>133828829</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518482</v>
+        <v>518329</v>
       </c>
       <c r="R38" t="n">
-        <v>6897062</v>
+        <v>6896969</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4772,7 +4759,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4782,12 +4769,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4814,32 +4801,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133828788</v>
+        <v>133828790</v>
       </c>
       <c r="B39" t="n">
-        <v>79116</v>
+        <v>99181</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4849,10 +4836,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518403</v>
+        <v>518391</v>
       </c>
       <c r="R39" t="n">
-        <v>6897135</v>
+        <v>6897080</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4884,7 +4871,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4894,7 +4881,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>16 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4921,45 +4913,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133828790</v>
+        <v>133828840</v>
       </c>
       <c r="B40" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518391</v>
+        <v>518482</v>
       </c>
       <c r="R40" t="n">
-        <v>6897080</v>
+        <v>6897062</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>16 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5380,32 +5380,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133828805</v>
+        <v>133828811</v>
       </c>
       <c r="B44" t="n">
-        <v>99181</v>
+        <v>80474</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518243</v>
+        <v>518240</v>
       </c>
       <c r="R44" t="n">
-        <v>6896917</v>
+        <v>6896871</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5460,12 +5460,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5492,32 +5487,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133828811</v>
+        <v>133828805</v>
       </c>
       <c r="B45" t="n">
-        <v>80474</v>
+        <v>99181</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5527,10 +5522,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518240</v>
+        <v>518243</v>
       </c>
       <c r="R45" t="n">
-        <v>6896871</v>
+        <v>6896917</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5562,7 +5557,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5572,7 +5567,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5599,32 +5599,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133828783</v>
+        <v>133828793</v>
       </c>
       <c r="B46" t="n">
-        <v>99181</v>
+        <v>79391</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5634,13 +5634,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518406</v>
+        <v>518352</v>
       </c>
       <c r="R46" t="n">
-        <v>6897153</v>
+        <v>6897090</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5679,12 +5679,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>11 ex</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5711,10 +5706,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133828816</v>
+        <v>133828800</v>
       </c>
       <c r="B47" t="n">
-        <v>79359</v>
+        <v>83336</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5722,21 +5717,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5746,10 +5741,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518222</v>
+        <v>518301</v>
       </c>
       <c r="R47" t="n">
-        <v>6896862</v>
+        <v>6896988</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5781,7 +5776,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5791,7 +5786,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5818,32 +5813,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133828793</v>
+        <v>133828783</v>
       </c>
       <c r="B48" t="n">
-        <v>79391</v>
+        <v>99181</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5853,13 +5848,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518352</v>
+        <v>518406</v>
       </c>
       <c r="R48" t="n">
-        <v>6897090</v>
+        <v>6897153</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5888,7 +5883,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5898,7 +5893,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6032,10 +6032,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133828800</v>
+        <v>133828816</v>
       </c>
       <c r="B50" t="n">
-        <v>83336</v>
+        <v>79359</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6043,21 +6043,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518301</v>
+        <v>518222</v>
       </c>
       <c r="R50" t="n">
-        <v>6896988</v>
+        <v>6896862</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6139,32 +6139,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133828773</v>
+        <v>133828833</v>
       </c>
       <c r="B51" t="n">
-        <v>83344</v>
+        <v>80479</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6174,13 +6174,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518414</v>
+        <v>518405</v>
       </c>
       <c r="R51" t="n">
-        <v>6897216</v>
+        <v>6897021</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6246,10 +6246,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133828819</v>
+        <v>133828773</v>
       </c>
       <c r="B52" t="n">
-        <v>57975</v>
+        <v>83344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6257,42 +6257,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518221</v>
+        <v>518414</v>
       </c>
       <c r="R52" t="n">
-        <v>6896825</v>
+        <v>6897216</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6324,7 +6316,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6334,12 +6326,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6366,48 +6353,56 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133828833</v>
+        <v>133828819</v>
       </c>
       <c r="B53" t="n">
-        <v>80479</v>
+        <v>57975</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518405</v>
+        <v>518221</v>
       </c>
       <c r="R53" t="n">
-        <v>6897021</v>
+        <v>6896825</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6436,7 +6431,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6446,7 +6441,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6473,10 +6473,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133828850</v>
+        <v>133828806</v>
       </c>
       <c r="B54" t="n">
-        <v>79359</v>
+        <v>80474</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6484,21 +6484,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518594</v>
+        <v>518246</v>
       </c>
       <c r="R54" t="n">
-        <v>6897257</v>
+        <v>6896911</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6580,10 +6580,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133828809</v>
+        <v>133828850</v>
       </c>
       <c r="B55" t="n">
-        <v>80474</v>
+        <v>79359</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518251</v>
+        <v>518594</v>
       </c>
       <c r="R55" t="n">
-        <v>6896886</v>
+        <v>6897257</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6687,7 +6687,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133828806</v>
+        <v>133828809</v>
       </c>
       <c r="B56" t="n">
         <v>80474</v>
@@ -6722,10 +6722,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518246</v>
+        <v>518251</v>
       </c>
       <c r="R56" t="n">
-        <v>6896911</v>
+        <v>6896886</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6906,10 +6906,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133828795</v>
+        <v>133828812</v>
       </c>
       <c r="B58" t="n">
-        <v>79116</v>
+        <v>80475</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6917,21 +6917,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6941,10 +6941,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518327</v>
+        <v>518235</v>
       </c>
       <c r="R58" t="n">
-        <v>6897030</v>
+        <v>6896851</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7120,10 +7120,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133828812</v>
+        <v>133828795</v>
       </c>
       <c r="B60" t="n">
-        <v>80475</v>
+        <v>79116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7131,21 +7131,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518235</v>
+        <v>518327</v>
       </c>
       <c r="R60" t="n">
-        <v>6896851</v>
+        <v>6897030</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7905,7 +7905,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133828798</v>
+        <v>133828777</v>
       </c>
       <c r="B67" t="n">
         <v>83327</v>
@@ -7940,10 +7940,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518339</v>
+        <v>518435</v>
       </c>
       <c r="R67" t="n">
-        <v>6897004</v>
+        <v>6897176</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8012,32 +8012,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133828777</v>
+        <v>133828808</v>
       </c>
       <c r="B68" t="n">
-        <v>83327</v>
+        <v>80474</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8047,10 +8047,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518435</v>
+        <v>518250</v>
       </c>
       <c r="R68" t="n">
-        <v>6897176</v>
+        <v>6896903</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8119,32 +8119,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133828808</v>
+        <v>133828798</v>
       </c>
       <c r="B69" t="n">
-        <v>80474</v>
+        <v>83327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8154,10 +8154,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>518250</v>
+        <v>518339</v>
       </c>
       <c r="R69" t="n">
-        <v>6896903</v>
+        <v>6897004</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8346,32 +8346,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133828803</v>
+        <v>133828771</v>
       </c>
       <c r="B71" t="n">
-        <v>99181</v>
+        <v>80479</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518221</v>
+        <v>518411</v>
       </c>
       <c r="R71" t="n">
-        <v>6896911</v>
+        <v>6897234</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8426,12 +8426,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8458,32 +8453,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133828843</v>
+        <v>133828803</v>
       </c>
       <c r="B72" t="n">
-        <v>80479</v>
+        <v>99181</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8493,10 +8488,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>518502</v>
+        <v>518221</v>
       </c>
       <c r="R72" t="n">
-        <v>6897111</v>
+        <v>6896911</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8528,7 +8523,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8538,7 +8533,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8565,7 +8565,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133828771</v>
+        <v>133828843</v>
       </c>
       <c r="B73" t="n">
         <v>80479</v>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>518411</v>
+        <v>518502</v>
       </c>
       <c r="R73" t="n">
-        <v>6897234</v>
+        <v>6897111</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8672,10 +8672,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133828849</v>
+        <v>133828787</v>
       </c>
       <c r="B74" t="n">
-        <v>80474</v>
+        <v>83336</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8683,21 +8683,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518564</v>
+        <v>518402</v>
       </c>
       <c r="R74" t="n">
-        <v>6897207</v>
+        <v>6897136</v>
       </c>
       <c r="S74" t="n">
         <v>6</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133828787</v>
+        <v>133828849</v>
       </c>
       <c r="B75" t="n">
-        <v>83336</v>
+        <v>80474</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8790,21 +8790,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>518402</v>
+        <v>518564</v>
       </c>
       <c r="R75" t="n">
-        <v>6897136</v>
+        <v>6897207</v>
       </c>
       <c r="S75" t="n">
         <v>6</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8886,10 +8886,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133828826</v>
+        <v>133828815</v>
       </c>
       <c r="B76" t="n">
-        <v>83336</v>
+        <v>80474</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8897,21 +8897,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>518269</v>
+        <v>518230</v>
       </c>
       <c r="R76" t="n">
-        <v>6896902</v>
+        <v>6896858</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8993,32 +8993,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133828815</v>
+        <v>133828772</v>
       </c>
       <c r="B77" t="n">
-        <v>80474</v>
+        <v>99181</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>518230</v>
+        <v>518419</v>
       </c>
       <c r="R77" t="n">
-        <v>6896858</v>
+        <v>6897228</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9073,7 +9073,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9100,32 +9105,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133828772</v>
+        <v>133828826</v>
       </c>
       <c r="B78" t="n">
-        <v>99181</v>
+        <v>83336</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9135,10 +9140,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>518419</v>
+        <v>518269</v>
       </c>
       <c r="R78" t="n">
-        <v>6897228</v>
+        <v>6896902</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9170,7 +9175,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9180,12 +9185,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>7 ex</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9426,10 +9426,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133828799</v>
+        <v>133828782</v>
       </c>
       <c r="B81" t="n">
-        <v>57975</v>
+        <v>80474</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9437,42 +9437,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>518312</v>
+        <v>518424</v>
       </c>
       <c r="R81" t="n">
-        <v>6896987</v>
+        <v>6897159</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9504,7 +9496,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9514,12 +9506,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9546,32 +9533,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133828782</v>
+        <v>133828786</v>
       </c>
       <c r="B82" t="n">
-        <v>80474</v>
+        <v>99181</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9581,10 +9568,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>518424</v>
+        <v>518399</v>
       </c>
       <c r="R82" t="n">
-        <v>6897159</v>
+        <v>6897137</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9616,7 +9603,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9626,7 +9613,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9653,45 +9645,53 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133828786</v>
+        <v>133828799</v>
       </c>
       <c r="B83" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>518399</v>
+        <v>518312</v>
       </c>
       <c r="R83" t="n">
-        <v>6897137</v>
+        <v>6896987</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9733,12 +9733,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>85 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9765,32 +9765,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133828814</v>
+        <v>133828791</v>
       </c>
       <c r="B84" t="n">
-        <v>99181</v>
+        <v>83336</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518236</v>
+        <v>518371</v>
       </c>
       <c r="R84" t="n">
-        <v>6896855</v>
+        <v>6897086</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9845,12 +9845,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>45 ex</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9877,32 +9872,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133828791</v>
+        <v>133828830</v>
       </c>
       <c r="B85" t="n">
-        <v>83336</v>
+        <v>99181</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9912,10 +9907,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518371</v>
+        <v>518373</v>
       </c>
       <c r="R85" t="n">
-        <v>6897086</v>
+        <v>6897009</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9947,7 +9942,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9957,7 +9952,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9984,32 +9984,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133828835</v>
+        <v>133828814</v>
       </c>
       <c r="B86" t="n">
-        <v>80474</v>
+        <v>99181</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10019,10 +10019,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518407</v>
+        <v>518236</v>
       </c>
       <c r="R86" t="n">
-        <v>6897030</v>
+        <v>6896855</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10064,7 +10064,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10091,32 +10096,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133828830</v>
+        <v>133828781</v>
       </c>
       <c r="B87" t="n">
-        <v>99181</v>
+        <v>83336</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10126,10 +10131,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518373</v>
+        <v>518427</v>
       </c>
       <c r="R87" t="n">
-        <v>6897009</v>
+        <v>6897159</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10161,7 +10166,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10171,12 +10176,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>9 ex</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10203,10 +10203,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133828781</v>
+        <v>133828835</v>
       </c>
       <c r="B88" t="n">
-        <v>83336</v>
+        <v>80474</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10214,21 +10214,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10238,10 +10238,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>518427</v>
+        <v>518407</v>
       </c>
       <c r="R88" t="n">
-        <v>6897159</v>
+        <v>6897030</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10310,32 +10310,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133828810</v>
+        <v>133828838</v>
       </c>
       <c r="B89" t="n">
-        <v>80479</v>
+        <v>79116</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10345,10 +10345,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>518240</v>
+        <v>518440</v>
       </c>
       <c r="R89" t="n">
-        <v>6896871</v>
+        <v>6897045</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10524,10 +10524,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133828838</v>
+        <v>133828804</v>
       </c>
       <c r="B91" t="n">
-        <v>79116</v>
+        <v>80474</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10535,21 +10535,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10559,10 +10559,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>518440</v>
+        <v>518231</v>
       </c>
       <c r="R91" t="n">
-        <v>6897045</v>
+        <v>6896913</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10631,32 +10631,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133828834</v>
+        <v>133828810</v>
       </c>
       <c r="B92" t="n">
-        <v>80474</v>
+        <v>80479</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10666,13 +10666,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>518405</v>
+        <v>518240</v>
       </c>
       <c r="R92" t="n">
-        <v>6897020</v>
+        <v>6896871</v>
       </c>
       <c r="S92" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10738,7 +10738,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133828804</v>
+        <v>133828834</v>
       </c>
       <c r="B93" t="n">
         <v>80474</v>
@@ -10773,13 +10773,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>518231</v>
+        <v>518405</v>
       </c>
       <c r="R93" t="n">
-        <v>6896913</v>
+        <v>6897020</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10845,32 +10845,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133828842</v>
+        <v>133828785</v>
       </c>
       <c r="B94" t="n">
-        <v>79116</v>
+        <v>80368</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10880,13 +10880,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>518539</v>
+        <v>518394</v>
       </c>
       <c r="R94" t="n">
-        <v>6897099</v>
+        <v>6897139</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10952,10 +10952,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133828852</v>
+        <v>133828794</v>
       </c>
       <c r="B95" t="n">
-        <v>80474</v>
+        <v>79359</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10963,21 +10963,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10987,10 +10987,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>518557</v>
+        <v>518380</v>
       </c>
       <c r="R95" t="n">
-        <v>6897217</v>
+        <v>6897032</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11059,32 +11059,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133828785</v>
+        <v>133828842</v>
       </c>
       <c r="B96" t="n">
-        <v>80368</v>
+        <v>79116</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11094,13 +11094,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>518394</v>
+        <v>518539</v>
       </c>
       <c r="R96" t="n">
-        <v>6897139</v>
+        <v>6897099</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11166,10 +11166,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133828794</v>
+        <v>133828852</v>
       </c>
       <c r="B97" t="n">
-        <v>79359</v>
+        <v>80474</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11177,21 +11177,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11201,10 +11201,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>518380</v>
+        <v>518557</v>
       </c>
       <c r="R97" t="n">
-        <v>6897032</v>
+        <v>6897217</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -3054,7 +3054,7 @@
         <v>133828824</v>
       </c>
       <c r="B23" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,10 +3158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133828845</v>
+        <v>133828823</v>
       </c>
       <c r="B24" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518477</v>
+        <v>518272</v>
       </c>
       <c r="R24" t="n">
-        <v>6897110</v>
+        <v>6896819</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,10 +3270,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133828823</v>
+        <v>133828845</v>
       </c>
       <c r="B25" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3305,10 +3305,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518272</v>
+        <v>518477</v>
       </c>
       <c r="R25" t="n">
-        <v>6896819</v>
+        <v>6897110</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,10 +3382,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133828837</v>
+        <v>133828848</v>
       </c>
       <c r="B26" t="n">
-        <v>83336</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3393,34 +3393,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518437</v>
+        <v>518510</v>
       </c>
       <c r="R26" t="n">
-        <v>6897050</v>
+        <v>6897194</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3452,7 +3460,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,7 +3470,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3489,32 +3502,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133828841</v>
+        <v>133828789</v>
       </c>
       <c r="B27" t="n">
-        <v>83336</v>
+        <v>99188</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3524,13 +3537,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518489</v>
+        <v>518446</v>
       </c>
       <c r="R27" t="n">
-        <v>6897064</v>
+        <v>6897134</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3559,7 +3572,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3569,7 +3582,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3596,10 +3614,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133828848</v>
+        <v>133828841</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>83343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,42 +3625,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518510</v>
+        <v>518489</v>
       </c>
       <c r="R28" t="n">
-        <v>6897194</v>
+        <v>6897064</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3674,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3684,12 +3694,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3716,32 +3721,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133828789</v>
+        <v>133828837</v>
       </c>
       <c r="B29" t="n">
-        <v>99181</v>
+        <v>83343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3751,13 +3756,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518446</v>
+        <v>518437</v>
       </c>
       <c r="R29" t="n">
-        <v>6897134</v>
+        <v>6897050</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3786,7 +3791,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3796,12 +3801,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3828,10 +3828,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828813</v>
+        <v>133828807</v>
       </c>
       <c r="B30" t="n">
-        <v>80474</v>
+        <v>79366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3839,21 +3839,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518235</v>
+        <v>518247</v>
       </c>
       <c r="R30" t="n">
-        <v>6896853</v>
+        <v>6896909</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3938,7 +3938,7 @@
         <v>133828821</v>
       </c>
       <c r="B31" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4042,10 +4042,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828831</v>
+        <v>133828813</v>
       </c>
       <c r="B32" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518389</v>
+        <v>518235</v>
       </c>
       <c r="R32" t="n">
-        <v>6897022</v>
+        <v>6896853</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4149,32 +4149,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133828807</v>
+        <v>133828825</v>
       </c>
       <c r="B33" t="n">
-        <v>79359</v>
+        <v>99188</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518247</v>
+        <v>518279</v>
       </c>
       <c r="R33" t="n">
-        <v>6896909</v>
+        <v>6896843</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4229,7 +4229,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,10 +4261,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133828820</v>
+        <v>133828831</v>
       </c>
       <c r="B34" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4291,10 +4296,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518236</v>
+        <v>518389</v>
       </c>
       <c r="R34" t="n">
-        <v>6896830</v>
+        <v>6897022</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4326,7 +4331,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,7 +4341,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4363,10 +4368,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133828775</v>
+        <v>133828820</v>
       </c>
       <c r="B35" t="n">
-        <v>83336</v>
+        <v>80481</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4374,21 +4379,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4398,10 +4403,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518420</v>
+        <v>518236</v>
       </c>
       <c r="R35" t="n">
-        <v>6897194</v>
+        <v>6896830</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4433,7 +4438,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4443,7 +4448,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4470,32 +4475,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133828825</v>
+        <v>133828775</v>
       </c>
       <c r="B36" t="n">
-        <v>99181</v>
+        <v>83343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4505,10 +4510,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518279</v>
+        <v>518420</v>
       </c>
       <c r="R36" t="n">
-        <v>6896843</v>
+        <v>6897194</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4540,7 +4545,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4550,12 +4555,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>1 ex</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4582,32 +4582,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133828788</v>
+        <v>133828829</v>
       </c>
       <c r="B37" t="n">
-        <v>79116</v>
+        <v>99188</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518403</v>
+        <v>518329</v>
       </c>
       <c r="R37" t="n">
-        <v>6897135</v>
+        <v>6896969</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4662,7 +4662,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4689,45 +4694,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133828829</v>
+        <v>133828840</v>
       </c>
       <c r="B38" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518329</v>
+        <v>518482</v>
       </c>
       <c r="R38" t="n">
-        <v>6896969</v>
+        <v>6897062</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4759,7 +4772,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4769,12 +4782,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4801,32 +4814,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133828790</v>
+        <v>133828788</v>
       </c>
       <c r="B39" t="n">
-        <v>99181</v>
+        <v>79123</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4836,10 +4849,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518391</v>
+        <v>518403</v>
       </c>
       <c r="R39" t="n">
-        <v>6897080</v>
+        <v>6897135</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4871,7 +4884,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4881,12 +4894,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>16 ex</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4913,53 +4921,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133828840</v>
+        <v>133828790</v>
       </c>
       <c r="B40" t="n">
-        <v>57975</v>
+        <v>99188</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518482</v>
+        <v>518391</v>
       </c>
       <c r="R40" t="n">
-        <v>6897062</v>
+        <v>6897080</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>16 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5276,7 +5276,7 @@
         <v>133828796</v>
       </c>
       <c r="B43" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5380,32 +5380,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133828811</v>
+        <v>133828805</v>
       </c>
       <c r="B44" t="n">
-        <v>80474</v>
+        <v>99188</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518240</v>
+        <v>518243</v>
       </c>
       <c r="R44" t="n">
-        <v>6896871</v>
+        <v>6896917</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5460,7 +5460,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5487,32 +5492,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133828805</v>
+        <v>133828811</v>
       </c>
       <c r="B45" t="n">
-        <v>99181</v>
+        <v>80481</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5522,10 +5527,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518243</v>
+        <v>518240</v>
       </c>
       <c r="R45" t="n">
-        <v>6896917</v>
+        <v>6896871</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5557,7 +5562,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5567,12 +5572,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5599,32 +5599,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133828793</v>
+        <v>133828783</v>
       </c>
       <c r="B46" t="n">
-        <v>79391</v>
+        <v>99188</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5634,13 +5634,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518352</v>
+        <v>518406</v>
       </c>
       <c r="R46" t="n">
-        <v>6897090</v>
+        <v>6897153</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5679,7 +5679,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5706,10 +5711,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133828800</v>
+        <v>133828816</v>
       </c>
       <c r="B47" t="n">
-        <v>83336</v>
+        <v>79366</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5717,21 +5722,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5741,10 +5746,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518301</v>
+        <v>518222</v>
       </c>
       <c r="R47" t="n">
-        <v>6896988</v>
+        <v>6896862</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5776,7 +5781,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5786,7 +5791,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5813,32 +5818,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133828783</v>
+        <v>133828793</v>
       </c>
       <c r="B48" t="n">
-        <v>99181</v>
+        <v>79398</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5848,13 +5853,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518406</v>
+        <v>518352</v>
       </c>
       <c r="R48" t="n">
-        <v>6897153</v>
+        <v>6897090</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5883,7 +5888,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5893,12 +5898,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>11 ex</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5928,7 +5928,7 @@
         <v>133828778</v>
       </c>
       <c r="B49" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133828816</v>
+        <v>133828800</v>
       </c>
       <c r="B50" t="n">
-        <v>79359</v>
+        <v>83343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6043,21 +6043,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518222</v>
+        <v>518301</v>
       </c>
       <c r="R50" t="n">
-        <v>6896862</v>
+        <v>6896988</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6139,32 +6139,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133828833</v>
+        <v>133828773</v>
       </c>
       <c r="B51" t="n">
-        <v>80479</v>
+        <v>83351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6174,13 +6174,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518405</v>
+        <v>518414</v>
       </c>
       <c r="R51" t="n">
-        <v>6897021</v>
+        <v>6897216</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6246,10 +6246,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133828773</v>
+        <v>133828819</v>
       </c>
       <c r="B52" t="n">
-        <v>83344</v>
+        <v>57975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6257,34 +6257,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518414</v>
+        <v>518221</v>
       </c>
       <c r="R52" t="n">
-        <v>6897216</v>
+        <v>6896825</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6316,7 +6324,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6326,7 +6334,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6353,56 +6366,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133828819</v>
+        <v>133828833</v>
       </c>
       <c r="B53" t="n">
-        <v>57975</v>
+        <v>80486</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518221</v>
+        <v>518405</v>
       </c>
       <c r="R53" t="n">
-        <v>6896825</v>
+        <v>6897021</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6431,7 +6436,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6441,12 +6446,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6473,10 +6473,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133828806</v>
+        <v>133828850</v>
       </c>
       <c r="B54" t="n">
-        <v>80474</v>
+        <v>79366</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6484,21 +6484,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518246</v>
+        <v>518594</v>
       </c>
       <c r="R54" t="n">
-        <v>6896911</v>
+        <v>6897257</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6580,10 +6580,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133828850</v>
+        <v>133828809</v>
       </c>
       <c r="B55" t="n">
-        <v>79359</v>
+        <v>80481</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518594</v>
+        <v>518251</v>
       </c>
       <c r="R55" t="n">
-        <v>6897257</v>
+        <v>6896886</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6687,10 +6687,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133828809</v>
+        <v>133828806</v>
       </c>
       <c r="B56" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6722,10 +6722,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518251</v>
+        <v>518246</v>
       </c>
       <c r="R56" t="n">
-        <v>6896886</v>
+        <v>6896911</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6797,7 +6797,7 @@
         <v>133828784</v>
       </c>
       <c r="B57" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>133828812</v>
       </c>
       <c r="B58" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7013,10 +7013,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133828776</v>
+        <v>133828795</v>
       </c>
       <c r="B59" t="n">
-        <v>83336</v>
+        <v>79123</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7024,21 +7024,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>308</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518435</v>
+        <v>518327</v>
       </c>
       <c r="R59" t="n">
-        <v>6897176</v>
+        <v>6897030</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7120,10 +7120,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133828795</v>
+        <v>133828776</v>
       </c>
       <c r="B60" t="n">
-        <v>79116</v>
+        <v>83343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7131,21 +7131,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518327</v>
+        <v>518435</v>
       </c>
       <c r="R60" t="n">
-        <v>6897030</v>
+        <v>6897176</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7230,7 +7230,7 @@
         <v>133828822</v>
       </c>
       <c r="B61" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>133828847</v>
       </c>
       <c r="B63" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>133828851</v>
       </c>
       <c r="B64" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>133828779</v>
       </c>
       <c r="B66" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7905,45 +7905,53 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133828777</v>
+        <v>133828827</v>
       </c>
       <c r="B67" t="n">
-        <v>83327</v>
+        <v>57975</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518435</v>
+        <v>518303</v>
       </c>
       <c r="R67" t="n">
-        <v>6897176</v>
+        <v>6896962</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7975,7 +7983,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7985,7 +7993,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8012,32 +8025,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133828808</v>
+        <v>133828798</v>
       </c>
       <c r="B68" t="n">
-        <v>80474</v>
+        <v>83334</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8047,10 +8060,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518250</v>
+        <v>518339</v>
       </c>
       <c r="R68" t="n">
-        <v>6896903</v>
+        <v>6897004</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8082,7 +8095,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8092,7 +8105,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8119,10 +8132,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133828798</v>
+        <v>133828777</v>
       </c>
       <c r="B69" t="n">
-        <v>83327</v>
+        <v>83334</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8154,10 +8167,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>518339</v>
+        <v>518435</v>
       </c>
       <c r="R69" t="n">
-        <v>6897004</v>
+        <v>6897176</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8189,7 +8202,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8199,7 +8212,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8226,10 +8239,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133828827</v>
+        <v>133828808</v>
       </c>
       <c r="B70" t="n">
-        <v>57975</v>
+        <v>80481</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8237,42 +8250,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>518303</v>
+        <v>518250</v>
       </c>
       <c r="R70" t="n">
-        <v>6896962</v>
+        <v>6896903</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8304,7 +8309,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8314,12 +8319,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8346,32 +8346,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133828771</v>
+        <v>133828849</v>
       </c>
       <c r="B71" t="n">
-        <v>80479</v>
+        <v>80481</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518411</v>
+        <v>518564</v>
       </c>
       <c r="R71" t="n">
-        <v>6897234</v>
+        <v>6897207</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8456,7 +8456,7 @@
         <v>133828803</v>
       </c>
       <c r="B72" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8565,32 +8565,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133828843</v>
+        <v>133828787</v>
       </c>
       <c r="B73" t="n">
-        <v>80479</v>
+        <v>83343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8600,13 +8600,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>518502</v>
+        <v>518402</v>
       </c>
       <c r="R73" t="n">
-        <v>6897111</v>
+        <v>6897136</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8672,32 +8672,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133828787</v>
+        <v>133828843</v>
       </c>
       <c r="B74" t="n">
-        <v>83336</v>
+        <v>80486</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518402</v>
+        <v>518502</v>
       </c>
       <c r="R74" t="n">
-        <v>6897136</v>
+        <v>6897111</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8779,32 +8779,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133828849</v>
+        <v>133828771</v>
       </c>
       <c r="B75" t="n">
-        <v>80474</v>
+        <v>80486</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8814,13 +8814,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>518564</v>
+        <v>518411</v>
       </c>
       <c r="R75" t="n">
-        <v>6897207</v>
+        <v>6897234</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8886,10 +8886,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133828815</v>
+        <v>133828826</v>
       </c>
       <c r="B76" t="n">
-        <v>80474</v>
+        <v>83343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8897,21 +8897,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>518230</v>
+        <v>518269</v>
       </c>
       <c r="R76" t="n">
-        <v>6896858</v>
+        <v>6896902</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8993,32 +8993,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133828772</v>
+        <v>133828815</v>
       </c>
       <c r="B77" t="n">
-        <v>99181</v>
+        <v>80481</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>518419</v>
+        <v>518230</v>
       </c>
       <c r="R77" t="n">
-        <v>6897228</v>
+        <v>6896858</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9073,12 +9073,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>7 ex</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9105,32 +9100,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133828826</v>
+        <v>133828772</v>
       </c>
       <c r="B78" t="n">
-        <v>83336</v>
+        <v>99188</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9140,10 +9135,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>518269</v>
+        <v>518419</v>
       </c>
       <c r="R78" t="n">
-        <v>6896902</v>
+        <v>6897228</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9175,7 +9170,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9185,7 +9180,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9215,7 +9215,7 @@
         <v>133828836</v>
       </c>
       <c r="B79" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>133828780</v>
       </c>
       <c r="B80" t="n">
-        <v>97294</v>
+        <v>97301</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9426,10 +9426,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133828782</v>
+        <v>133828799</v>
       </c>
       <c r="B81" t="n">
-        <v>80474</v>
+        <v>57975</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9437,34 +9437,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>518424</v>
+        <v>518312</v>
       </c>
       <c r="R81" t="n">
-        <v>6897159</v>
+        <v>6896987</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9496,7 +9504,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9506,7 +9514,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9536,7 +9549,7 @@
         <v>133828786</v>
       </c>
       <c r="B82" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9645,10 +9658,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133828799</v>
+        <v>133828782</v>
       </c>
       <c r="B83" t="n">
-        <v>57975</v>
+        <v>80481</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9656,42 +9669,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Grubban, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>518312</v>
+        <v>518424</v>
       </c>
       <c r="R83" t="n">
-        <v>6896987</v>
+        <v>6897159</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9723,7 +9728,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9733,12 +9738,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9765,32 +9765,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133828791</v>
+        <v>133828814</v>
       </c>
       <c r="B84" t="n">
-        <v>83336</v>
+        <v>99188</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518371</v>
+        <v>518236</v>
       </c>
       <c r="R84" t="n">
-        <v>6897086</v>
+        <v>6896855</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9845,7 +9845,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9872,32 +9877,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133828830</v>
+        <v>133828791</v>
       </c>
       <c r="B85" t="n">
-        <v>99181</v>
+        <v>83343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9907,10 +9912,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518373</v>
+        <v>518371</v>
       </c>
       <c r="R85" t="n">
-        <v>6897009</v>
+        <v>6897086</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9942,7 +9947,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9952,12 +9957,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>9 ex</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9984,32 +9984,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133828814</v>
+        <v>133828835</v>
       </c>
       <c r="B86" t="n">
-        <v>99181</v>
+        <v>80481</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10019,10 +10019,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518236</v>
+        <v>518407</v>
       </c>
       <c r="R86" t="n">
-        <v>6896855</v>
+        <v>6897030</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10064,12 +10064,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>45 ex</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10096,32 +10091,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133828781</v>
+        <v>133828830</v>
       </c>
       <c r="B87" t="n">
-        <v>83336</v>
+        <v>99188</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10131,10 +10126,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518427</v>
+        <v>518373</v>
       </c>
       <c r="R87" t="n">
-        <v>6897159</v>
+        <v>6897009</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10166,7 +10161,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10176,7 +10171,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10203,10 +10203,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133828835</v>
+        <v>133828781</v>
       </c>
       <c r="B88" t="n">
-        <v>80474</v>
+        <v>83343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10214,21 +10214,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10238,10 +10238,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>518407</v>
+        <v>518427</v>
       </c>
       <c r="R88" t="n">
-        <v>6897030</v>
+        <v>6897159</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10310,32 +10310,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133828838</v>
+        <v>133828810</v>
       </c>
       <c r="B89" t="n">
-        <v>79116</v>
+        <v>80486</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10345,10 +10345,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>518440</v>
+        <v>518240</v>
       </c>
       <c r="R89" t="n">
-        <v>6897045</v>
+        <v>6896871</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10420,7 +10420,7 @@
         <v>133828844</v>
       </c>
       <c r="B90" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10524,10 +10524,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133828804</v>
+        <v>133828838</v>
       </c>
       <c r="B91" t="n">
-        <v>80474</v>
+        <v>79123</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10535,21 +10535,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10559,10 +10559,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>518231</v>
+        <v>518440</v>
       </c>
       <c r="R91" t="n">
-        <v>6896913</v>
+        <v>6897045</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10631,32 +10631,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133828810</v>
+        <v>133828834</v>
       </c>
       <c r="B92" t="n">
-        <v>80479</v>
+        <v>80481</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10666,13 +10666,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>518240</v>
+        <v>518405</v>
       </c>
       <c r="R92" t="n">
-        <v>6896871</v>
+        <v>6897020</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10738,10 +10738,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133828834</v>
+        <v>133828804</v>
       </c>
       <c r="B93" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10773,13 +10773,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>518405</v>
+        <v>518231</v>
       </c>
       <c r="R93" t="n">
-        <v>6897020</v>
+        <v>6896913</v>
       </c>
       <c r="S93" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10845,32 +10845,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133828785</v>
+        <v>133828842</v>
       </c>
       <c r="B94" t="n">
-        <v>80368</v>
+        <v>79123</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10880,13 +10880,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>518394</v>
+        <v>518539</v>
       </c>
       <c r="R94" t="n">
-        <v>6897139</v>
+        <v>6897099</v>
       </c>
       <c r="S94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10952,10 +10952,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133828794</v>
+        <v>133828852</v>
       </c>
       <c r="B95" t="n">
-        <v>79359</v>
+        <v>80481</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10963,21 +10963,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10987,10 +10987,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>518380</v>
+        <v>518557</v>
       </c>
       <c r="R95" t="n">
-        <v>6897032</v>
+        <v>6897217</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11059,32 +11059,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133828842</v>
+        <v>133828785</v>
       </c>
       <c r="B96" t="n">
-        <v>79116</v>
+        <v>80375</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11094,13 +11094,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>518539</v>
+        <v>518394</v>
       </c>
       <c r="R96" t="n">
-        <v>6897099</v>
+        <v>6897139</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11166,10 +11166,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133828852</v>
+        <v>133828794</v>
       </c>
       <c r="B97" t="n">
-        <v>80474</v>
+        <v>79366</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11177,21 +11177,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11201,10 +11201,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>518557</v>
+        <v>518380</v>
       </c>
       <c r="R97" t="n">
-        <v>6897217</v>
+        <v>6897032</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 23570-2026 artfynd.xlsx
+++ b/artfynd/A 23570-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AZ116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828793</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828775</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828776</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828781</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828787</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828791</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828800</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828826</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828837</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828841</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828824</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102482</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2043,6 +2108,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102588</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2140,6 +2210,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82277751</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2237,6 +2312,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82279523</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2344,6 +2424,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828812</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2451,6 +2536,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828780</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2548,6 +2638,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102476</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2655,6 +2750,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828779</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2752,6 +2852,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102586</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2859,6 +2964,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828778</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2966,6 +3076,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828794</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3073,6 +3188,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828807</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3180,6 +3300,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828816</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3287,6 +3412,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828850</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3394,6 +3524,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828777</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3501,6 +3636,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828798</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3608,6 +3748,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828773</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3715,6 +3860,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828836</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3822,6 +3972,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828847</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3919,6 +4074,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102491</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4016,6 +4176,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102495</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4123,6 +4288,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828788</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4230,6 +4400,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828795</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4337,6 +4512,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828796</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4444,6 +4624,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828838</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4551,6 +4736,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828842</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4658,6 +4848,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828785</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4755,6 +4950,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102477</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4852,6 +5052,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102483</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4949,6 +5154,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102484</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5046,6 +5256,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102488</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5143,6 +5358,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102489</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5240,6 +5460,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102493</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5337,6 +5562,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102496</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5434,6 +5664,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102507</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5531,6 +5766,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102575</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5628,6 +5868,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102576</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5725,6 +5970,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102577</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5822,6 +6072,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102578</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5919,6 +6174,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102579</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6016,6 +6276,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102580</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6113,6 +6378,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102581</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6210,6 +6480,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102582</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6307,6 +6582,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102583</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6404,6 +6684,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102584</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6501,6 +6786,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102585</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6598,6 +6888,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102587</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6695,6 +6990,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102589</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6796,6 +7096,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82278151</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6897,6 +7202,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82278154</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6998,6 +7308,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82278155</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7099,6 +7414,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82278159</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7196,6 +7516,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82279525</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7303,6 +7628,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828782</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7410,6 +7740,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828804</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7517,6 +7852,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828806</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7624,6 +7964,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828808</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7731,6 +8076,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828809</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7838,6 +8188,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828811</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7945,6 +8300,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828813</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8052,6 +8412,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828815</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8159,6 +8524,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828820</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8266,6 +8636,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828821</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8373,6 +8748,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828831</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8480,6 +8860,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828834</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8587,6 +8972,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828835</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8694,6 +9084,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828844</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8801,6 +9196,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828849</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8908,6 +9308,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828852</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9005,6 +9410,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102481</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9102,6 +9512,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102492</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9209,6 +9624,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828771</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9316,6 +9736,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828810</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9423,6 +9848,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828833</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9530,6 +9960,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828843</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9650,6 +10085,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828792</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9770,6 +10210,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828797</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9890,6 +10335,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828799</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10010,6 +10460,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828801</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10130,6 +10585,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828802</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10250,6 +10710,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828817</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10370,6 +10835,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828818</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10490,6 +10960,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828819</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10610,6 +11085,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828827</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10730,6 +11210,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828839</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10850,6 +11335,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828840</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10970,6 +11460,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828848</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11082,6 +11577,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828772</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11194,6 +11694,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828783</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11306,6 +11811,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828784</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11418,6 +11928,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828786</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11530,6 +12045,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828789</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11642,6 +12162,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828790</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11754,6 +12279,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828803</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11866,6 +12396,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828805</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11978,6 +12513,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828814</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12090,6 +12630,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828822</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12202,6 +12747,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828823</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12314,6 +12864,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828825</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12426,6 +12981,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828829</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12538,6 +13098,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828830</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12650,6 +13215,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828845</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12762,6 +13332,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828851</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12859,8 +13434,130 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80102573</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>